--- a/EL MIRADOR/Noviembre/Noviembre - EL MIRADOR.xlsx
+++ b/EL MIRADOR/Noviembre/Noviembre - EL MIRADOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\EL MIRADOR\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{032D9D5D-6F51-4BAE-972C-3941ED9F199C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EECC163-49F6-4AA3-9DD5-97F27DFB1A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="367">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1026,18 +1026,6 @@
     <t>Heredia, Christian</t>
   </si>
   <si>
-    <t>VTO 14/11</t>
-  </si>
-  <si>
-    <t>PERÍODO: OCTUBRE</t>
-  </si>
-  <si>
-    <t>ADS - Abono de mantenimiento ascensores OCTUBRE del 2025</t>
-  </si>
-  <si>
-    <t>Articulos de limpieza - Mes de OCTUBRE</t>
-  </si>
-  <si>
     <t>Transf 17/10</t>
   </si>
   <si>
@@ -1124,6 +1112,36 @@
   </si>
   <si>
     <t>Aclaracion</t>
+  </si>
+  <si>
+    <t>VTO 15/12</t>
+  </si>
+  <si>
+    <t>PERÍODO: NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>ADS - Abono de mantenimiento ascensores NOVIEMBRE del 2025</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza - Mes de NOVIEMBRE</t>
+  </si>
+  <si>
+    <t>Transf 13/11</t>
+  </si>
+  <si>
+    <t>Citta Cerrajeria - Service Blindex por cierre defectuoso</t>
+  </si>
+  <si>
+    <t>Transf 18/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esponja Vulcano super fuerte - Limpieza Pileta </t>
+  </si>
+  <si>
+    <t>Servisur - Restablecimiento de emergencia generador por salto de</t>
+  </si>
+  <si>
+    <t>Transf 11/11</t>
   </si>
 </sst>
 </file>
@@ -1725,7 +1743,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="300">
+  <cellXfs count="304">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2019,6 +2037,18 @@
     <xf numFmtId="4" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2055,26 +2085,14 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2154,8 +2172,17 @@
     <xf numFmtId="1" fontId="19" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2166,23 +2193,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2720,7 +2744,7 @@
       <c r="A5" s="123"/>
       <c r="B5" s="128"/>
       <c r="C5" s="128" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="D5" s="128"/>
       <c r="E5" s="128" t="s">
@@ -2763,108 +2787,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="241" t="s">
+      <c r="A14" s="249" t="s">
         <v>265</v>
       </c>
-      <c r="B14" s="241"/>
-      <c r="C14" s="241"/>
-      <c r="D14" s="241"/>
-      <c r="E14" s="241"/>
-      <c r="F14" s="241"/>
-      <c r="G14" s="241"/>
-      <c r="H14" s="241"/>
-      <c r="I14" s="241"/>
-      <c r="J14" s="241"/>
+      <c r="B14" s="249"/>
+      <c r="C14" s="249"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
+      <c r="F14" s="249"/>
+      <c r="G14" s="249"/>
+      <c r="H14" s="249"/>
+      <c r="I14" s="249"/>
+      <c r="J14" s="249"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="241"/>
-      <c r="B15" s="241"/>
-      <c r="C15" s="241"/>
-      <c r="D15" s="241"/>
-      <c r="E15" s="241"/>
-      <c r="F15" s="241"/>
-      <c r="G15" s="241"/>
-      <c r="H15" s="241"/>
-      <c r="I15" s="241"/>
-      <c r="J15" s="241"/>
+      <c r="A15" s="249"/>
+      <c r="B15" s="249"/>
+      <c r="C15" s="249"/>
+      <c r="D15" s="249"/>
+      <c r="E15" s="249"/>
+      <c r="F15" s="249"/>
+      <c r="G15" s="249"/>
+      <c r="H15" s="249"/>
+      <c r="I15" s="249"/>
+      <c r="J15" s="249"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="241"/>
-      <c r="B16" s="241"/>
-      <c r="C16" s="241"/>
-      <c r="D16" s="241"/>
-      <c r="E16" s="241"/>
-      <c r="F16" s="241"/>
-      <c r="G16" s="241"/>
-      <c r="H16" s="241"/>
-      <c r="I16" s="241"/>
-      <c r="J16" s="241"/>
+      <c r="A16" s="249"/>
+      <c r="B16" s="249"/>
+      <c r="C16" s="249"/>
+      <c r="D16" s="249"/>
+      <c r="E16" s="249"/>
+      <c r="F16" s="249"/>
+      <c r="G16" s="249"/>
+      <c r="H16" s="249"/>
+      <c r="I16" s="249"/>
+      <c r="J16" s="249"/>
     </row>
     <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="241"/>
-      <c r="B17" s="241"/>
-      <c r="C17" s="241"/>
-      <c r="D17" s="241"/>
-      <c r="E17" s="241"/>
-      <c r="F17" s="241"/>
-      <c r="G17" s="241"/>
-      <c r="H17" s="241"/>
-      <c r="I17" s="241"/>
-      <c r="J17" s="241"/>
+      <c r="A17" s="249"/>
+      <c r="B17" s="249"/>
+      <c r="C17" s="249"/>
+      <c r="D17" s="249"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="249"/>
+      <c r="I17" s="249"/>
+      <c r="J17" s="249"/>
     </row>
     <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="241"/>
-      <c r="B18" s="241"/>
-      <c r="C18" s="241"/>
-      <c r="D18" s="241"/>
-      <c r="E18" s="241"/>
-      <c r="F18" s="241"/>
-      <c r="G18" s="241"/>
-      <c r="H18" s="241"/>
-      <c r="I18" s="241"/>
-      <c r="J18" s="241"/>
+      <c r="A18" s="249"/>
+      <c r="B18" s="249"/>
+      <c r="C18" s="249"/>
+      <c r="D18" s="249"/>
+      <c r="E18" s="249"/>
+      <c r="F18" s="249"/>
+      <c r="G18" s="249"/>
+      <c r="H18" s="249"/>
+      <c r="I18" s="249"/>
+      <c r="J18" s="249"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="100"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="250" t="s">
-        <v>328</v>
-      </c>
-      <c r="B20" s="250"/>
-      <c r="C20" s="250"/>
-      <c r="D20" s="250"/>
-      <c r="E20" s="250"/>
-      <c r="F20" s="250"/>
-      <c r="G20" s="250"/>
-      <c r="H20" s="250"/>
-      <c r="I20" s="250"/>
-      <c r="J20" s="250"/>
+      <c r="A20" s="258" t="s">
+        <v>357</v>
+      </c>
+      <c r="B20" s="258"/>
+      <c r="C20" s="258"/>
+      <c r="D20" s="258"/>
+      <c r="E20" s="258"/>
+      <c r="F20" s="258"/>
+      <c r="G20" s="258"/>
+      <c r="H20" s="258"/>
+      <c r="I20" s="258"/>
+      <c r="J20" s="258"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="250"/>
-      <c r="B21" s="250"/>
-      <c r="C21" s="250"/>
-      <c r="D21" s="250"/>
-      <c r="E21" s="250"/>
-      <c r="F21" s="250"/>
-      <c r="G21" s="250"/>
-      <c r="H21" s="250"/>
-      <c r="I21" s="250"/>
-      <c r="J21" s="250"/>
+      <c r="A21" s="258"/>
+      <c r="B21" s="258"/>
+      <c r="C21" s="258"/>
+      <c r="D21" s="258"/>
+      <c r="E21" s="258"/>
+      <c r="F21" s="258"/>
+      <c r="G21" s="258"/>
+      <c r="H21" s="258"/>
+      <c r="I21" s="258"/>
+      <c r="J21" s="258"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="250"/>
-      <c r="B22" s="250"/>
-      <c r="C22" s="250"/>
-      <c r="D22" s="250"/>
-      <c r="E22" s="250"/>
-      <c r="F22" s="250"/>
-      <c r="G22" s="250"/>
-      <c r="H22" s="250"/>
-      <c r="I22" s="250"/>
-      <c r="J22" s="250"/>
+      <c r="A22" s="258"/>
+      <c r="B22" s="258"/>
+      <c r="C22" s="258"/>
+      <c r="D22" s="258"/>
+      <c r="E22" s="258"/>
+      <c r="F22" s="258"/>
+      <c r="G22" s="258"/>
+      <c r="H22" s="258"/>
+      <c r="I22" s="258"/>
+      <c r="J22" s="258"/>
     </row>
     <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="100"/>
@@ -3536,7 +3560,7 @@
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D59" s="44">
         <v>56231.41</v>
@@ -3555,7 +3579,7 @@
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D60" s="44">
         <v>64940.71</v>
@@ -3632,9 +3656,9 @@
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="D63" s="44">
+        <v>336</v>
+      </c>
+      <c r="D63" s="300">
         <v>160913</v>
       </c>
       <c r="E63" s="58">
@@ -3673,9 +3697,9 @@
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="D64" s="44">
+        <v>336</v>
+      </c>
+      <c r="D64" s="300">
         <v>7907</v>
       </c>
       <c r="E64" s="58">
@@ -3714,9 +3738,9 @@
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="D65" s="44">
+        <v>336</v>
+      </c>
+      <c r="D65" s="300">
         <v>7907</v>
       </c>
       <c r="E65" s="58">
@@ -3813,7 +3837,7 @@
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D68" s="220">
         <v>242436.29</v>
@@ -3865,42 +3889,42 @@
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="D69" s="220">
-        <v>561764.05000000005</v>
+        <v>334</v>
+      </c>
+      <c r="D69" s="301">
+        <v>797235.97</v>
       </c>
       <c r="E69" s="68">
         <f>D69*93.2%</f>
-        <v>523564.09460000007</v>
+        <v>743023.92404000007</v>
       </c>
       <c r="F69" s="58">
         <f>$D69*1.08%</f>
-        <v>6067.0517400000008</v>
+        <v>8610.1484760000003</v>
       </c>
       <c r="G69" s="58">
         <f>$D69*1.28%</f>
-        <v>7190.5798400000012</v>
+        <v>10204.620416</v>
       </c>
       <c r="H69" s="58">
         <f>$D69*1.21%</f>
-        <v>6797.3450050000001</v>
+        <v>9646.5552369999987</v>
       </c>
       <c r="I69" s="58">
         <f>$D69*1.49%</f>
-        <v>8370.284345</v>
+        <v>11878.815952999999</v>
       </c>
       <c r="J69" s="58">
         <f>D69*1.74%</f>
-        <v>9774.6944700000004</v>
+        <v>13871.905877999998</v>
       </c>
       <c r="K69" s="43">
         <f>D69</f>
-        <v>561764.05000000005</v>
+        <v>797235.97</v>
       </c>
       <c r="L69" s="75">
         <f>SUM(E69:J69)</f>
-        <v>561764.05000000016</v>
+        <v>797235.97</v>
       </c>
       <c r="M69" s="86"/>
       <c r="N69" s="86"/>
@@ -3911,7 +3935,7 @@
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D70" s="221">
         <v>200479.44</v>
@@ -3957,42 +3981,42 @@
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
-        <v>336</v>
-      </c>
-      <c r="D71" s="221">
-        <v>2000000</v>
+        <v>332</v>
+      </c>
+      <c r="D71" s="302">
+        <v>2334594.12</v>
       </c>
       <c r="E71" s="68">
         <f t="shared" si="7"/>
-        <v>1864000</v>
+        <v>2175841.7198400004</v>
       </c>
       <c r="F71" s="58">
         <f t="shared" si="8"/>
-        <v>21600</v>
+        <v>25213.616496000002</v>
       </c>
       <c r="G71" s="58">
         <f t="shared" si="9"/>
-        <v>25600</v>
+        <v>29882.804736000002</v>
       </c>
       <c r="H71" s="58">
         <f t="shared" si="10"/>
-        <v>24200</v>
+        <v>28248.588852000001</v>
       </c>
       <c r="I71" s="58">
         <f t="shared" si="11"/>
-        <v>29800</v>
+        <v>34785.452388000005</v>
       </c>
       <c r="J71" s="58">
         <f t="shared" si="12"/>
-        <v>34800</v>
+        <v>40621.937687999998</v>
       </c>
       <c r="K71" s="43">
         <f t="shared" si="13"/>
-        <v>2000000</v>
+        <v>2334594.12</v>
       </c>
       <c r="L71" s="75">
         <f t="shared" si="14"/>
-        <v>2000000</v>
+        <v>2334594.1200000006</v>
       </c>
       <c r="M71" s="86"/>
       <c r="N71" s="86"/>
@@ -4002,16 +4026,15 @@
         <v>246</v>
       </c>
       <c r="B72" s="6"/>
-      <c r="C72" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="D72" s="44">
-        <f>109824+3824</f>
-        <v>113648</v>
+      <c r="C72" s="229" t="s">
+        <v>337</v>
+      </c>
+      <c r="D72" s="300">
+        <v>109824</v>
       </c>
       <c r="E72" s="68">
         <f>D72</f>
-        <v>113648</v>
+        <v>109824</v>
       </c>
       <c r="F72" s="58"/>
       <c r="G72" s="58"/>
@@ -4020,11 +4043,11 @@
       <c r="J72" s="58"/>
       <c r="K72" s="43">
         <f t="shared" si="13"/>
-        <v>113648</v>
+        <v>109824</v>
       </c>
       <c r="L72" s="75">
         <f>E72+J72+I72+H72+G72+F72</f>
-        <v>113648</v>
+        <v>109824</v>
       </c>
       <c r="M72" s="86">
         <f>L72-D72</f>
@@ -4037,11 +4060,11 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="35" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D73" s="44">
         <v>309917.37</v>
@@ -4072,7 +4095,7 @@
       </c>
       <c r="B74" s="35"/>
       <c r="C74" s="35" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D74" s="44">
         <v>30000</v>
@@ -4109,7 +4132,7 @@
       </c>
       <c r="B75" s="35"/>
       <c r="C75" s="35" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D75" s="44">
         <v>6170.82</v>
@@ -4161,7 +4184,7 @@
       </c>
       <c r="B76" s="35"/>
       <c r="C76" s="35" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D76" s="44">
         <v>5794.2</v>
@@ -4213,7 +4236,7 @@
       </c>
       <c r="B77" s="35"/>
       <c r="C77" s="35" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D77" s="44">
         <v>374755.03</v>
@@ -4265,7 +4288,7 @@
       </c>
       <c r="B78" s="35"/>
       <c r="C78" s="35" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D78" s="44">
         <v>976755.57</v>
@@ -4314,7 +4337,7 @@
       </c>
       <c r="B79" s="35"/>
       <c r="C79" s="35" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="D79" s="44">
         <v>982560.93</v>
@@ -4394,10 +4417,16 @@
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="156"/>
+      <c r="A81" s="303" t="s">
+        <v>365</v>
+      </c>
       <c r="B81" s="154"/>
-      <c r="C81" s="154"/>
-      <c r="D81" s="44"/>
+      <c r="C81" s="154" t="s">
+        <v>366</v>
+      </c>
+      <c r="D81" s="300">
+        <v>60000</v>
+      </c>
       <c r="E81" s="68"/>
       <c r="F81" s="68"/>
       <c r="G81" s="68"/>
@@ -4406,7 +4435,7 @@
       <c r="J81" s="58"/>
       <c r="K81" s="43">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="L81" s="75">
         <f t="shared" si="15"/>
@@ -4419,9 +4448,9 @@
       </c>
     </row>
     <row r="82" spans="1:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="248"/>
-      <c r="B82" s="249"/>
-      <c r="C82" s="251"/>
+      <c r="A82" s="256"/>
+      <c r="B82" s="257"/>
+      <c r="C82" s="259"/>
       <c r="D82" s="44"/>
       <c r="E82" s="68"/>
       <c r="F82" s="68"/>
@@ -4444,9 +4473,9 @@
       </c>
     </row>
     <row r="83" spans="1:14" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="248"/>
-      <c r="B83" s="249"/>
-      <c r="C83" s="251"/>
+      <c r="A83" s="256"/>
+      <c r="B83" s="257"/>
+      <c r="C83" s="259"/>
       <c r="D83" s="44"/>
       <c r="E83" s="68"/>
       <c r="F83" s="68"/>
@@ -4547,43 +4576,43 @@
       <c r="C87" s="34"/>
       <c r="D87" s="42">
         <f t="shared" ref="D87:J87" si="19">SUM(D68:D86)</f>
-        <v>5804281.7000000002</v>
+        <v>6430523.7400000002</v>
       </c>
       <c r="E87" s="42">
         <f t="shared" si="19"/>
-        <v>5440432.9895600006</v>
+        <v>5967910.5388399996</v>
       </c>
       <c r="F87" s="42">
         <f t="shared" si="19"/>
-        <v>57787.736364000004</v>
+        <v>63944.449596000006</v>
       </c>
       <c r="G87" s="42">
         <f t="shared" si="19"/>
-        <v>68489.169024000003</v>
+        <v>75786.014335999993</v>
       </c>
       <c r="H87" s="42">
         <f t="shared" si="19"/>
-        <v>64743.667592999991</v>
+        <v>71641.466676999989</v>
       </c>
       <c r="I87" s="42">
         <f t="shared" si="19"/>
-        <v>79725.673317000008</v>
+        <v>88219.657313000003</v>
       </c>
       <c r="J87" s="42">
         <f t="shared" si="19"/>
-        <v>93102.464141999997</v>
+        <v>103021.61323799999</v>
       </c>
       <c r="K87" s="43">
         <f>E87+J87+F87+G87+H87+I87</f>
-        <v>5804281.7000000011</v>
+        <v>6370523.7400000002</v>
       </c>
       <c r="L87" s="69" t="str">
         <f>IF(D87=K87, "", "Error")</f>
-        <v/>
+        <v>Error</v>
       </c>
       <c r="M87" s="86">
         <f>D87-K87</f>
-        <v>0</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -4629,50 +4658,56 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="B91" s="35"/>
       <c r="C91" s="35" t="s">
-        <v>332</v>
-      </c>
-      <c r="D91" s="44">
-        <v>467500</v>
+        <v>361</v>
+      </c>
+      <c r="D91" s="300">
+        <v>442900</v>
       </c>
       <c r="E91" s="68">
         <f>D91*93.2%</f>
-        <v>435710</v>
+        <v>412782.80000000005</v>
       </c>
       <c r="F91" s="58">
         <f>$D91*1.08%</f>
-        <v>5049</v>
+        <v>4783.3200000000006</v>
       </c>
       <c r="G91" s="58">
         <f>$D91*1.28%</f>
-        <v>5984</v>
+        <v>5669.12</v>
       </c>
       <c r="H91" s="58">
         <f>$D91*1.21%</f>
-        <v>5656.75</v>
+        <v>5359.09</v>
       </c>
       <c r="I91" s="58">
         <f>$D91*1.49%</f>
-        <v>6965.75</v>
+        <v>6599.21</v>
       </c>
       <c r="J91" s="58">
         <f>D91*1.74%</f>
-        <v>8134.4999999999991</v>
+        <v>7706.4599999999991</v>
       </c>
       <c r="K91" s="74"/>
       <c r="L91" s="69"/>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A92" s="6"/>
+      <c r="A92" s="6" t="s">
+        <v>362</v>
+      </c>
       <c r="B92" s="35"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="44"/>
+      <c r="C92" s="35" t="s">
+        <v>363</v>
+      </c>
+      <c r="D92" s="300">
+        <v>90000</v>
+      </c>
       <c r="E92" s="68">
         <f>D92</f>
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="F92" s="58"/>
       <c r="G92" s="58"/>
@@ -4683,10 +4718,14 @@
       <c r="L92" s="69"/>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A93" s="6"/>
+      <c r="A93" s="6" t="s">
+        <v>364</v>
+      </c>
       <c r="B93" s="35"/>
       <c r="C93" s="6"/>
-      <c r="D93" s="44"/>
+      <c r="D93" s="300">
+        <v>34596.519999999997</v>
+      </c>
       <c r="E93" s="68"/>
       <c r="F93" s="58"/>
       <c r="G93" s="58"/>
@@ -4746,39 +4785,39 @@
       <c r="C97" s="33"/>
       <c r="D97" s="42">
         <f>SUM(D91:D96)</f>
-        <v>467500</v>
+        <v>567496.52</v>
       </c>
       <c r="E97" s="42">
         <f t="shared" ref="E97:J97" si="20">SUM(E91:E96)</f>
-        <v>435710</v>
+        <v>502782.80000000005</v>
       </c>
       <c r="F97" s="42">
         <f t="shared" si="20"/>
-        <v>5049</v>
+        <v>4783.3200000000006</v>
       </c>
       <c r="G97" s="42">
         <f t="shared" si="20"/>
-        <v>5984</v>
+        <v>5669.12</v>
       </c>
       <c r="H97" s="42">
         <f t="shared" si="20"/>
-        <v>5656.75</v>
+        <v>5359.09</v>
       </c>
       <c r="I97" s="42">
         <f t="shared" si="20"/>
-        <v>6965.75</v>
+        <v>6599.21</v>
       </c>
       <c r="J97" s="42">
         <f t="shared" si="20"/>
-        <v>8134.4999999999991</v>
+        <v>7706.4599999999991</v>
       </c>
       <c r="K97" s="43">
         <f>E97+J97+F97+G97+H97+I97</f>
-        <v>467500</v>
+        <v>532900</v>
       </c>
       <c r="L97" s="69" t="str">
         <f>IF(D97=K97, "", "Error")</f>
-        <v/>
+        <v>Error</v>
       </c>
       <c r="N97" s="43"/>
     </row>
@@ -4859,7 +4898,7 @@
         <v>13114.38</v>
       </c>
       <c r="L101" s="69" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.3">
@@ -5123,43 +5162,43 @@
       <c r="C111" s="4"/>
       <c r="D111" s="91">
         <f t="shared" ref="D111:J111" si="23">SUM(D109+D57+D52+D107+D104+D97+D87+D66+D47+D42+D61)</f>
-        <v>11000000</v>
+        <v>11726238.560000001</v>
       </c>
       <c r="E111" s="91">
         <f t="shared" si="23"/>
-        <v>10282842.445160002</v>
+        <v>10877392.794439999</v>
       </c>
       <c r="F111" s="91">
         <f t="shared" si="23"/>
-        <v>113901.49400400001</v>
+        <v>119792.52723600001</v>
       </c>
       <c r="G111" s="91">
         <f t="shared" si="23"/>
-        <v>134994.36326400004</v>
+        <v>141976.32857600003</v>
       </c>
       <c r="H111" s="91">
         <f t="shared" si="23"/>
-        <v>127611.859023</v>
+        <v>134211.99810699996</v>
       </c>
       <c r="I111" s="91">
         <f t="shared" si="23"/>
-        <v>157141.87598700004</v>
+        <v>165269.31998300002</v>
       </c>
       <c r="J111" s="91">
         <f t="shared" si="23"/>
-        <v>183507.96256200003</v>
+        <v>192999.07165800003</v>
       </c>
       <c r="K111" s="61">
         <f>E111+J111+F111+G111+H111+I111</f>
-        <v>11000000.000000002</v>
+        <v>11631642.039999999</v>
       </c>
       <c r="L111" s="69" t="str">
         <f>IF(D111=K111, "", "Error")</f>
-        <v/>
+        <v>Error</v>
       </c>
       <c r="M111" s="86">
         <f>D111-K111</f>
-        <v>0</v>
+        <v>94596.520000001416</v>
       </c>
     </row>
     <row r="112" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5184,7 +5223,7 @@
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C114" s="136">
         <v>25000</v>
@@ -5197,7 +5236,7 @@
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C115" s="136">
         <v>25000</v>
@@ -5210,7 +5249,7 @@
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="C116" s="136">
         <v>12000</v>
@@ -5223,7 +5262,7 @@
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C117" s="136">
         <v>12000</v>
@@ -5236,7 +5275,7 @@
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C118" s="136">
         <v>12000</v>
@@ -5249,7 +5288,7 @@
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C119" s="136">
         <v>12000</v>
@@ -5262,7 +5301,7 @@
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="C120" s="136">
         <v>12000</v>
@@ -5275,7 +5314,7 @@
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C121" s="136">
         <v>24000</v>
@@ -5288,7 +5327,7 @@
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C122" s="136">
         <f>3*12000</f>
@@ -5302,7 +5341,7 @@
     </row>
     <row r="123" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C123" s="136">
         <f>3*12000</f>
@@ -5344,12 +5383,12 @@
       <c r="I126" s="60"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A127" s="246" t="s">
+      <c r="A127" s="254" t="s">
         <v>36</v>
       </c>
-      <c r="B127" s="247"/>
-      <c r="C127" s="247"/>
-      <c r="D127" s="247"/>
+      <c r="B127" s="255"/>
+      <c r="C127" s="255"/>
+      <c r="D127" s="255"/>
       <c r="E127" s="82" t="s">
         <v>11</v>
       </c>
@@ -5370,8 +5409,8 @@
       </c>
     </row>
     <row r="128" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="248"/>
-      <c r="B128" s="249"/>
+      <c r="A128" s="256"/>
+      <c r="B128" s="257"/>
       <c r="C128" s="84"/>
       <c r="D128" s="44"/>
       <c r="E128" s="68">
@@ -5385,8 +5424,8 @@
       <c r="J128" s="58"/>
     </row>
     <row r="129" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="248"/>
-      <c r="B129" s="249"/>
+      <c r="A129" s="256"/>
+      <c r="B129" s="257"/>
       <c r="C129" s="84"/>
       <c r="D129" s="44"/>
       <c r="E129" s="68"/>
@@ -5397,11 +5436,11 @@
       <c r="J129" s="58"/>
     </row>
     <row r="130" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A130" s="243" t="s">
+      <c r="A130" s="251" t="s">
         <v>17</v>
       </c>
-      <c r="B130" s="244"/>
-      <c r="C130" s="245"/>
+      <c r="B130" s="252"/>
+      <c r="C130" s="253"/>
       <c r="D130" s="81">
         <f>SUM(D128:D129)</f>
         <v>0</v>
@@ -5440,7 +5479,7 @@
       </c>
       <c r="B133" s="39">
         <f>D111</f>
-        <v>11000000</v>
+        <v>11726238.560000001</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5449,24 +5488,24 @@
       </c>
       <c r="B134" s="41">
         <f>D111-D109</f>
-        <v>9608383.8599999994</v>
-      </c>
-      <c r="D134" s="252" t="s">
+        <v>10334622.42</v>
+      </c>
+      <c r="D134" s="260" t="s">
         <v>323</v>
       </c>
-      <c r="E134" s="252"/>
-      <c r="F134" s="252"/>
-      <c r="G134" s="252"/>
-      <c r="H134" s="252"/>
-      <c r="I134" s="252"/>
+      <c r="E134" s="260"/>
+      <c r="F134" s="260"/>
+      <c r="G134" s="260"/>
+      <c r="H134" s="260"/>
+      <c r="I134" s="260"/>
     </row>
     <row r="135" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="D135" s="252"/>
-      <c r="E135" s="252"/>
-      <c r="F135" s="252"/>
-      <c r="G135" s="252"/>
-      <c r="H135" s="252"/>
-      <c r="I135" s="252"/>
+      <c r="D135" s="260"/>
+      <c r="E135" s="260"/>
+      <c r="F135" s="260"/>
+      <c r="G135" s="260"/>
+      <c r="H135" s="260"/>
+      <c r="I135" s="260"/>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A136" s="16" t="s">
@@ -5474,12 +5513,12 @@
       </c>
       <c r="B136" s="17"/>
       <c r="C136" s="18"/>
-      <c r="D136" s="252"/>
-      <c r="E136" s="252"/>
-      <c r="F136" s="252"/>
-      <c r="G136" s="252"/>
-      <c r="H136" s="252"/>
-      <c r="I136" s="252"/>
+      <c r="D136" s="260"/>
+      <c r="E136" s="260"/>
+      <c r="F136" s="260"/>
+      <c r="G136" s="260"/>
+      <c r="H136" s="260"/>
+      <c r="I136" s="260"/>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A137" s="19" t="s">
@@ -5489,12 +5528,12 @@
         <v>-1505552.0204280028</v>
       </c>
       <c r="C137" s="20"/>
-      <c r="D137" s="252"/>
-      <c r="E137" s="252"/>
-      <c r="F137" s="252"/>
-      <c r="G137" s="252"/>
-      <c r="H137" s="252"/>
-      <c r="I137" s="252"/>
+      <c r="D137" s="260"/>
+      <c r="E137" s="260"/>
+      <c r="F137" s="260"/>
+      <c r="G137" s="260"/>
+      <c r="H137" s="260"/>
+      <c r="I137" s="260"/>
     </row>
     <row r="138" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A138" s="21" t="s">
@@ -5507,12 +5546,12 @@
       <c r="C138" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D138" s="252"/>
-      <c r="E138" s="252"/>
-      <c r="F138" s="252"/>
-      <c r="G138" s="252"/>
-      <c r="H138" s="252"/>
-      <c r="I138" s="252"/>
+      <c r="D138" s="260"/>
+      <c r="E138" s="260"/>
+      <c r="F138" s="260"/>
+      <c r="G138" s="260"/>
+      <c r="H138" s="260"/>
+      <c r="I138" s="260"/>
     </row>
     <row r="139" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A139" s="21" t="s">
@@ -5520,15 +5559,15 @@
       </c>
       <c r="B139" s="85">
         <f>-B134</f>
-        <v>-9608383.8599999994</v>
+        <v>-10334622.42</v>
       </c>
       <c r="C139" s="18"/>
-      <c r="D139" s="252"/>
-      <c r="E139" s="252"/>
-      <c r="F139" s="252"/>
-      <c r="G139" s="252"/>
-      <c r="H139" s="252"/>
-      <c r="I139" s="252"/>
+      <c r="D139" s="260"/>
+      <c r="E139" s="260"/>
+      <c r="F139" s="260"/>
+      <c r="G139" s="260"/>
+      <c r="H139" s="260"/>
+      <c r="I139" s="260"/>
       <c r="K139" s="44"/>
     </row>
     <row r="140" spans="1:13" x14ac:dyDescent="0.3">
@@ -5540,12 +5579,12 @@
         <v>0</v>
       </c>
       <c r="C140" s="18"/>
-      <c r="D140" s="252"/>
-      <c r="E140" s="252"/>
-      <c r="F140" s="252"/>
-      <c r="G140" s="252"/>
-      <c r="H140" s="252"/>
-      <c r="I140" s="252"/>
+      <c r="D140" s="260"/>
+      <c r="E140" s="260"/>
+      <c r="F140" s="260"/>
+      <c r="G140" s="260"/>
+      <c r="H140" s="260"/>
+      <c r="I140" s="260"/>
       <c r="K140" s="52"/>
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.3">
@@ -5557,12 +5596,12 @@
         <v>0</v>
       </c>
       <c r="C141" s="18"/>
-      <c r="D141" s="252"/>
-      <c r="E141" s="252"/>
-      <c r="F141" s="252"/>
-      <c r="G141" s="252"/>
-      <c r="H141" s="252"/>
-      <c r="I141" s="252"/>
+      <c r="D141" s="260"/>
+      <c r="E141" s="260"/>
+      <c r="F141" s="260"/>
+      <c r="G141" s="260"/>
+      <c r="H141" s="260"/>
+      <c r="I141" s="260"/>
       <c r="K141" s="52"/>
     </row>
     <row r="142" spans="1:13" x14ac:dyDescent="0.3">
@@ -5574,12 +5613,12 @@
         <v>0</v>
       </c>
       <c r="C142" s="22"/>
-      <c r="D142" s="252"/>
-      <c r="E142" s="252"/>
-      <c r="F142" s="252"/>
-      <c r="G142" s="252"/>
-      <c r="H142" s="252"/>
-      <c r="I142" s="252"/>
+      <c r="D142" s="260"/>
+      <c r="E142" s="260"/>
+      <c r="F142" s="260"/>
+      <c r="G142" s="260"/>
+      <c r="H142" s="260"/>
+      <c r="I142" s="260"/>
     </row>
     <row r="143" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A143" s="21" t="s">
@@ -5589,12 +5628,12 @@
         <v>0</v>
       </c>
       <c r="C143" s="22"/>
-      <c r="D143" s="252"/>
-      <c r="E143" s="252"/>
-      <c r="F143" s="252"/>
-      <c r="G143" s="252"/>
-      <c r="H143" s="252"/>
-      <c r="I143" s="252"/>
+      <c r="D143" s="260"/>
+      <c r="E143" s="260"/>
+      <c r="F143" s="260"/>
+      <c r="G143" s="260"/>
+      <c r="H143" s="260"/>
+      <c r="I143" s="260"/>
     </row>
     <row r="144" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A144" s="21" t="s">
@@ -5605,27 +5644,27 @@
         <v>-206000</v>
       </c>
       <c r="C144" s="22"/>
-      <c r="D144" s="252"/>
-      <c r="E144" s="252"/>
-      <c r="F144" s="252"/>
-      <c r="G144" s="252"/>
-      <c r="H144" s="252"/>
-      <c r="I144" s="252"/>
+      <c r="D144" s="260"/>
+      <c r="E144" s="260"/>
+      <c r="F144" s="260"/>
+      <c r="G144" s="260"/>
+      <c r="H144" s="260"/>
+      <c r="I144" s="260"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="21" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B145" s="195">
         <v>400000</v>
       </c>
       <c r="C145" s="22"/>
-      <c r="D145" s="252"/>
-      <c r="E145" s="252"/>
-      <c r="F145" s="252"/>
-      <c r="G145" s="252"/>
-      <c r="H145" s="252"/>
-      <c r="I145" s="252"/>
+      <c r="D145" s="260"/>
+      <c r="E145" s="260"/>
+      <c r="F145" s="260"/>
+      <c r="G145" s="260"/>
+      <c r="H145" s="260"/>
+      <c r="I145" s="260"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="19" t="s">
@@ -5633,25 +5672,25 @@
       </c>
       <c r="B146" s="23">
         <f>SUM(B137:B145)</f>
-        <v>-979600.31345474347</v>
+        <v>-1705838.873454744</v>
       </c>
       <c r="C146" s="70"/>
-      <c r="D146" s="252"/>
-      <c r="E146" s="252"/>
-      <c r="F146" s="252"/>
-      <c r="G146" s="252"/>
-      <c r="H146" s="252"/>
-      <c r="I146" s="252"/>
+      <c r="D146" s="260"/>
+      <c r="E146" s="260"/>
+      <c r="F146" s="260"/>
+      <c r="G146" s="260"/>
+      <c r="H146" s="260"/>
+      <c r="I146" s="260"/>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="22"/>
       <c r="C147" s="18"/>
-      <c r="D147" s="252"/>
-      <c r="E147" s="252"/>
-      <c r="F147" s="252"/>
-      <c r="G147" s="252"/>
-      <c r="H147" s="252"/>
-      <c r="I147" s="252"/>
+      <c r="D147" s="260"/>
+      <c r="E147" s="260"/>
+      <c r="F147" s="260"/>
+      <c r="G147" s="260"/>
+      <c r="H147" s="260"/>
+      <c r="I147" s="260"/>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="16" t="s">
@@ -5659,12 +5698,12 @@
       </c>
       <c r="B148" s="8"/>
       <c r="C148" s="18"/>
-      <c r="D148" s="252"/>
-      <c r="E148" s="252"/>
-      <c r="F148" s="252"/>
-      <c r="G148" s="252"/>
-      <c r="H148" s="252"/>
-      <c r="I148" s="252"/>
+      <c r="D148" s="260"/>
+      <c r="E148" s="260"/>
+      <c r="F148" s="260"/>
+      <c r="G148" s="260"/>
+      <c r="H148" s="260"/>
+      <c r="I148" s="260"/>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="19"/>
@@ -5769,50 +5808,50 @@
       <c r="R162" s="9"/>
     </row>
     <row r="165" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B165" s="242"/>
-      <c r="C165" s="242"/>
-      <c r="D165" s="242"/>
-      <c r="E165" s="242"/>
+      <c r="B165" s="250"/>
+      <c r="C165" s="250"/>
+      <c r="D165" s="250"/>
+      <c r="E165" s="250"/>
       <c r="F165" s="95"/>
       <c r="G165" s="95"/>
       <c r="H165" s="95"/>
       <c r="I165" s="95"/>
     </row>
     <row r="166" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B166" s="242"/>
-      <c r="C166" s="242"/>
-      <c r="D166" s="242"/>
-      <c r="E166" s="242"/>
+      <c r="B166" s="250"/>
+      <c r="C166" s="250"/>
+      <c r="D166" s="250"/>
+      <c r="E166" s="250"/>
       <c r="F166" s="95"/>
       <c r="G166" s="95"/>
       <c r="H166" s="95"/>
       <c r="I166" s="95"/>
     </row>
     <row r="167" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B167" s="242"/>
-      <c r="C167" s="242"/>
-      <c r="D167" s="242"/>
-      <c r="E167" s="242"/>
+      <c r="B167" s="250"/>
+      <c r="C167" s="250"/>
+      <c r="D167" s="250"/>
+      <c r="E167" s="250"/>
       <c r="F167" s="95"/>
       <c r="G167" s="95"/>
       <c r="H167" s="95"/>
       <c r="I167" s="95"/>
     </row>
     <row r="168" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B168" s="242"/>
-      <c r="C168" s="242"/>
-      <c r="D168" s="242"/>
-      <c r="E168" s="242"/>
+      <c r="B168" s="250"/>
+      <c r="C168" s="250"/>
+      <c r="D168" s="250"/>
+      <c r="E168" s="250"/>
       <c r="F168" s="95"/>
       <c r="G168" s="95"/>
       <c r="H168" s="95"/>
       <c r="I168" s="95"/>
     </row>
     <row r="169" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B169" s="242"/>
-      <c r="C169" s="242"/>
-      <c r="D169" s="242"/>
-      <c r="E169" s="242"/>
+      <c r="B169" s="250"/>
+      <c r="C169" s="250"/>
+      <c r="D169" s="250"/>
+      <c r="E169" s="250"/>
       <c r="F169" s="95"/>
       <c r="G169" s="95"/>
       <c r="H169" s="95"/>
@@ -5876,11 +5915,11 @@
       <c r="K1" s="181" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="262">
+      <c r="L1" s="266">
         <f>RESUMEN!D111-RESUMEN!D109</f>
-        <v>9608383.8599999994</v>
-      </c>
-      <c r="M1" s="263"/>
+        <v>10334622.42</v>
+      </c>
+      <c r="M1" s="267"/>
       <c r="N1" s="182"/>
       <c r="O1" s="59"/>
     </row>
@@ -5910,7 +5949,7 @@
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="183" t="str">
         <f>RESUMEN!C5</f>
-        <v>PERÍODO: OCTUBRE</v>
+        <v>PERÍODO: NOVIEMBRE</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -5949,192 +5988,192 @@
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="271" t="s">
-        <v>337</v>
-      </c>
-      <c r="D5" s="272"/>
-      <c r="E5" s="272"/>
-      <c r="F5" s="272"/>
-      <c r="G5" s="272"/>
-      <c r="H5" s="272"/>
-      <c r="I5" s="272"/>
-      <c r="J5" s="272"/>
-      <c r="K5" s="272"/>
-      <c r="L5" s="272"/>
-      <c r="M5" s="272"/>
-      <c r="N5" s="273"/>
+      <c r="C5" s="275" t="s">
+        <v>333</v>
+      </c>
+      <c r="D5" s="276"/>
+      <c r="E5" s="276"/>
+      <c r="F5" s="276"/>
+      <c r="G5" s="276"/>
+      <c r="H5" s="276"/>
+      <c r="I5" s="276"/>
+      <c r="J5" s="276"/>
+      <c r="K5" s="276"/>
+      <c r="L5" s="276"/>
+      <c r="M5" s="276"/>
+      <c r="N5" s="277"/>
       <c r="O5" s="15"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="274"/>
-      <c r="D6" s="275"/>
-      <c r="E6" s="275"/>
-      <c r="F6" s="275"/>
-      <c r="G6" s="275"/>
-      <c r="H6" s="275"/>
-      <c r="I6" s="275"/>
-      <c r="J6" s="275"/>
-      <c r="K6" s="275"/>
-      <c r="L6" s="275"/>
-      <c r="M6" s="275"/>
-      <c r="N6" s="276"/>
+      <c r="C6" s="278"/>
+      <c r="D6" s="279"/>
+      <c r="E6" s="279"/>
+      <c r="F6" s="279"/>
+      <c r="G6" s="279"/>
+      <c r="H6" s="279"/>
+      <c r="I6" s="279"/>
+      <c r="J6" s="279"/>
+      <c r="K6" s="279"/>
+      <c r="L6" s="279"/>
+      <c r="M6" s="279"/>
+      <c r="N6" s="280"/>
       <c r="O6" s="15"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="274"/>
-      <c r="D7" s="275"/>
-      <c r="E7" s="275"/>
-      <c r="F7" s="275"/>
-      <c r="G7" s="275"/>
-      <c r="H7" s="275"/>
-      <c r="I7" s="275"/>
-      <c r="J7" s="275"/>
-      <c r="K7" s="275"/>
-      <c r="L7" s="275"/>
-      <c r="M7" s="275"/>
-      <c r="N7" s="276"/>
+      <c r="C7" s="278"/>
+      <c r="D7" s="279"/>
+      <c r="E7" s="279"/>
+      <c r="F7" s="279"/>
+      <c r="G7" s="279"/>
+      <c r="H7" s="279"/>
+      <c r="I7" s="279"/>
+      <c r="J7" s="279"/>
+      <c r="K7" s="279"/>
+      <c r="L7" s="279"/>
+      <c r="M7" s="279"/>
+      <c r="N7" s="280"/>
       <c r="O7" s="15"/>
     </row>
     <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="277"/>
-      <c r="D8" s="278"/>
-      <c r="E8" s="278"/>
-      <c r="F8" s="278"/>
-      <c r="G8" s="278"/>
-      <c r="H8" s="278"/>
-      <c r="I8" s="278"/>
-      <c r="J8" s="278"/>
-      <c r="K8" s="278"/>
-      <c r="L8" s="278"/>
-      <c r="M8" s="278"/>
-      <c r="N8" s="279"/>
+      <c r="C8" s="281"/>
+      <c r="D8" s="282"/>
+      <c r="E8" s="282"/>
+      <c r="F8" s="282"/>
+      <c r="G8" s="282"/>
+      <c r="H8" s="282"/>
+      <c r="I8" s="282"/>
+      <c r="J8" s="282"/>
+      <c r="K8" s="282"/>
+      <c r="L8" s="282"/>
+      <c r="M8" s="282"/>
+      <c r="N8" s="283"/>
       <c r="P8" s="86">
         <f>L1-K133</f>
-        <v>-1338773.6948400009</v>
+        <v>-612535.13484000042</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="280" t="s">
-        <v>355</v>
-      </c>
-      <c r="D9" s="281"/>
-      <c r="E9" s="281"/>
-      <c r="F9" s="281"/>
-      <c r="G9" s="281"/>
-      <c r="H9" s="281"/>
-      <c r="I9" s="281"/>
-      <c r="J9" s="281"/>
-      <c r="K9" s="281"/>
-      <c r="L9" s="281"/>
-      <c r="M9" s="281"/>
-      <c r="N9" s="282"/>
+      <c r="C9" s="284" t="s">
+        <v>351</v>
+      </c>
+      <c r="D9" s="285"/>
+      <c r="E9" s="285"/>
+      <c r="F9" s="285"/>
+      <c r="G9" s="285"/>
+      <c r="H9" s="285"/>
+      <c r="I9" s="285"/>
+      <c r="J9" s="285"/>
+      <c r="K9" s="285"/>
+      <c r="L9" s="285"/>
+      <c r="M9" s="285"/>
+      <c r="N9" s="286"/>
       <c r="P9" s="86"/>
     </row>
     <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="283"/>
-      <c r="D10" s="284"/>
-      <c r="E10" s="284"/>
-      <c r="F10" s="284"/>
-      <c r="G10" s="284"/>
-      <c r="H10" s="284"/>
-      <c r="I10" s="284"/>
-      <c r="J10" s="284"/>
-      <c r="K10" s="284"/>
-      <c r="L10" s="284"/>
-      <c r="M10" s="284"/>
-      <c r="N10" s="285"/>
+      <c r="C10" s="287"/>
+      <c r="D10" s="288"/>
+      <c r="E10" s="288"/>
+      <c r="F10" s="288"/>
+      <c r="G10" s="288"/>
+      <c r="H10" s="288"/>
+      <c r="I10" s="288"/>
+      <c r="J10" s="288"/>
+      <c r="K10" s="288"/>
+      <c r="L10" s="288"/>
+      <c r="M10" s="288"/>
+      <c r="N10" s="289"/>
       <c r="P10" s="86"/>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="253" t="s">
+      <c r="A11" s="262" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="255" t="s">
+      <c r="B11" s="290" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="253" t="s">
+      <c r="C11" s="262" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="257" t="s">
+      <c r="D11" s="292" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="257" t="s">
+      <c r="E11" s="292" t="s">
         <v>274</v>
       </c>
-      <c r="F11" s="253" t="s">
+      <c r="F11" s="262" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="253" t="s">
+      <c r="G11" s="262" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="253" t="s">
+      <c r="H11" s="262" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="264" t="s">
+      <c r="I11" s="268" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="266" t="s">
+      <c r="J11" s="270" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="266" t="s">
+      <c r="K11" s="270" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="269" t="s">
+      <c r="L11" s="273" t="s">
         <v>42</v>
       </c>
-      <c r="M11" s="266" t="s">
+      <c r="M11" s="270" t="s">
         <v>285</v>
       </c>
-      <c r="N11" s="266" t="s">
+      <c r="N11" s="270" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="254"/>
-      <c r="B12" s="256"/>
-      <c r="C12" s="254"/>
-      <c r="D12" s="258"/>
-      <c r="E12" s="258"/>
-      <c r="F12" s="254"/>
-      <c r="G12" s="254"/>
-      <c r="H12" s="254"/>
-      <c r="I12" s="265"/>
-      <c r="J12" s="267"/>
-      <c r="K12" s="267"/>
-      <c r="L12" s="270"/>
-      <c r="M12" s="267"/>
-      <c r="N12" s="267"/>
+      <c r="A12" s="263"/>
+      <c r="B12" s="291"/>
+      <c r="C12" s="263"/>
+      <c r="D12" s="293"/>
+      <c r="E12" s="293"/>
+      <c r="F12" s="263"/>
+      <c r="G12" s="263"/>
+      <c r="H12" s="263"/>
+      <c r="I12" s="269"/>
+      <c r="J12" s="271"/>
+      <c r="K12" s="271"/>
+      <c r="L12" s="274"/>
+      <c r="M12" s="271"/>
+      <c r="N12" s="271"/>
     </row>
     <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="254"/>
-      <c r="B13" s="256"/>
-      <c r="C13" s="254"/>
-      <c r="D13" s="258"/>
-      <c r="E13" s="258"/>
-      <c r="F13" s="254"/>
-      <c r="G13" s="254"/>
-      <c r="H13" s="254"/>
-      <c r="I13" s="265"/>
-      <c r="J13" s="267"/>
-      <c r="K13" s="268"/>
-      <c r="L13" s="270"/>
+      <c r="A13" s="263"/>
+      <c r="B13" s="291"/>
+      <c r="C13" s="263"/>
+      <c r="D13" s="293"/>
+      <c r="E13" s="293"/>
+      <c r="F13" s="263"/>
+      <c r="G13" s="263"/>
+      <c r="H13" s="263"/>
+      <c r="I13" s="269"/>
+      <c r="J13" s="271"/>
+      <c r="K13" s="272"/>
+      <c r="L13" s="274"/>
       <c r="M13" s="140" t="str">
         <f>RESUMEN!A20</f>
-        <v>VTO 14/11</v>
+        <v>VTO 15/12</v>
       </c>
       <c r="N13" s="139" t="str">
         <f>RESUMEN!A20</f>
-        <v>VTO 14/11</v>
+        <v>VTO 15/12</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -6183,10 +6222,10 @@
         <v>120735.58364424</v>
       </c>
       <c r="O14" s="121"/>
-      <c r="Q14" s="259" t="s">
+      <c r="Q14" s="261" t="s">
         <v>259</v>
       </c>
-      <c r="R14" s="259"/>
+      <c r="R14" s="261"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
@@ -6230,8 +6269,8 @@
         <v>143094.02505984006</v>
       </c>
       <c r="O15" s="121"/>
-      <c r="Q15" s="259"/>
-      <c r="R15" s="259"/>
+      <c r="Q15" s="261"/>
+      <c r="R15" s="261"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
@@ -6282,7 +6321,7 @@
       </c>
       <c r="R16">
         <f>RESUMEN!F111</f>
-        <v>113901.49400400001</v>
+        <v>119792.52723600001</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -6334,7 +6373,7 @@
       </c>
       <c r="R17">
         <f>RESUMEN!G111</f>
-        <v>134994.36326400004</v>
+        <v>141976.32857600003</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6386,7 +6425,7 @@
       </c>
       <c r="R18">
         <f>RESUMEN!H111</f>
-        <v>127611.859023</v>
+        <v>134211.99810699996</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -6442,7 +6481,7 @@
       </c>
       <c r="R19">
         <f>RESUMEN!I111</f>
-        <v>157141.87598700004</v>
+        <v>165269.31998300002</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -6499,7 +6538,7 @@
       </c>
       <c r="R20">
         <f>RESUMEN!J111</f>
-        <v>183507.96256200003</v>
+        <v>192999.07165800003</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -6603,7 +6642,7 @@
         <v>0.04</v>
       </c>
       <c r="P22" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -9562,7 +9601,7 @@
         <v>0.55000000000000027</v>
       </c>
       <c r="P73" s="239" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.3">
@@ -12433,36 +12472,36 @@
     <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K134" s="61">
         <f>K133-L1</f>
-        <v>1338773.6948400009</v>
+        <v>612535.13484000042</v>
       </c>
     </row>
     <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C135" s="261"/>
-      <c r="D135" s="261"/>
-      <c r="E135" s="261"/>
-      <c r="F135" s="261"/>
-      <c r="G135" s="261"/>
-      <c r="H135" s="261"/>
-      <c r="I135" s="261"/>
-      <c r="J135" s="261"/>
-      <c r="K135" s="261"/>
-      <c r="L135" s="261"/>
-      <c r="M135" s="261"/>
-      <c r="N135" s="261"/>
+      <c r="C135" s="265"/>
+      <c r="D135" s="265"/>
+      <c r="E135" s="265"/>
+      <c r="F135" s="265"/>
+      <c r="G135" s="265"/>
+      <c r="H135" s="265"/>
+      <c r="I135" s="265"/>
+      <c r="J135" s="265"/>
+      <c r="K135" s="265"/>
+      <c r="L135" s="265"/>
+      <c r="M135" s="265"/>
+      <c r="N135" s="265"/>
     </row>
     <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C136" s="261"/>
-      <c r="D136" s="261"/>
-      <c r="E136" s="261"/>
-      <c r="F136" s="261"/>
-      <c r="G136" s="261"/>
-      <c r="H136" s="261"/>
-      <c r="I136" s="261"/>
-      <c r="J136" s="261"/>
-      <c r="K136" s="261"/>
-      <c r="L136" s="261"/>
-      <c r="M136" s="261"/>
-      <c r="N136" s="261"/>
+      <c r="C136" s="265"/>
+      <c r="D136" s="265"/>
+      <c r="E136" s="265"/>
+      <c r="F136" s="265"/>
+      <c r="G136" s="265"/>
+      <c r="H136" s="265"/>
+      <c r="I136" s="265"/>
+      <c r="J136" s="265"/>
+      <c r="K136" s="265"/>
+      <c r="L136" s="265"/>
+      <c r="M136" s="265"/>
+      <c r="N136" s="265"/>
     </row>
     <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="79"/>
@@ -12479,118 +12518,118 @@
       <c r="N137" s="79"/>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C138" s="261" t="s">
+      <c r="C138" s="265" t="s">
         <v>265</v>
       </c>
-      <c r="D138" s="261"/>
-      <c r="E138" s="261"/>
-      <c r="F138" s="261"/>
-      <c r="G138" s="261"/>
-      <c r="H138" s="261"/>
-      <c r="I138" s="261"/>
-      <c r="J138" s="261"/>
-      <c r="K138" s="261"/>
-      <c r="L138" s="261"/>
-      <c r="M138" s="261"/>
-      <c r="N138" s="261"/>
+      <c r="D138" s="265"/>
+      <c r="E138" s="265"/>
+      <c r="F138" s="265"/>
+      <c r="G138" s="265"/>
+      <c r="H138" s="265"/>
+      <c r="I138" s="265"/>
+      <c r="J138" s="265"/>
+      <c r="K138" s="265"/>
+      <c r="L138" s="265"/>
+      <c r="M138" s="265"/>
+      <c r="N138" s="265"/>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C139" s="261"/>
-      <c r="D139" s="261"/>
-      <c r="E139" s="261"/>
-      <c r="F139" s="261"/>
-      <c r="G139" s="261"/>
-      <c r="H139" s="261"/>
-      <c r="I139" s="261"/>
-      <c r="J139" s="261"/>
-      <c r="K139" s="261"/>
-      <c r="L139" s="261"/>
-      <c r="M139" s="261"/>
-      <c r="N139" s="261"/>
+      <c r="C139" s="265"/>
+      <c r="D139" s="265"/>
+      <c r="E139" s="265"/>
+      <c r="F139" s="265"/>
+      <c r="G139" s="265"/>
+      <c r="H139" s="265"/>
+      <c r="I139" s="265"/>
+      <c r="J139" s="265"/>
+      <c r="K139" s="265"/>
+      <c r="L139" s="265"/>
+      <c r="M139" s="265"/>
+      <c r="N139" s="265"/>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C140" s="261"/>
-      <c r="D140" s="261"/>
-      <c r="E140" s="261"/>
-      <c r="F140" s="261"/>
-      <c r="G140" s="261"/>
-      <c r="H140" s="261"/>
-      <c r="I140" s="261"/>
-      <c r="J140" s="261"/>
-      <c r="K140" s="261"/>
-      <c r="L140" s="261"/>
-      <c r="M140" s="261"/>
-      <c r="N140" s="261"/>
+      <c r="C140" s="265"/>
+      <c r="D140" s="265"/>
+      <c r="E140" s="265"/>
+      <c r="F140" s="265"/>
+      <c r="G140" s="265"/>
+      <c r="H140" s="265"/>
+      <c r="I140" s="265"/>
+      <c r="J140" s="265"/>
+      <c r="K140" s="265"/>
+      <c r="L140" s="265"/>
+      <c r="M140" s="265"/>
+      <c r="N140" s="265"/>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C141" s="261"/>
-      <c r="D141" s="261"/>
-      <c r="E141" s="261"/>
-      <c r="F141" s="261"/>
-      <c r="G141" s="261"/>
-      <c r="H141" s="261"/>
-      <c r="I141" s="261"/>
-      <c r="J141" s="261"/>
-      <c r="K141" s="261"/>
-      <c r="L141" s="261"/>
-      <c r="M141" s="261"/>
-      <c r="N141" s="261"/>
+      <c r="C141" s="265"/>
+      <c r="D141" s="265"/>
+      <c r="E141" s="265"/>
+      <c r="F141" s="265"/>
+      <c r="G141" s="265"/>
+      <c r="H141" s="265"/>
+      <c r="I141" s="265"/>
+      <c r="J141" s="265"/>
+      <c r="K141" s="265"/>
+      <c r="L141" s="265"/>
+      <c r="M141" s="265"/>
+      <c r="N141" s="265"/>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C142" s="261"/>
-      <c r="D142" s="261"/>
-      <c r="E142" s="261"/>
-      <c r="F142" s="261"/>
-      <c r="G142" s="261"/>
-      <c r="H142" s="261"/>
-      <c r="I142" s="261"/>
-      <c r="J142" s="261"/>
-      <c r="K142" s="261"/>
-      <c r="L142" s="261"/>
-      <c r="M142" s="261"/>
-      <c r="N142" s="261"/>
+      <c r="C142" s="265"/>
+      <c r="D142" s="265"/>
+      <c r="E142" s="265"/>
+      <c r="F142" s="265"/>
+      <c r="G142" s="265"/>
+      <c r="H142" s="265"/>
+      <c r="I142" s="265"/>
+      <c r="J142" s="265"/>
+      <c r="K142" s="265"/>
+      <c r="L142" s="265"/>
+      <c r="M142" s="265"/>
+      <c r="N142" s="265"/>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C143" s="261"/>
-      <c r="D143" s="261"/>
-      <c r="E143" s="261"/>
-      <c r="F143" s="261"/>
-      <c r="G143" s="261"/>
-      <c r="H143" s="261"/>
-      <c r="I143" s="261"/>
-      <c r="J143" s="261"/>
-      <c r="K143" s="261"/>
-      <c r="L143" s="261"/>
-      <c r="M143" s="261"/>
-      <c r="N143" s="261"/>
+      <c r="C143" s="265"/>
+      <c r="D143" s="265"/>
+      <c r="E143" s="265"/>
+      <c r="F143" s="265"/>
+      <c r="G143" s="265"/>
+      <c r="H143" s="265"/>
+      <c r="I143" s="265"/>
+      <c r="J143" s="265"/>
+      <c r="K143" s="265"/>
+      <c r="L143" s="265"/>
+      <c r="M143" s="265"/>
+      <c r="N143" s="265"/>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C144" s="261"/>
-      <c r="D144" s="261"/>
-      <c r="E144" s="261"/>
-      <c r="F144" s="261"/>
-      <c r="G144" s="261"/>
-      <c r="H144" s="261"/>
-      <c r="I144" s="261"/>
-      <c r="J144" s="261"/>
-      <c r="K144" s="261"/>
-      <c r="L144" s="261"/>
-      <c r="M144" s="261"/>
-      <c r="N144" s="261"/>
+      <c r="C144" s="265"/>
+      <c r="D144" s="265"/>
+      <c r="E144" s="265"/>
+      <c r="F144" s="265"/>
+      <c r="G144" s="265"/>
+      <c r="H144" s="265"/>
+      <c r="I144" s="265"/>
+      <c r="J144" s="265"/>
+      <c r="K144" s="265"/>
+      <c r="L144" s="265"/>
+      <c r="M144" s="265"/>
+      <c r="N144" s="265"/>
     </row>
     <row r="145" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C145" s="261"/>
-      <c r="D145" s="261"/>
-      <c r="E145" s="261"/>
-      <c r="F145" s="261"/>
-      <c r="G145" s="261"/>
-      <c r="H145" s="261"/>
-      <c r="I145" s="261"/>
-      <c r="J145" s="261"/>
-      <c r="K145" s="261"/>
-      <c r="L145" s="261"/>
-      <c r="M145" s="261"/>
-      <c r="N145" s="261"/>
+      <c r="C145" s="265"/>
+      <c r="D145" s="265"/>
+      <c r="E145" s="265"/>
+      <c r="F145" s="265"/>
+      <c r="G145" s="265"/>
+      <c r="H145" s="265"/>
+      <c r="I145" s="265"/>
+      <c r="J145" s="265"/>
+      <c r="K145" s="265"/>
+      <c r="L145" s="265"/>
+      <c r="M145" s="265"/>
+      <c r="N145" s="265"/>
     </row>
     <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="79"/>
@@ -12621,111 +12660,117 @@
       <c r="N147" s="79"/>
     </row>
     <row r="148" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C148" s="260" t="s">
+      <c r="C148" s="264" t="s">
         <v>264</v>
       </c>
-      <c r="D148" s="260"/>
-      <c r="E148" s="260"/>
-      <c r="F148" s="260"/>
-      <c r="G148" s="260"/>
-      <c r="H148" s="260"/>
-      <c r="I148" s="260"/>
-      <c r="J148" s="260"/>
-      <c r="K148" s="260"/>
-      <c r="L148" s="260"/>
-      <c r="M148" s="260"/>
-      <c r="N148" s="260"/>
+      <c r="D148" s="264"/>
+      <c r="E148" s="264"/>
+      <c r="F148" s="264"/>
+      <c r="G148" s="264"/>
+      <c r="H148" s="264"/>
+      <c r="I148" s="264"/>
+      <c r="J148" s="264"/>
+      <c r="K148" s="264"/>
+      <c r="L148" s="264"/>
+      <c r="M148" s="264"/>
+      <c r="N148" s="264"/>
     </row>
     <row r="149" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C149" s="260"/>
-      <c r="D149" s="260"/>
-      <c r="E149" s="260"/>
-      <c r="F149" s="260"/>
-      <c r="G149" s="260"/>
-      <c r="H149" s="260"/>
-      <c r="I149" s="260"/>
-      <c r="J149" s="260"/>
-      <c r="K149" s="260"/>
-      <c r="L149" s="260"/>
-      <c r="M149" s="260"/>
-      <c r="N149" s="260"/>
+      <c r="C149" s="264"/>
+      <c r="D149" s="264"/>
+      <c r="E149" s="264"/>
+      <c r="F149" s="264"/>
+      <c r="G149" s="264"/>
+      <c r="H149" s="264"/>
+      <c r="I149" s="264"/>
+      <c r="J149" s="264"/>
+      <c r="K149" s="264"/>
+      <c r="L149" s="264"/>
+      <c r="M149" s="264"/>
+      <c r="N149" s="264"/>
     </row>
     <row r="150" spans="3:16" x14ac:dyDescent="0.3">
-      <c r="C150" s="260"/>
-      <c r="D150" s="260"/>
-      <c r="E150" s="260"/>
-      <c r="F150" s="260"/>
-      <c r="G150" s="260"/>
-      <c r="H150" s="260"/>
-      <c r="I150" s="260"/>
-      <c r="J150" s="260"/>
-      <c r="K150" s="260"/>
-      <c r="L150" s="260"/>
-      <c r="M150" s="260"/>
-      <c r="N150" s="260"/>
+      <c r="C150" s="264"/>
+      <c r="D150" s="264"/>
+      <c r="E150" s="264"/>
+      <c r="F150" s="264"/>
+      <c r="G150" s="264"/>
+      <c r="H150" s="264"/>
+      <c r="I150" s="264"/>
+      <c r="J150" s="264"/>
+      <c r="K150" s="264"/>
+      <c r="L150" s="264"/>
+      <c r="M150" s="264"/>
+      <c r="N150" s="264"/>
       <c r="P150" s="86">
         <f>L1-K133</f>
-        <v>-1338773.6948400009</v>
+        <v>-612535.13484000042</v>
       </c>
     </row>
     <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="260"/>
-      <c r="D151" s="260"/>
-      <c r="E151" s="260"/>
-      <c r="F151" s="260"/>
-      <c r="G151" s="260"/>
-      <c r="H151" s="260"/>
-      <c r="I151" s="260"/>
-      <c r="J151" s="260"/>
-      <c r="K151" s="260"/>
-      <c r="L151" s="260"/>
-      <c r="M151" s="260"/>
-      <c r="N151" s="260"/>
+      <c r="C151" s="264"/>
+      <c r="D151" s="264"/>
+      <c r="E151" s="264"/>
+      <c r="F151" s="264"/>
+      <c r="G151" s="264"/>
+      <c r="H151" s="264"/>
+      <c r="I151" s="264"/>
+      <c r="J151" s="264"/>
+      <c r="K151" s="264"/>
+      <c r="L151" s="264"/>
+      <c r="M151" s="264"/>
+      <c r="N151" s="264"/>
     </row>
     <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C152" s="260"/>
-      <c r="D152" s="260"/>
-      <c r="E152" s="260"/>
-      <c r="F152" s="260"/>
-      <c r="G152" s="260"/>
-      <c r="H152" s="260"/>
-      <c r="I152" s="260"/>
-      <c r="J152" s="260"/>
-      <c r="K152" s="260"/>
-      <c r="L152" s="260"/>
-      <c r="M152" s="260"/>
-      <c r="N152" s="260"/>
+      <c r="C152" s="264"/>
+      <c r="D152" s="264"/>
+      <c r="E152" s="264"/>
+      <c r="F152" s="264"/>
+      <c r="G152" s="264"/>
+      <c r="H152" s="264"/>
+      <c r="I152" s="264"/>
+      <c r="J152" s="264"/>
+      <c r="K152" s="264"/>
+      <c r="L152" s="264"/>
+      <c r="M152" s="264"/>
+      <c r="N152" s="264"/>
     </row>
     <row r="153" spans="3:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C153" s="260"/>
-      <c r="D153" s="260"/>
-      <c r="E153" s="260"/>
-      <c r="F153" s="260"/>
-      <c r="G153" s="260"/>
-      <c r="H153" s="260"/>
-      <c r="I153" s="260"/>
-      <c r="J153" s="260"/>
-      <c r="K153" s="260"/>
-      <c r="L153" s="260"/>
-      <c r="M153" s="260"/>
-      <c r="N153" s="260"/>
+      <c r="C153" s="264"/>
+      <c r="D153" s="264"/>
+      <c r="E153" s="264"/>
+      <c r="F153" s="264"/>
+      <c r="G153" s="264"/>
+      <c r="H153" s="264"/>
+      <c r="I153" s="264"/>
+      <c r="J153" s="264"/>
+      <c r="K153" s="264"/>
+      <c r="L153" s="264"/>
+      <c r="M153" s="264"/>
+      <c r="N153" s="264"/>
     </row>
     <row r="154" spans="3:16" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C154" s="260"/>
-      <c r="D154" s="260"/>
-      <c r="E154" s="260"/>
-      <c r="F154" s="260"/>
-      <c r="G154" s="260"/>
-      <c r="H154" s="260"/>
-      <c r="I154" s="260"/>
-      <c r="J154" s="260"/>
-      <c r="K154" s="260"/>
-      <c r="L154" s="260"/>
-      <c r="M154" s="260"/>
-      <c r="N154" s="260"/>
+      <c r="C154" s="264"/>
+      <c r="D154" s="264"/>
+      <c r="E154" s="264"/>
+      <c r="F154" s="264"/>
+      <c r="G154" s="264"/>
+      <c r="H154" s="264"/>
+      <c r="I154" s="264"/>
+      <c r="J154" s="264"/>
+      <c r="K154" s="264"/>
+      <c r="L154" s="264"/>
+      <c r="M154" s="264"/>
+      <c r="N154" s="264"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="Q14:R15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:N154"/>
@@ -12741,12 +12786,6 @@
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="C5:N8"/>
     <mergeCell ref="C9:N10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12762,7 +12801,7 @@
   <sheetData>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="240" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C4" s="239"/>
       <c r="D4" s="239"/>
@@ -12786,24 +12825,24 @@
   <sheetData>
     <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C3" s="287" t="str">
+      <c r="C3" s="294" t="str">
         <f>RESUMEN!C5</f>
-        <v>PERÍODO: OCTUBRE</v>
-      </c>
-      <c r="D3" s="288"/>
-      <c r="E3" s="288"/>
-      <c r="F3" s="288" t="str">
+        <v>PERÍODO: NOVIEMBRE</v>
+      </c>
+      <c r="D3" s="295"/>
+      <c r="E3" s="295"/>
+      <c r="F3" s="295" t="str">
         <f>[1]RESUMEN!A22</f>
         <v xml:space="preserve">Sueldo encargada Sonia Arzamendia Galeano </v>
       </c>
-      <c r="G3" s="288"/>
-      <c r="H3" s="288"/>
-      <c r="I3" s="288"/>
-      <c r="J3" s="289"/>
+      <c r="G3" s="295"/>
+      <c r="H3" s="295"/>
+      <c r="I3" s="295"/>
+      <c r="J3" s="296"/>
     </row>
     <row r="4" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
-      <c r="J4" s="290"/>
+      <c r="J4" s="241"/>
     </row>
     <row r="5" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="str">
@@ -12814,11 +12853,11 @@
         <f>RESUMEN!D26</f>
         <v>1026046</v>
       </c>
-      <c r="H5" s="291" t="s">
-        <v>358</v>
-      </c>
-      <c r="I5" s="291"/>
-      <c r="J5" s="292"/>
+      <c r="H5" s="297" t="s">
+        <v>354</v>
+      </c>
+      <c r="I5" s="297"/>
+      <c r="J5" s="298"/>
     </row>
     <row r="6" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="str">
@@ -12829,11 +12868,11 @@
         <f>RESUMEN!D27</f>
         <v>35809.699999999997</v>
       </c>
-      <c r="H6" s="291" t="s">
-        <v>359</v>
-      </c>
-      <c r="I6" s="291"/>
-      <c r="J6" s="292"/>
+      <c r="H6" s="297" t="s">
+        <v>355</v>
+      </c>
+      <c r="I6" s="297"/>
+      <c r="J6" s="298"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="str">
@@ -12844,9 +12883,9 @@
         <f>RESUMEN!D28</f>
         <v>124792</v>
       </c>
-      <c r="H7" s="291"/>
-      <c r="I7" s="291"/>
-      <c r="J7" s="292"/>
+      <c r="H7" s="297"/>
+      <c r="I7" s="297"/>
+      <c r="J7" s="298"/>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="str">
@@ -12857,7 +12896,7 @@
         <f>RESUMEN!D29</f>
         <v>21286.799999999999</v>
       </c>
-      <c r="J8" s="290"/>
+      <c r="J8" s="241"/>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C9" s="1" t="str">
@@ -12868,11 +12907,11 @@
         <f>RESUMEN!D30</f>
         <v>59852.7</v>
       </c>
-      <c r="H9" s="291" t="s">
-        <v>360</v>
-      </c>
-      <c r="I9" s="291"/>
-      <c r="J9" s="292"/>
+      <c r="H9" s="297" t="s">
+        <v>356</v>
+      </c>
+      <c r="I9" s="297"/>
+      <c r="J9" s="298"/>
     </row>
     <row r="10" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="str">
@@ -12883,70 +12922,70 @@
         <f>RESUMEN!D31</f>
         <v>50000</v>
       </c>
-      <c r="H10" s="291" t="s">
-        <v>359</v>
-      </c>
-      <c r="I10" s="291"/>
-      <c r="J10" s="292"/>
+      <c r="H10" s="297" t="s">
+        <v>355</v>
+      </c>
+      <c r="I10" s="297"/>
+      <c r="J10" s="298"/>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
-      <c r="H11" s="291"/>
-      <c r="I11" s="291"/>
-      <c r="J11" s="292"/>
+      <c r="H11" s="297"/>
+      <c r="I11" s="297"/>
+      <c r="J11" s="298"/>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C12" s="293" t="s">
+      <c r="C12" s="244" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="294">
+      <c r="G12" s="245">
         <f>SUM(G5:G11)</f>
         <v>1317787.2</v>
       </c>
-      <c r="J12" s="290"/>
+      <c r="J12" s="241"/>
     </row>
     <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="295"/>
-      <c r="D13" s="296"/>
-      <c r="E13" s="296"/>
-      <c r="F13" s="296"/>
-      <c r="G13" s="296"/>
-      <c r="H13" s="296"/>
-      <c r="I13" s="296"/>
-      <c r="J13" s="297"/>
+      <c r="C13" s="246"/>
+      <c r="D13" s="247"/>
+      <c r="E13" s="247"/>
+      <c r="F13" s="247"/>
+      <c r="G13" s="247"/>
+      <c r="H13" s="247"/>
+      <c r="I13" s="247"/>
+      <c r="J13" s="248"/>
     </row>
     <row r="15" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="287" t="str">
+      <c r="C16" s="294" t="str">
         <f>C3</f>
-        <v>PERÍODO: OCTUBRE</v>
-      </c>
-      <c r="D16" s="288"/>
-      <c r="E16" s="288"/>
-      <c r="F16" s="288" t="str">
+        <v>PERÍODO: NOVIEMBRE</v>
+      </c>
+      <c r="D16" s="295"/>
+      <c r="E16" s="295"/>
+      <c r="F16" s="295" t="str">
         <f>[1]RESUMEN!A30</f>
         <v>Sueldo encargada Miriam</v>
       </c>
-      <c r="G16" s="288"/>
-      <c r="H16" s="288"/>
-      <c r="I16" s="288"/>
-      <c r="J16" s="289"/>
+      <c r="G16" s="295"/>
+      <c r="H16" s="295"/>
+      <c r="I16" s="295"/>
+      <c r="J16" s="296"/>
     </row>
     <row r="17" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C17" s="1"/>
-      <c r="J17" s="290"/>
+      <c r="J17" s="241"/>
     </row>
     <row r="18" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C18" s="1"/>
       <c r="G18" s="43"/>
-      <c r="H18" s="291" t="s">
-        <v>358</v>
-      </c>
-      <c r="I18" s="291"/>
-      <c r="J18" s="292"/>
+      <c r="H18" s="297" t="s">
+        <v>354</v>
+      </c>
+      <c r="I18" s="297"/>
+      <c r="J18" s="298"/>
     </row>
     <row r="19" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="str">
@@ -12957,11 +12996,11 @@
         <f>RESUMEN!D34</f>
         <v>513023</v>
       </c>
-      <c r="H19" s="291" t="s">
-        <v>359</v>
-      </c>
-      <c r="I19" s="291"/>
-      <c r="J19" s="292"/>
+      <c r="H19" s="297" t="s">
+        <v>355</v>
+      </c>
+      <c r="I19" s="297"/>
+      <c r="J19" s="298"/>
     </row>
     <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" s="1" t="str">
@@ -12972,9 +13011,9 @@
         <f>RESUMEN!D35</f>
         <v>0</v>
       </c>
-      <c r="H20" s="291"/>
-      <c r="I20" s="291"/>
-      <c r="J20" s="292"/>
+      <c r="H20" s="297"/>
+      <c r="I20" s="297"/>
+      <c r="J20" s="298"/>
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C21" s="1" t="str">
@@ -12985,7 +13024,7 @@
         <f>RESUMEN!D36</f>
         <v>35809.699999999997</v>
       </c>
-      <c r="J21" s="290"/>
+      <c r="J21" s="241"/>
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C22" s="1" t="str">
@@ -12996,11 +13035,11 @@
         <f>RESUMEN!D37</f>
         <v>124792</v>
       </c>
-      <c r="H22" s="291" t="s">
-        <v>360</v>
-      </c>
-      <c r="I22" s="291"/>
-      <c r="J22" s="292"/>
+      <c r="H22" s="297" t="s">
+        <v>356</v>
+      </c>
+      <c r="I22" s="297"/>
+      <c r="J22" s="298"/>
     </row>
     <row r="23" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C23" s="1" t="str">
@@ -13011,11 +13050,11 @@
         <f>RESUMEN!D38</f>
         <v>21286.799999999999</v>
       </c>
-      <c r="H23" s="291" t="s">
-        <v>359</v>
-      </c>
-      <c r="I23" s="291"/>
-      <c r="J23" s="292"/>
+      <c r="H23" s="297" t="s">
+        <v>355</v>
+      </c>
+      <c r="I23" s="297"/>
+      <c r="J23" s="298"/>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="str">
@@ -13026,9 +13065,9 @@
         <f>RESUMEN!D39</f>
         <v>59852.7</v>
       </c>
-      <c r="H24" s="291"/>
-      <c r="I24" s="291"/>
-      <c r="J24" s="292"/>
+      <c r="H24" s="297"/>
+      <c r="I24" s="297"/>
+      <c r="J24" s="298"/>
     </row>
     <row r="25" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C25" s="1" t="str">
@@ -13039,40 +13078,35 @@
         <f>RESUMEN!D40</f>
         <v>50000</v>
       </c>
-      <c r="H25" s="298"/>
-      <c r="I25" s="298"/>
-      <c r="J25" s="299"/>
+      <c r="H25" s="242"/>
+      <c r="I25" s="242"/>
+      <c r="J25" s="243"/>
     </row>
     <row r="26" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C26" s="293" t="s">
+      <c r="C26" s="244" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="294">
+      <c r="G26" s="245">
         <f>SUM(G18:G25)</f>
         <v>804764.2</v>
       </c>
-      <c r="J26" s="290"/>
+      <c r="J26" s="241"/>
     </row>
     <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C27" s="295"/>
-      <c r="D27" s="296"/>
-      <c r="E27" s="296"/>
-      <c r="F27" s="296"/>
-      <c r="G27" s="296"/>
-      <c r="H27" s="296"/>
-      <c r="I27" s="296"/>
-      <c r="J27" s="297"/>
+      <c r="C27" s="246"/>
+      <c r="D27" s="247"/>
+      <c r="E27" s="247"/>
+      <c r="F27" s="247"/>
+      <c r="G27" s="247"/>
+      <c r="H27" s="247"/>
+      <c r="I27" s="247"/>
+      <c r="J27" s="248"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J20"/>
-    <mergeCell ref="H22:J22"/>
     <mergeCell ref="H23:J24"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="F3:J3"/>
@@ -13080,6 +13114,11 @@
     <mergeCell ref="H6:J7"/>
     <mergeCell ref="H9:J9"/>
     <mergeCell ref="H10:J11"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J20"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -13095,10 +13134,10 @@
   </cols>
   <sheetData>
     <row r="4" spans="3:4" x14ac:dyDescent="0.3">
-      <c r="C4" s="286" t="s">
+      <c r="C4" s="299" t="s">
         <v>287</v>
       </c>
-      <c r="D4" s="286"/>
+      <c r="D4" s="299"/>
     </row>
     <row r="5" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C5" s="145">

--- a/EL MIRADOR/Noviembre/Noviembre - EL MIRADOR.xlsx
+++ b/EL MIRADOR/Noviembre/Noviembre - EL MIRADOR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\EL MIRADOR\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B55856D3-E75B-4021-B82B-74396168854C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE29061-D4CC-4DA1-9D9B-ECD59DF8C453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -172,9 +172,6 @@
     <t xml:space="preserve">Haberes </t>
   </si>
   <si>
-    <t xml:space="preserve">FONDO DE GASTOS ORDINARIOS </t>
-  </si>
-  <si>
     <t>2ºA</t>
   </si>
   <si>
@@ -1130,6 +1127,9 @@
   </si>
   <si>
     <t>Destapacion camara PB 26/11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FONDO DE GASTOS ORDINARIOS - PARA EDESUR </t>
   </si>
 </sst>
 </file>
@@ -2063,26 +2063,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2161,6 +2149,18 @@
     </xf>
     <xf numFmtId="1" fontId="21" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2658,7 +2658,7 @@
       <c r="A1" s="118"/>
       <c r="B1" s="127"/>
       <c r="C1" s="137" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D1" s="137"/>
       <c r="E1" s="138"/>
@@ -2672,7 +2672,7 @@
       <c r="A2" s="119"/>
       <c r="B2" s="128"/>
       <c r="C2" s="128" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D2" s="128"/>
       <c r="E2" s="129"/>
@@ -2686,11 +2686,11 @@
       <c r="A3" s="119"/>
       <c r="B3" s="128"/>
       <c r="C3" s="128" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D3" s="128"/>
       <c r="E3" s="128" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F3" s="129"/>
       <c r="G3" s="129"/>
@@ -2702,7 +2702,7 @@
       <c r="A4" s="119"/>
       <c r="B4" s="128"/>
       <c r="C4" s="128" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D4" s="129"/>
       <c r="E4" s="129"/>
@@ -2716,11 +2716,11 @@
       <c r="A5" s="123"/>
       <c r="B5" s="128"/>
       <c r="C5" s="128" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D5" s="128"/>
       <c r="E5" s="128" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F5" s="128"/>
       <c r="G5" s="128"/>
@@ -2760,7 +2760,7 @@
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="237" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B14" s="237"/>
       <c r="C14" s="237"/>
@@ -2826,7 +2826,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="246" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B20" s="246"/>
       <c r="C20" s="246"/>
@@ -2873,27 +2873,27 @@
       <c r="C24" s="14"/>
       <c r="D24" s="10"/>
       <c r="E24" s="102" t="s">
+        <v>171</v>
+      </c>
+      <c r="F24" s="102" t="s">
         <v>172</v>
       </c>
-      <c r="F24" s="102" t="s">
+      <c r="G24" s="102" t="s">
         <v>173</v>
       </c>
-      <c r="G24" s="102" t="s">
+      <c r="H24" s="102" t="s">
         <v>174</v>
       </c>
-      <c r="H24" s="102" t="s">
+      <c r="I24" s="102" t="s">
         <v>175</v>
       </c>
-      <c r="I24" s="102" t="s">
+      <c r="J24" s="103" t="s">
         <v>176</v>
-      </c>
-      <c r="J24" s="103" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="50" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -2939,7 +2939,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -2956,7 +2956,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -2972,7 +2972,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -2988,7 +2988,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -3004,7 +3004,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="99" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B32" s="96"/>
       <c r="C32" s="96"/>
@@ -3021,7 +3021,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="50" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -3067,7 +3067,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -3084,7 +3084,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -3101,7 +3101,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -3135,7 +3135,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -3151,7 +3151,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="99" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B41" s="96"/>
       <c r="C41" s="96"/>
@@ -3312,7 +3312,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="32" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="32" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B53" s="35"/>
       <c r="C53" s="35"/>
@@ -3427,11 +3427,11 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B54" s="35"/>
       <c r="C54" s="35" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D54" s="87">
         <v>278973.90000000002</v>
@@ -3446,11 +3446,11 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="35" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B55" s="35"/>
       <c r="C55" s="35" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D55" s="87">
         <v>14032.9</v>
@@ -3465,10 +3465,10 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="35" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B56" s="35" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C56" s="35"/>
       <c r="D56" s="87">
@@ -3484,10 +3484,10 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="35" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B57" s="35" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C57" s="35"/>
       <c r="D57" s="87">
@@ -3503,10 +3503,10 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B58" s="35" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C58" s="35"/>
       <c r="D58" s="87">
@@ -3522,10 +3522,10 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="35" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B59" s="35" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C59" s="35"/>
       <c r="D59" s="87">
@@ -3541,7 +3541,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="33" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B60" s="33"/>
       <c r="C60" s="33"/>
@@ -3599,11 +3599,11 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D62" s="44">
         <v>56231.41</v>
@@ -3618,11 +3618,11 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D63" s="44">
         <v>64940.71</v>
@@ -3637,7 +3637,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="33" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B64" s="33"/>
       <c r="C64" s="33"/>
@@ -3680,7 +3680,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="32" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -3695,7 +3695,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
@@ -3870,11 +3870,11 @@
     </row>
     <row r="71" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="71" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D71" s="234">
         <v>839647.54</v>
@@ -3916,11 +3916,11 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D72" s="235">
         <v>2334594.12</v>
@@ -3962,11 +3962,11 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D73" s="44">
         <v>118908</v>
@@ -3999,7 +3999,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="35"/>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="35" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B75" s="35"/>
       <c r="C75" s="35"/>
@@ -4063,7 +4063,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="35" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B76" s="35"/>
       <c r="C76" s="35"/>
@@ -4113,7 +4113,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="35" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B77" s="35"/>
       <c r="C77" s="35"/>
@@ -4163,11 +4163,11 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="154" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B78" s="152"/>
       <c r="C78" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D78" s="44">
         <v>100000</v>
@@ -4215,11 +4215,11 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="244" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B79" s="248"/>
       <c r="C79" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D79" s="44">
         <v>25000</v>
@@ -4246,11 +4246,11 @@
     </row>
     <row r="80" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="244" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B80" s="248"/>
       <c r="C80" s="152" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D80" s="44">
         <v>60000</v>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="32" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -4414,11 +4414,11 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B87" s="35"/>
       <c r="C87" s="35" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D87" s="44">
         <v>442900</v>
@@ -4452,11 +4452,11 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B88" s="35"/>
       <c r="C88" s="35" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D88" s="44">
         <v>90000</v>
@@ -4475,11 +4475,11 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B89" s="35"/>
       <c r="C89" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D89" s="44">
         <v>34596.519999999997</v>
@@ -4498,11 +4498,11 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B90" s="35"/>
       <c r="C90" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D90" s="44">
         <v>60000</v>
@@ -4521,11 +4521,11 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B91" s="35"/>
       <c r="C91" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D91" s="44">
         <v>60000</v>
@@ -4558,7 +4558,7 @@
     </row>
     <row r="93" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B93" s="33"/>
       <c r="C93" s="33"/>
@@ -4677,7 +4677,7 @@
         <v>13114.38</v>
       </c>
       <c r="L97" s="69" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
@@ -4822,7 +4822,7 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B103" s="33"/>
       <c r="C103" s="33"/>
@@ -4878,41 +4878,41 @@
     </row>
     <row r="105" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="106" t="s">
-        <v>46</v>
+        <v>362</v>
       </c>
       <c r="B105" s="107"/>
       <c r="C105" s="107"/>
       <c r="D105" s="108">
-        <f>12500000-10547732.29-60000*2</f>
-        <v>1832267.7100000009</v>
+        <f>12500000-10547732.29-60000*2+2000000</f>
+        <v>3832267.7100000009</v>
       </c>
       <c r="E105" s="131">
         <f>D105*93.2%</f>
-        <v>1707673.5057200009</v>
+        <v>3571673.5057200012</v>
       </c>
       <c r="F105" s="131">
         <f>$D105*1.08%</f>
-        <v>19788.491268000012</v>
+        <v>41388.491268000012</v>
       </c>
       <c r="G105" s="131">
         <f>$D105*1.28%</f>
-        <v>23453.026688000013</v>
+        <v>49053.026688000013</v>
       </c>
       <c r="H105" s="131">
         <f>$D105*1.21%</f>
-        <v>22170.43929100001</v>
+        <v>46370.43929100001</v>
       </c>
       <c r="I105" s="131">
         <f>$D105*1.49%</f>
-        <v>27300.788879000014</v>
+        <v>57100.788879000014</v>
       </c>
       <c r="J105" s="132">
         <f>D105*1.74%</f>
-        <v>31881.458154000014</v>
+        <v>66681.458154000007</v>
       </c>
       <c r="K105" s="43">
         <f>E105+J105+F105+G105+H105+I105</f>
-        <v>1832267.7100000011</v>
+        <v>3832267.7100000014</v>
       </c>
       <c r="L105" s="69" t="str">
         <f>IF(D105=K105, "", "Error")</f>
@@ -4941,35 +4941,35 @@
       <c r="C107" s="4"/>
       <c r="D107" s="91">
         <f>SUM(D105+D60+D52+D103+D100+D93+D83+D69+D47+D42+D64)</f>
-        <v>12499999.999999998</v>
+        <v>14499999.999999998</v>
       </c>
       <c r="E107" s="91">
-        <f t="shared" ref="D107:J107" si="22">SUM(E105+E60+E52+E103+E100+E93+E83+E69+E47+E42+E64)</f>
-        <v>11680498.307360003</v>
+        <f t="shared" ref="E107:J107" si="22">SUM(E105+E60+E52+E103+E100+E93+E83+E69+E47+E42+E64)</f>
+        <v>13544498.307360003</v>
       </c>
       <c r="F107" s="91">
         <f t="shared" si="22"/>
-        <v>130156.151184</v>
+        <v>151756.15118400005</v>
       </c>
       <c r="G107" s="91">
         <f t="shared" si="22"/>
-        <v>154259.14214400001</v>
+        <v>179859.14214400004</v>
       </c>
       <c r="H107" s="91">
         <f t="shared" si="22"/>
-        <v>145823.09530799999</v>
+        <v>170023.09530800002</v>
       </c>
       <c r="I107" s="91">
         <f t="shared" si="22"/>
-        <v>179567.28265200002</v>
+        <v>209367.28265200002</v>
       </c>
       <c r="J107" s="91">
         <f t="shared" si="22"/>
-        <v>209696.02135200001</v>
+        <v>244496.02135200001</v>
       </c>
       <c r="K107" s="61">
         <f>E107+J107+F107+G107+H107+I107</f>
-        <v>12500000.000000004</v>
+        <v>14500000.000000004</v>
       </c>
       <c r="L107" s="69" t="str">
         <f>IF(D107=K107, "", "Error")</f>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B110" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C110" s="136">
         <v>24000</v>
@@ -5018,10 +5018,10 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B111" t="s">
         <v>359</v>
-      </c>
-      <c r="B111" t="s">
-        <v>360</v>
       </c>
       <c r="C111" s="136">
         <v>12000</v>
@@ -5144,19 +5144,19 @@
         <v>11</v>
       </c>
       <c r="F123" s="82" t="s">
+        <v>172</v>
+      </c>
+      <c r="G123" s="82" t="s">
         <v>173</v>
       </c>
-      <c r="G123" s="82" t="s">
+      <c r="H123" s="82" t="s">
         <v>174</v>
       </c>
-      <c r="H123" s="82" t="s">
+      <c r="I123" s="82" t="s">
         <v>175</v>
       </c>
-      <c r="I123" s="82" t="s">
+      <c r="J123" s="83" t="s">
         <v>176</v>
-      </c>
-      <c r="J123" s="83" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="B129" s="39">
         <f>D107</f>
-        <v>12499999.999999998</v>
+        <v>14499999.999999998</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5242,7 +5242,7 @@
         <v>10667732.289999997</v>
       </c>
       <c r="D130" s="247" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E130" s="247"/>
       <c r="F130" s="247"/>
@@ -5340,7 +5340,7 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B137" s="30">
         <f>B146</f>
@@ -5373,7 +5373,7 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="21" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B139" s="85">
         <f>-23500-3840</f>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B144" s="8"/>
       <c r="C144" s="18"/>
@@ -5507,7 +5507,7 @@
     </row>
     <row r="151" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B151" s="31"/>
       <c r="C151" s="24"/>
@@ -5648,7 +5648,7 @@
       <c r="D1" s="176"/>
       <c r="E1" s="176"/>
       <c r="F1" s="176" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G1" s="176"/>
       <c r="H1" s="176"/>
@@ -5657,11 +5657,11 @@
       <c r="K1" s="176" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="258">
+      <c r="L1" s="254">
         <f>RESUMEN!D107-RESUMEN!D105</f>
         <v>10667732.289999997</v>
       </c>
-      <c r="M1" s="259"/>
+      <c r="M1" s="255"/>
       <c r="N1" s="177"/>
       <c r="O1" s="59"/>
     </row>
@@ -5672,7 +5672,7 @@
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="L2" s="7"/>
       <c r="M2" s="179">
-        <v>12500000</v>
+        <v>14500000</v>
       </c>
       <c r="N2" s="180"/>
       <c r="O2" s="59"/>
@@ -5698,7 +5698,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -5730,185 +5730,185 @@
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="267" t="s">
-        <v>356</v>
-      </c>
-      <c r="D5" s="268"/>
-      <c r="E5" s="268"/>
-      <c r="F5" s="268"/>
-      <c r="G5" s="268"/>
-      <c r="H5" s="268"/>
-      <c r="I5" s="268"/>
-      <c r="J5" s="268"/>
-      <c r="K5" s="268"/>
-      <c r="L5" s="268"/>
-      <c r="M5" s="268"/>
-      <c r="N5" s="269"/>
+      <c r="C5" s="263" t="s">
+        <v>355</v>
+      </c>
+      <c r="D5" s="264"/>
+      <c r="E5" s="264"/>
+      <c r="F5" s="264"/>
+      <c r="G5" s="264"/>
+      <c r="H5" s="264"/>
+      <c r="I5" s="264"/>
+      <c r="J5" s="264"/>
+      <c r="K5" s="264"/>
+      <c r="L5" s="264"/>
+      <c r="M5" s="264"/>
+      <c r="N5" s="265"/>
       <c r="O5" s="15"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="270"/>
-      <c r="D6" s="271"/>
-      <c r="E6" s="271"/>
-      <c r="F6" s="271"/>
-      <c r="G6" s="271"/>
-      <c r="H6" s="271"/>
-      <c r="I6" s="271"/>
-      <c r="J6" s="271"/>
-      <c r="K6" s="271"/>
-      <c r="L6" s="271"/>
-      <c r="M6" s="271"/>
-      <c r="N6" s="272"/>
+      <c r="C6" s="266"/>
+      <c r="D6" s="267"/>
+      <c r="E6" s="267"/>
+      <c r="F6" s="267"/>
+      <c r="G6" s="267"/>
+      <c r="H6" s="267"/>
+      <c r="I6" s="267"/>
+      <c r="J6" s="267"/>
+      <c r="K6" s="267"/>
+      <c r="L6" s="267"/>
+      <c r="M6" s="267"/>
+      <c r="N6" s="268"/>
       <c r="O6" s="15"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="270"/>
-      <c r="D7" s="271"/>
-      <c r="E7" s="271"/>
-      <c r="F7" s="271"/>
-      <c r="G7" s="271"/>
-      <c r="H7" s="271"/>
-      <c r="I7" s="271"/>
-      <c r="J7" s="271"/>
-      <c r="K7" s="271"/>
-      <c r="L7" s="271"/>
-      <c r="M7" s="271"/>
-      <c r="N7" s="272"/>
+      <c r="C7" s="266"/>
+      <c r="D7" s="267"/>
+      <c r="E7" s="267"/>
+      <c r="F7" s="267"/>
+      <c r="G7" s="267"/>
+      <c r="H7" s="267"/>
+      <c r="I7" s="267"/>
+      <c r="J7" s="267"/>
+      <c r="K7" s="267"/>
+      <c r="L7" s="267"/>
+      <c r="M7" s="267"/>
+      <c r="N7" s="268"/>
       <c r="O7" s="15"/>
     </row>
     <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="273"/>
-      <c r="D8" s="274"/>
-      <c r="E8" s="274"/>
-      <c r="F8" s="274"/>
-      <c r="G8" s="274"/>
-      <c r="H8" s="274"/>
-      <c r="I8" s="274"/>
-      <c r="J8" s="274"/>
-      <c r="K8" s="274"/>
-      <c r="L8" s="274"/>
-      <c r="M8" s="274"/>
-      <c r="N8" s="275"/>
+      <c r="C8" s="269"/>
+      <c r="D8" s="270"/>
+      <c r="E8" s="270"/>
+      <c r="F8" s="270"/>
+      <c r="G8" s="270"/>
+      <c r="H8" s="270"/>
+      <c r="I8" s="270"/>
+      <c r="J8" s="270"/>
+      <c r="K8" s="270"/>
+      <c r="L8" s="270"/>
+      <c r="M8" s="270"/>
+      <c r="N8" s="271"/>
       <c r="P8" s="86">
         <f>L1-K133</f>
-        <v>-1784929.4026400018</v>
+        <v>-3644929.4026400018</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="276" t="s">
-        <v>329</v>
-      </c>
-      <c r="D9" s="277"/>
-      <c r="E9" s="277"/>
-      <c r="F9" s="277"/>
-      <c r="G9" s="277"/>
-      <c r="H9" s="277"/>
-      <c r="I9" s="277"/>
-      <c r="J9" s="277"/>
-      <c r="K9" s="277"/>
-      <c r="L9" s="277"/>
-      <c r="M9" s="277"/>
-      <c r="N9" s="278"/>
+      <c r="C9" s="272" t="s">
+        <v>328</v>
+      </c>
+      <c r="D9" s="273"/>
+      <c r="E9" s="273"/>
+      <c r="F9" s="273"/>
+      <c r="G9" s="273"/>
+      <c r="H9" s="273"/>
+      <c r="I9" s="273"/>
+      <c r="J9" s="273"/>
+      <c r="K9" s="273"/>
+      <c r="L9" s="273"/>
+      <c r="M9" s="273"/>
+      <c r="N9" s="274"/>
       <c r="P9" s="86"/>
     </row>
     <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="279"/>
-      <c r="D10" s="280"/>
-      <c r="E10" s="280"/>
-      <c r="F10" s="280"/>
-      <c r="G10" s="280"/>
-      <c r="H10" s="280"/>
-      <c r="I10" s="280"/>
-      <c r="J10" s="280"/>
-      <c r="K10" s="280"/>
-      <c r="L10" s="280"/>
-      <c r="M10" s="280"/>
-      <c r="N10" s="281"/>
+      <c r="C10" s="275"/>
+      <c r="D10" s="276"/>
+      <c r="E10" s="276"/>
+      <c r="F10" s="276"/>
+      <c r="G10" s="276"/>
+      <c r="H10" s="276"/>
+      <c r="I10" s="276"/>
+      <c r="J10" s="276"/>
+      <c r="K10" s="276"/>
+      <c r="L10" s="276"/>
+      <c r="M10" s="276"/>
+      <c r="N10" s="277"/>
       <c r="P10" s="86"/>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="249" t="s">
+      <c r="A11" s="250" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="251" t="s">
+      <c r="B11" s="278" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="249" t="s">
+      <c r="C11" s="250" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="253" t="s">
+      <c r="D11" s="280" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="253" t="s">
-        <v>274</v>
-      </c>
-      <c r="F11" s="249" t="s">
+      <c r="E11" s="280" t="s">
+        <v>273</v>
+      </c>
+      <c r="F11" s="250" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="249" t="s">
+      <c r="G11" s="250" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="249" t="s">
+      <c r="H11" s="250" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="260" t="s">
+      <c r="I11" s="256" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="262" t="s">
+      <c r="J11" s="258" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="262" t="s">
+      <c r="K11" s="258" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="265" t="s">
+      <c r="L11" s="261" t="s">
         <v>42</v>
       </c>
-      <c r="M11" s="262" t="s">
-        <v>285</v>
-      </c>
-      <c r="N11" s="262" t="s">
+      <c r="M11" s="258" t="s">
         <v>284</v>
       </c>
+      <c r="N11" s="258" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="250"/>
-      <c r="B12" s="252"/>
-      <c r="C12" s="250"/>
-      <c r="D12" s="254"/>
-      <c r="E12" s="254"/>
-      <c r="F12" s="250"/>
-      <c r="G12" s="250"/>
-      <c r="H12" s="250"/>
-      <c r="I12" s="261"/>
-      <c r="J12" s="263"/>
-      <c r="K12" s="263"/>
-      <c r="L12" s="266"/>
-      <c r="M12" s="263"/>
-      <c r="N12" s="263"/>
+      <c r="A12" s="251"/>
+      <c r="B12" s="279"/>
+      <c r="C12" s="251"/>
+      <c r="D12" s="281"/>
+      <c r="E12" s="281"/>
+      <c r="F12" s="251"/>
+      <c r="G12" s="251"/>
+      <c r="H12" s="251"/>
+      <c r="I12" s="257"/>
+      <c r="J12" s="259"/>
+      <c r="K12" s="259"/>
+      <c r="L12" s="262"/>
+      <c r="M12" s="259"/>
+      <c r="N12" s="259"/>
     </row>
     <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="250"/>
-      <c r="B13" s="252"/>
-      <c r="C13" s="250"/>
-      <c r="D13" s="254"/>
-      <c r="E13" s="254"/>
-      <c r="F13" s="250"/>
-      <c r="G13" s="250"/>
-      <c r="H13" s="250"/>
-      <c r="I13" s="261"/>
-      <c r="J13" s="263"/>
-      <c r="K13" s="264"/>
-      <c r="L13" s="266"/>
+      <c r="A13" s="251"/>
+      <c r="B13" s="279"/>
+      <c r="C13" s="251"/>
+      <c r="D13" s="281"/>
+      <c r="E13" s="281"/>
+      <c r="F13" s="251"/>
+      <c r="G13" s="251"/>
+      <c r="H13" s="251"/>
+      <c r="I13" s="257"/>
+      <c r="J13" s="259"/>
+      <c r="K13" s="260"/>
+      <c r="L13" s="262"/>
       <c r="M13" s="140" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 15/12</v>
@@ -5920,17 +5920,17 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="35" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D14" s="114" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E14" s="114" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F14" s="155">
         <v>1.0800000000000001E-2</v>
@@ -5963,19 +5963,19 @@
         <v>139339.28025504001</v>
       </c>
       <c r="O14" s="121"/>
-      <c r="Q14" s="255" t="s">
-        <v>259</v>
-      </c>
-      <c r="R14" s="255"/>
+      <c r="Q14" s="249" t="s">
+        <v>258</v>
+      </c>
+      <c r="R14" s="249"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D15" s="114" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E15" s="114"/>
       <c r="F15" s="155">
@@ -6010,19 +6010,19 @@
         <v>150267.97667264001</v>
       </c>
       <c r="O15" s="121"/>
-      <c r="Q15" s="255"/>
-      <c r="R15" s="255"/>
+      <c r="Q15" s="249"/>
+      <c r="R15" s="249"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="35" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D16" s="114" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E16" s="114"/>
       <c r="F16" s="155">
@@ -6058,23 +6058,23 @@
       </c>
       <c r="O16" s="121"/>
       <c r="Q16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="R16">
         <f>RESUMEN!F107</f>
-        <v>130156.151184</v>
+        <v>151756.15118400005</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D17" s="114" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E17" s="114"/>
       <c r="F17" s="155">
@@ -6107,23 +6107,23 @@
       </c>
       <c r="O17" s="121"/>
       <c r="Q17" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="R17">
         <f>RESUMEN!G107</f>
-        <v>154259.14214400001</v>
+        <v>179859.14214400004</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="160" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D18" s="161" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E18" s="161"/>
       <c r="F18" s="162">
@@ -6159,23 +6159,23 @@
       </c>
       <c r="O18" s="121"/>
       <c r="Q18" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R18">
         <f>RESUMEN!H107</f>
-        <v>145823.09530799999</v>
+        <v>170023.09530800002</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="168" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D19" s="143" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E19" s="143"/>
       <c r="F19" s="146">
@@ -6198,40 +6198,40 @@
       </c>
       <c r="K19" s="171">
         <f>M$2*F19</f>
-        <v>235000</v>
+        <v>272600</v>
       </c>
       <c r="L19" s="189">
         <v>0</v>
       </c>
       <c r="M19" s="172">
         <f>ROUND((K19+J19+I19+L19),0) + O19</f>
-        <v>235000.01</v>
+        <v>272600.01</v>
       </c>
       <c r="N19" s="172">
         <f>ROUND((M19*6% + M19 ),0) + O19</f>
-        <v>249100.01</v>
+        <v>288956.01</v>
       </c>
       <c r="O19" s="141">
         <v>0.01</v>
       </c>
       <c r="Q19" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="R19">
         <f>RESUMEN!I107</f>
-        <v>179567.28265200002</v>
+        <v>209367.28265200002</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D20" s="114" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E20" s="143"/>
       <c r="F20" s="146">
@@ -6254,41 +6254,41 @@
       </c>
       <c r="K20" s="157">
         <f t="shared" ref="K20:K50" si="5">M$2*F20</f>
-        <v>105000</v>
+        <v>121799.99999999999</v>
       </c>
       <c r="L20" s="189">
         <v>0</v>
       </c>
       <c r="M20" s="159">
         <f>ROUND((K20+J20+I20+L20),0) + O20</f>
-        <v>105000.02</v>
+        <v>121800.02</v>
       </c>
       <c r="N20" s="159">
         <f t="shared" ref="N20:N83" si="6">ROUND((M20*6% + M20 ),0) + O20</f>
-        <v>111300.02</v>
+        <v>129108.02</v>
       </c>
       <c r="O20" s="141">
         <f>O19+0.01</f>
         <v>0.02</v>
       </c>
       <c r="Q20" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="R20">
         <f>RESUMEN!J107</f>
-        <v>209696.02135200001</v>
+        <v>244496.02135200001</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" s="114" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E21" s="143"/>
       <c r="F21" s="146">
@@ -6311,18 +6311,18 @@
       </c>
       <c r="K21" s="157">
         <f t="shared" si="5"/>
-        <v>251250</v>
+        <v>291450</v>
       </c>
       <c r="L21" s="189">
         <v>0</v>
       </c>
       <c r="M21" s="159">
         <f t="shared" ref="M21:M83" si="7">ROUND((K21+J21+I21+L21),0) + O21</f>
-        <v>251250.03</v>
+        <v>291450.03000000003</v>
       </c>
       <c r="N21" s="159">
         <f t="shared" si="6"/>
-        <v>266325.03000000003</v>
+        <v>308937.03000000003</v>
       </c>
       <c r="O21" s="141">
         <f t="shared" ref="O21:O84" si="8">O20+0.01</f>
@@ -6331,17 +6331,17 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="191" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D22" s="192" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E22" s="193" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F22" s="194">
         <v>9.4000000000000004E-3</v>
@@ -6362,40 +6362,40 @@
       </c>
       <c r="K22" s="197">
         <f t="shared" si="5"/>
-        <v>117500</v>
+        <v>136300</v>
       </c>
       <c r="L22" s="198">
         <v>0</v>
       </c>
       <c r="M22" s="199">
         <f t="shared" si="7"/>
-        <v>282672.03999999998</v>
+        <v>301472.03999999998</v>
       </c>
       <c r="N22" s="199">
         <f t="shared" si="6"/>
-        <v>299632.03999999998</v>
+        <v>319560.03999999998</v>
       </c>
       <c r="O22" s="141">
         <f t="shared" si="8"/>
         <v>0.04</v>
       </c>
       <c r="P22" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="35" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D23" s="114" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E23" s="143" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F23" s="146">
         <v>8.6999999999999994E-3</v>
@@ -6417,18 +6417,18 @@
       </c>
       <c r="K23" s="157">
         <f t="shared" si="5"/>
-        <v>108749.99999999999</v>
+        <v>126149.99999999999</v>
       </c>
       <c r="L23" s="189">
         <v>0</v>
       </c>
       <c r="M23" s="159">
         <f t="shared" si="7"/>
-        <v>195750.05</v>
+        <v>213150.05</v>
       </c>
       <c r="N23" s="159">
         <f t="shared" si="6"/>
-        <v>207495.05</v>
+        <v>225939.05</v>
       </c>
       <c r="O23" s="141">
         <f t="shared" si="8"/>
@@ -6437,17 +6437,17 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D24" s="114" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E24" s="143" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F24" s="146">
         <v>9.4999999999999998E-3</v>
@@ -6469,18 +6469,18 @@
       </c>
       <c r="K24" s="157">
         <f t="shared" si="5"/>
-        <v>118750</v>
+        <v>137750</v>
       </c>
       <c r="L24" s="189">
         <v>0</v>
       </c>
       <c r="M24" s="159">
         <f t="shared" si="7"/>
-        <v>118750.06</v>
+        <v>137750.06</v>
       </c>
       <c r="N24" s="159">
         <f t="shared" si="6"/>
-        <v>125875.06</v>
+        <v>146015.06</v>
       </c>
       <c r="O24" s="141">
         <f t="shared" si="8"/>
@@ -6489,17 +6489,17 @@
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="191" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D25" s="192" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E25" s="193" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F25" s="194">
         <v>1.6500000000000001E-2</v>
@@ -6520,18 +6520,18 @@
       </c>
       <c r="K25" s="197">
         <f t="shared" si="5"/>
-        <v>206250</v>
+        <v>239250</v>
       </c>
       <c r="L25" s="198">
         <v>0</v>
       </c>
       <c r="M25" s="199">
         <f t="shared" si="7"/>
-        <v>334227.07</v>
+        <v>367227.07</v>
       </c>
       <c r="N25" s="199">
         <f t="shared" si="6"/>
-        <v>354281.07</v>
+        <v>389261.07</v>
       </c>
       <c r="O25" s="141">
         <f t="shared" si="8"/>
@@ -6540,14 +6540,14 @@
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D26" s="114" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E26" s="143"/>
       <c r="F26" s="146">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="K26" s="157">
         <f t="shared" si="5"/>
-        <v>91250</v>
+        <v>105850</v>
       </c>
       <c r="L26" s="189">
         <f>24000+20000</f>
@@ -6578,11 +6578,11 @@
       </c>
       <c r="M26" s="159">
         <f t="shared" si="7"/>
-        <v>135250.07999999999</v>
+        <v>149850.07999999999</v>
       </c>
       <c r="N26" s="159">
         <f t="shared" si="6"/>
-        <v>143365.07999999999</v>
+        <v>158841.07999999999</v>
       </c>
       <c r="O26" s="141">
         <f t="shared" si="8"/>
@@ -6591,14 +6591,14 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="114" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B27" s="35"/>
       <c r="C27" s="35" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D27" s="114" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E27" s="143"/>
       <c r="F27" s="146">
@@ -6618,18 +6618,18 @@
       </c>
       <c r="K27" s="157">
         <f t="shared" si="5"/>
-        <v>222500</v>
+        <v>258100</v>
       </c>
       <c r="L27" s="189">
         <v>0</v>
       </c>
       <c r="M27" s="159">
         <f t="shared" si="7"/>
-        <v>950872.09</v>
+        <v>986472.09</v>
       </c>
       <c r="N27" s="159">
         <f t="shared" si="6"/>
-        <v>1007924.09</v>
+        <v>1045660.09</v>
       </c>
       <c r="O27" s="141">
         <f t="shared" si="8"/>
@@ -6638,14 +6638,14 @@
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B28" s="35"/>
       <c r="C28" s="35" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D28" s="114" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E28" s="143"/>
       <c r="F28" s="146">
@@ -6665,18 +6665,18 @@
       </c>
       <c r="K28" s="157">
         <f t="shared" si="5"/>
-        <v>117500</v>
+        <v>136300</v>
       </c>
       <c r="L28" s="189">
         <v>0</v>
       </c>
       <c r="M28" s="159">
         <f t="shared" si="7"/>
-        <v>230300.1</v>
+        <v>249100.1</v>
       </c>
       <c r="N28" s="159">
         <f t="shared" si="6"/>
-        <v>244118.1</v>
+        <v>264046.09999999998</v>
       </c>
       <c r="O28" s="141">
         <f t="shared" si="8"/>
@@ -6685,14 +6685,14 @@
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B29" s="35"/>
       <c r="C29" s="35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D29" s="114" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E29" s="143"/>
       <c r="F29" s="146">
@@ -6715,18 +6715,18 @@
       </c>
       <c r="K29" s="157">
         <f t="shared" si="5"/>
-        <v>108749.99999999999</v>
+        <v>126149.99999999999</v>
       </c>
       <c r="L29" s="189">
         <v>0</v>
       </c>
       <c r="M29" s="159">
         <f t="shared" si="7"/>
-        <v>108750.11</v>
+        <v>126150.11</v>
       </c>
       <c r="N29" s="159">
         <f t="shared" si="6"/>
-        <v>115275.11</v>
+        <v>133719.10999999999</v>
       </c>
       <c r="O29" s="141">
         <f t="shared" si="8"/>
@@ -6735,14 +6735,14 @@
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B30" s="35"/>
       <c r="C30" s="35" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D30" s="114" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E30" s="143"/>
       <c r="F30" s="146">
@@ -6762,18 +6762,18 @@
       </c>
       <c r="K30" s="157">
         <f t="shared" si="5"/>
-        <v>118750</v>
+        <v>137750</v>
       </c>
       <c r="L30" s="189">
         <v>0</v>
       </c>
       <c r="M30" s="159">
         <f t="shared" si="7"/>
-        <v>498750.12</v>
+        <v>517750.12</v>
       </c>
       <c r="N30" s="159">
         <f t="shared" si="6"/>
-        <v>528675.12</v>
+        <v>548815.12</v>
       </c>
       <c r="O30" s="141">
         <f t="shared" si="8"/>
@@ -6782,14 +6782,14 @@
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="114" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B31" s="35"/>
       <c r="C31" s="35" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D31" s="114" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E31" s="143"/>
       <c r="F31" s="146">
@@ -6812,18 +6812,18 @@
       </c>
       <c r="K31" s="157">
         <f t="shared" si="5"/>
-        <v>205000.00000000003</v>
+        <v>237800.00000000003</v>
       </c>
       <c r="L31" s="189">
         <v>0</v>
       </c>
       <c r="M31" s="159">
         <f t="shared" si="7"/>
-        <v>205000.13</v>
+        <v>237800.13</v>
       </c>
       <c r="N31" s="159">
         <f t="shared" si="6"/>
-        <v>217300.13</v>
+        <v>252068.13</v>
       </c>
       <c r="O31" s="141">
         <f t="shared" si="8"/>
@@ -6832,17 +6832,17 @@
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D32" s="114" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E32" s="143" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F32" s="146">
         <v>7.1999999999999998E-3</v>
@@ -6864,18 +6864,18 @@
       </c>
       <c r="K32" s="157">
         <f t="shared" si="5"/>
-        <v>90000</v>
+        <v>104400</v>
       </c>
       <c r="L32" s="189">
         <v>0</v>
       </c>
       <c r="M32" s="159">
         <f t="shared" si="7"/>
-        <v>90000.14</v>
+        <v>104400.14</v>
       </c>
       <c r="N32" s="159">
         <f t="shared" si="6"/>
-        <v>95400.14</v>
+        <v>110664.14</v>
       </c>
       <c r="O32" s="141">
         <f t="shared" si="8"/>
@@ -6884,14 +6884,14 @@
     </row>
     <row r="33" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A33" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D33" s="114" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E33" s="143"/>
       <c r="F33" s="146">
@@ -6914,18 +6914,18 @@
       </c>
       <c r="K33" s="157">
         <f t="shared" si="5"/>
-        <v>216250</v>
+        <v>250850</v>
       </c>
       <c r="L33" s="189">
         <v>0</v>
       </c>
       <c r="M33" s="159">
         <f t="shared" si="7"/>
-        <v>216250.15</v>
+        <v>250850.15</v>
       </c>
       <c r="N33" s="159">
         <f t="shared" si="6"/>
-        <v>229225.15</v>
+        <v>265901.15000000002</v>
       </c>
       <c r="O33" s="141">
         <f t="shared" si="8"/>
@@ -6934,14 +6934,14 @@
     </row>
     <row r="34" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A34" s="149" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B34" s="148"/>
       <c r="C34" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D34" s="114" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E34" s="143"/>
       <c r="F34" s="146">
@@ -6963,18 +6963,18 @@
       </c>
       <c r="K34" s="157">
         <f t="shared" si="5"/>
-        <v>117500</v>
+        <v>136300</v>
       </c>
       <c r="L34" s="189">
         <v>0</v>
       </c>
       <c r="M34" s="159">
         <f t="shared" si="7"/>
-        <v>110012.16</v>
+        <v>128812.16</v>
       </c>
       <c r="N34" s="159">
         <f t="shared" si="6"/>
-        <v>116613.16</v>
+        <v>136541.16</v>
       </c>
       <c r="O34" s="141">
         <f t="shared" si="8"/>
@@ -6983,17 +6983,17 @@
     </row>
     <row r="35" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A35" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D35" s="114" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E35" s="143" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F35" s="146">
         <v>8.6999999999999994E-3</v>
@@ -7014,18 +7014,18 @@
       </c>
       <c r="K35" s="157">
         <f t="shared" si="5"/>
-        <v>108749.99999999999</v>
+        <v>126149.99999999999</v>
       </c>
       <c r="L35" s="189">
         <v>0</v>
       </c>
       <c r="M35" s="159">
         <f t="shared" si="7"/>
-        <v>117450.17</v>
+        <v>134850.17000000001</v>
       </c>
       <c r="N35" s="159">
         <f t="shared" si="6"/>
-        <v>124497.17</v>
+        <v>142941.17000000001</v>
       </c>
       <c r="O35" s="141">
         <f t="shared" si="8"/>
@@ -7034,14 +7034,14 @@
     </row>
     <row r="36" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A36" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D36" s="114" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E36" s="143"/>
       <c r="F36" s="146">
@@ -7061,18 +7061,18 @@
       </c>
       <c r="K36" s="157">
         <f t="shared" si="5"/>
-        <v>118750</v>
+        <v>137750</v>
       </c>
       <c r="L36" s="189">
         <v>0</v>
       </c>
       <c r="M36" s="159">
         <f t="shared" si="7"/>
-        <v>327750.18</v>
+        <v>346750.18</v>
       </c>
       <c r="N36" s="159">
         <f t="shared" si="6"/>
-        <v>347415.18</v>
+        <v>367555.18</v>
       </c>
       <c r="O36" s="141">
         <f t="shared" si="8"/>
@@ -7081,17 +7081,17 @@
     </row>
     <row r="37" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A37" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D37" s="114" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E37" s="143" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F37" s="146">
         <v>1.6400000000000001E-2</v>
@@ -7113,18 +7113,18 @@
       </c>
       <c r="K37" s="157">
         <f t="shared" si="5"/>
-        <v>205000.00000000003</v>
+        <v>237800.00000000003</v>
       </c>
       <c r="L37" s="189">
         <v>20000</v>
       </c>
       <c r="M37" s="159">
         <f t="shared" si="7"/>
-        <v>225000.19</v>
+        <v>257800.19</v>
       </c>
       <c r="N37" s="159">
         <f t="shared" si="6"/>
-        <v>238500.19</v>
+        <v>273268.19</v>
       </c>
       <c r="O37" s="141">
         <f t="shared" si="8"/>
@@ -7133,14 +7133,14 @@
     </row>
     <row r="38" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A38" s="57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D38" s="114" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E38" s="143"/>
       <c r="F38" s="146">
@@ -7163,18 +7163,18 @@
       </c>
       <c r="K38" s="157">
         <f t="shared" si="5"/>
-        <v>90000</v>
+        <v>104400</v>
       </c>
       <c r="L38" s="189">
         <v>0</v>
       </c>
       <c r="M38" s="159">
         <f t="shared" si="7"/>
-        <v>90000.2</v>
+        <v>104400.2</v>
       </c>
       <c r="N38" s="159">
         <f t="shared" si="6"/>
-        <v>95400.2</v>
+        <v>110664.2</v>
       </c>
       <c r="O38" s="141">
         <f t="shared" si="8"/>
@@ -7183,14 +7183,14 @@
     </row>
     <row r="39" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="114" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B39" s="35"/>
       <c r="C39" s="35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D39" s="114" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E39" s="143"/>
       <c r="F39" s="146">
@@ -7213,18 +7213,18 @@
       </c>
       <c r="K39" s="157">
         <f t="shared" si="5"/>
-        <v>216250</v>
+        <v>250850</v>
       </c>
       <c r="L39" s="189">
         <v>0</v>
       </c>
       <c r="M39" s="159">
         <f t="shared" si="7"/>
-        <v>216250.21</v>
+        <v>250850.21</v>
       </c>
       <c r="N39" s="159">
         <f t="shared" si="6"/>
-        <v>229225.21</v>
+        <v>265901.21000000002</v>
       </c>
       <c r="O39" s="211">
         <f t="shared" si="8"/>
@@ -7331,14 +7331,14 @@
     </row>
     <row r="40" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B40" s="35"/>
       <c r="C40" s="35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D40" s="114" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E40" s="143"/>
       <c r="F40" s="146">
@@ -7358,18 +7358,18 @@
       </c>
       <c r="K40" s="157">
         <f t="shared" si="5"/>
-        <v>117500</v>
+        <v>136300</v>
       </c>
       <c r="L40" s="189">
         <v>0</v>
       </c>
       <c r="M40" s="159">
         <f t="shared" si="7"/>
-        <v>324300.21999999997</v>
+        <v>343100.22</v>
       </c>
       <c r="N40" s="159">
         <f t="shared" si="6"/>
-        <v>343758.22</v>
+        <v>363686.22</v>
       </c>
       <c r="O40" s="211">
         <f t="shared" si="8"/>
@@ -7476,14 +7476,14 @@
     </row>
     <row r="41" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B41" s="35"/>
       <c r="C41" s="35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D41" s="114" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E41" s="143"/>
       <c r="F41" s="146">
@@ -7506,25 +7506,25 @@
       </c>
       <c r="K41" s="157">
         <f t="shared" si="5"/>
-        <v>108749.99999999999</v>
+        <v>126149.99999999999</v>
       </c>
       <c r="L41" s="189">
         <v>0</v>
       </c>
       <c r="M41" s="159">
         <f t="shared" si="7"/>
-        <v>108750.23</v>
+        <v>126150.23</v>
       </c>
       <c r="N41" s="159">
         <f t="shared" si="6"/>
-        <v>115275.23</v>
+        <v>133719.23000000001</v>
       </c>
       <c r="O41" s="211">
         <f t="shared" si="8"/>
         <v>0.23000000000000007</v>
       </c>
       <c r="P41" s="74" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="Q41" s="74"/>
       <c r="R41" s="74"/>
@@ -7626,14 +7626,14 @@
     </row>
     <row r="42" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B42" s="35"/>
       <c r="C42" s="35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D42" s="114" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E42" s="143"/>
       <c r="F42" s="146">
@@ -7653,18 +7653,18 @@
       </c>
       <c r="K42" s="157">
         <f t="shared" si="5"/>
-        <v>118750</v>
+        <v>137750</v>
       </c>
       <c r="L42" s="189">
         <v>0</v>
       </c>
       <c r="M42" s="159">
         <f t="shared" si="7"/>
-        <v>327750.24</v>
+        <v>346750.24</v>
       </c>
       <c r="N42" s="159">
         <f t="shared" si="6"/>
-        <v>347415.24</v>
+        <v>367555.24</v>
       </c>
       <c r="O42" s="211">
         <f t="shared" si="8"/>
@@ -7771,14 +7771,14 @@
     </row>
     <row r="43" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A43" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D43" s="114" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E43" s="143"/>
       <c r="F43" s="146">
@@ -7801,18 +7801,18 @@
       </c>
       <c r="K43" s="157">
         <f t="shared" si="5"/>
-        <v>205000.00000000003</v>
+        <v>237800.00000000003</v>
       </c>
       <c r="L43" s="189">
         <v>0</v>
       </c>
       <c r="M43" s="159">
         <f t="shared" si="7"/>
-        <v>205000.25</v>
+        <v>237800.25</v>
       </c>
       <c r="N43" s="159">
         <f t="shared" si="6"/>
-        <v>217300.25</v>
+        <v>252068.25</v>
       </c>
       <c r="O43" s="141">
         <f t="shared" si="8"/>
@@ -7821,17 +7821,17 @@
     </row>
     <row r="44" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A44" s="57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D44" s="114" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E44" s="143" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F44" s="146">
         <v>7.1999999999999998E-3</v>
@@ -7853,18 +7853,18 @@
       </c>
       <c r="K44" s="157">
         <f t="shared" si="5"/>
-        <v>90000</v>
+        <v>104400</v>
       </c>
       <c r="L44" s="189">
         <v>0</v>
       </c>
       <c r="M44" s="159">
         <f t="shared" si="7"/>
-        <v>90000.26</v>
+        <v>104400.26</v>
       </c>
       <c r="N44" s="159">
         <f t="shared" si="6"/>
-        <v>95400.26</v>
+        <v>110664.26</v>
       </c>
       <c r="O44" s="141">
         <f t="shared" si="8"/>
@@ -7873,14 +7873,14 @@
     </row>
     <row r="45" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A45" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D45" s="114" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E45" s="143"/>
       <c r="F45" s="146">
@@ -7903,40 +7903,40 @@
       </c>
       <c r="K45" s="157">
         <f t="shared" si="5"/>
-        <v>216250</v>
+        <v>250850</v>
       </c>
       <c r="L45" s="189">
         <v>0</v>
       </c>
       <c r="M45" s="159">
         <f t="shared" si="7"/>
-        <v>216250.27</v>
+        <v>250850.27</v>
       </c>
       <c r="N45" s="159">
         <f t="shared" si="6"/>
-        <v>229225.27</v>
+        <v>265901.27</v>
       </c>
       <c r="O45" s="141">
         <f t="shared" si="8"/>
         <v>0.27000000000000007</v>
       </c>
       <c r="P45" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q45" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A46" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D46" s="114" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E46" s="143"/>
       <c r="F46" s="146">
@@ -7959,40 +7959,40 @@
       </c>
       <c r="K46" s="157">
         <f t="shared" si="5"/>
-        <v>117500</v>
+        <v>136300</v>
       </c>
       <c r="L46" s="189">
         <v>0</v>
       </c>
       <c r="M46" s="159">
         <f t="shared" si="7"/>
-        <v>117500.28</v>
+        <v>136300.28</v>
       </c>
       <c r="N46" s="159">
         <f t="shared" si="6"/>
-        <v>124550.28</v>
+        <v>144478.28</v>
       </c>
       <c r="O46" s="141">
         <f t="shared" si="8"/>
         <v>0.28000000000000008</v>
       </c>
       <c r="Q46" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A47" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D47" s="114" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E47" s="143" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F47" s="146">
         <v>8.6999999999999994E-3</v>
@@ -8011,18 +8011,18 @@
       </c>
       <c r="K47" s="157">
         <f t="shared" si="5"/>
-        <v>108749.99999999999</v>
+        <v>126149.99999999999</v>
       </c>
       <c r="L47" s="189">
         <v>0</v>
       </c>
       <c r="M47" s="159">
         <f t="shared" si="7"/>
-        <v>213150.29</v>
+        <v>230550.29</v>
       </c>
       <c r="N47" s="159">
         <f t="shared" si="6"/>
-        <v>225939.29</v>
+        <v>244383.29</v>
       </c>
       <c r="O47" s="141">
         <f t="shared" si="8"/>
@@ -8031,14 +8031,14 @@
     </row>
     <row r="48" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A48" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="35" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D48" s="114" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E48" s="143"/>
       <c r="F48" s="146">
@@ -8061,18 +8061,18 @@
       </c>
       <c r="K48" s="157">
         <f t="shared" si="5"/>
-        <v>118750</v>
+        <v>137750</v>
       </c>
       <c r="L48" s="189">
         <v>0</v>
       </c>
       <c r="M48" s="159">
         <f t="shared" si="7"/>
-        <v>118750.3</v>
+        <v>137750.29999999999</v>
       </c>
       <c r="N48" s="159">
         <f t="shared" si="6"/>
-        <v>125875.3</v>
+        <v>146015.29999999999</v>
       </c>
       <c r="O48" s="141">
         <f t="shared" si="8"/>
@@ -8081,14 +8081,14 @@
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="35" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D49" s="114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E49" s="143"/>
       <c r="F49" s="146">
@@ -8111,18 +8111,18 @@
       </c>
       <c r="K49" s="157">
         <f t="shared" si="5"/>
-        <v>205000.00000000003</v>
+        <v>237800.00000000003</v>
       </c>
       <c r="L49" s="189">
         <v>0</v>
       </c>
       <c r="M49" s="159">
         <f t="shared" si="7"/>
-        <v>205000.31</v>
+        <v>237800.31</v>
       </c>
       <c r="N49" s="159">
         <f t="shared" si="6"/>
-        <v>217300.31</v>
+        <v>252068.31</v>
       </c>
       <c r="O49" s="141">
         <f t="shared" si="8"/>
@@ -8131,14 +8131,14 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D50" s="114" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E50" s="143"/>
       <c r="F50" s="146">
@@ -8158,18 +8158,18 @@
       </c>
       <c r="K50" s="157">
         <f t="shared" si="5"/>
-        <v>90000</v>
+        <v>104400</v>
       </c>
       <c r="L50" s="189">
         <v>20000</v>
       </c>
       <c r="M50" s="159">
         <f t="shared" si="7"/>
-        <v>196400.32</v>
+        <v>210800.32</v>
       </c>
       <c r="N50" s="159">
         <f t="shared" si="6"/>
-        <v>208184.32000000001</v>
+        <v>223448.32000000001</v>
       </c>
       <c r="O50" s="141">
         <f t="shared" si="8"/>
@@ -8179,14 +8179,14 @@
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="35" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D51" s="114" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E51" s="143"/>
       <c r="F51" s="146">
@@ -8209,18 +8209,18 @@
       </c>
       <c r="K51" s="157">
         <f t="shared" ref="K51:K82" si="12">M$2*F51</f>
-        <v>216250</v>
+        <v>250850</v>
       </c>
       <c r="L51" s="189">
         <v>0</v>
       </c>
       <c r="M51" s="159">
         <f t="shared" si="7"/>
-        <v>216250.33</v>
+        <v>250850.33</v>
       </c>
       <c r="N51" s="159">
         <f t="shared" si="6"/>
-        <v>229225.33</v>
+        <v>265901.33</v>
       </c>
       <c r="O51" s="141">
         <f t="shared" si="8"/>
@@ -8230,14 +8230,14 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D52" s="114" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E52" s="143"/>
       <c r="F52" s="146">
@@ -8260,37 +8260,37 @@
       </c>
       <c r="K52" s="157">
         <f t="shared" si="12"/>
-        <v>117500</v>
+        <v>136300</v>
       </c>
       <c r="L52" s="189">
         <v>20000</v>
       </c>
       <c r="M52" s="159">
         <f t="shared" si="7"/>
-        <v>137500.34</v>
+        <v>156300.34</v>
       </c>
       <c r="N52" s="159">
         <f t="shared" si="6"/>
-        <v>145750.34</v>
+        <v>165678.34</v>
       </c>
       <c r="O52" s="141">
         <f t="shared" si="8"/>
         <v>0.34000000000000014</v>
       </c>
       <c r="P52" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B53" s="6"/>
       <c r="C53" s="35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D53" s="114" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E53" s="143"/>
       <c r="F53" s="146">
@@ -8313,18 +8313,18 @@
       </c>
       <c r="K53" s="157">
         <f t="shared" si="12"/>
-        <v>108749.99999999999</v>
+        <v>126149.99999999999</v>
       </c>
       <c r="L53" s="189">
         <v>0</v>
       </c>
       <c r="M53" s="159">
         <f t="shared" si="7"/>
-        <v>108750.35</v>
+        <v>126150.35</v>
       </c>
       <c r="N53" s="159">
         <f t="shared" si="6"/>
-        <v>115275.35</v>
+        <v>133719.35</v>
       </c>
       <c r="O53" s="141">
         <f t="shared" si="8"/>
@@ -8333,14 +8333,14 @@
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B54" s="6"/>
       <c r="C54" s="35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D54" s="114" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E54" s="143"/>
       <c r="F54" s="146">
@@ -8360,18 +8360,18 @@
       </c>
       <c r="K54" s="157">
         <f t="shared" si="12"/>
-        <v>118750</v>
+        <v>137750</v>
       </c>
       <c r="L54" s="189">
         <v>0</v>
       </c>
       <c r="M54" s="159">
         <f t="shared" si="7"/>
-        <v>268750.36</v>
+        <v>287750.36</v>
       </c>
       <c r="N54" s="159">
         <f t="shared" si="6"/>
-        <v>284875.36</v>
+        <v>305015.36</v>
       </c>
       <c r="O54" s="141">
         <f t="shared" si="8"/>
@@ -8380,14 +8380,14 @@
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B55" s="6"/>
       <c r="C55" s="35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D55" s="114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E55" s="143"/>
       <c r="F55" s="146">
@@ -8410,18 +8410,18 @@
       </c>
       <c r="K55" s="157">
         <f t="shared" si="12"/>
-        <v>205000.00000000003</v>
+        <v>237800.00000000003</v>
       </c>
       <c r="L55" s="189">
         <v>0</v>
       </c>
       <c r="M55" s="159">
         <f t="shared" si="7"/>
-        <v>205000.37</v>
+        <v>237800.37</v>
       </c>
       <c r="N55" s="159">
         <f t="shared" si="6"/>
-        <v>217300.37</v>
+        <v>252068.37</v>
       </c>
       <c r="O55" s="141">
         <f t="shared" si="8"/>
@@ -8431,17 +8431,17 @@
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B56" s="6"/>
       <c r="C56" s="35" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D56" s="114" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E56" s="143" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F56" s="146">
         <v>7.1999999999999998E-3</v>
@@ -8463,18 +8463,18 @@
       </c>
       <c r="K56" s="157">
         <f t="shared" si="12"/>
-        <v>90000</v>
+        <v>104400</v>
       </c>
       <c r="L56" s="189">
         <v>0</v>
       </c>
       <c r="M56" s="159">
         <f t="shared" si="7"/>
-        <v>90000.38</v>
+        <v>104400.38</v>
       </c>
       <c r="N56" s="159">
         <f t="shared" si="6"/>
-        <v>95400.38</v>
+        <v>110664.38</v>
       </c>
       <c r="O56" s="141">
         <f t="shared" si="8"/>
@@ -8483,14 +8483,14 @@
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B57" s="6"/>
       <c r="C57" s="35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D57" s="114" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E57" s="143"/>
       <c r="F57" s="146">
@@ -8513,18 +8513,18 @@
       </c>
       <c r="K57" s="157">
         <f t="shared" si="12"/>
-        <v>216250</v>
+        <v>250850</v>
       </c>
       <c r="L57" s="189">
         <v>0</v>
       </c>
       <c r="M57" s="159">
         <f t="shared" si="7"/>
-        <v>216250.39</v>
+        <v>250850.39</v>
       </c>
       <c r="N57" s="159">
         <f t="shared" si="6"/>
-        <v>229225.39</v>
+        <v>265901.39</v>
       </c>
       <c r="O57" s="141">
         <f t="shared" si="8"/>
@@ -8533,14 +8533,14 @@
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B58" s="6"/>
       <c r="C58" s="35" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D58" s="114" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E58" s="143"/>
       <c r="F58" s="146">
@@ -8563,18 +8563,18 @@
       </c>
       <c r="K58" s="157">
         <f t="shared" si="12"/>
-        <v>117500</v>
+        <v>136300</v>
       </c>
       <c r="L58" s="189">
         <v>0</v>
       </c>
       <c r="M58" s="159">
         <f t="shared" si="7"/>
-        <v>117500.4</v>
+        <v>136300.4</v>
       </c>
       <c r="N58" s="159">
         <f t="shared" si="6"/>
-        <v>124550.39999999999</v>
+        <v>144478.39999999999</v>
       </c>
       <c r="O58" s="141">
         <f t="shared" si="8"/>
@@ -8583,14 +8583,14 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B59" s="35"/>
       <c r="C59" s="201" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D59" s="202" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E59" s="203"/>
       <c r="F59" s="204">
@@ -8613,37 +8613,37 @@
       </c>
       <c r="K59" s="207">
         <f t="shared" si="12"/>
-        <v>108749.99999999999</v>
+        <v>126149.99999999999</v>
       </c>
       <c r="L59" s="208">
         <v>0</v>
       </c>
       <c r="M59" s="209">
         <f t="shared" si="7"/>
-        <v>108750.41</v>
+        <v>126150.41</v>
       </c>
       <c r="N59" s="209">
         <f t="shared" si="6"/>
-        <v>115275.41</v>
+        <v>133719.41</v>
       </c>
       <c r="O59" s="141">
         <f t="shared" si="8"/>
         <v>0.4100000000000002</v>
       </c>
       <c r="Q59" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B60" s="35"/>
       <c r="C60" s="35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D60" s="114" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E60" s="143"/>
       <c r="F60" s="146">
@@ -8666,37 +8666,37 @@
       </c>
       <c r="K60" s="157">
         <f t="shared" si="12"/>
-        <v>118750</v>
+        <v>137750</v>
       </c>
       <c r="L60" s="189">
         <v>20000</v>
       </c>
       <c r="M60" s="159">
         <f t="shared" si="7"/>
-        <v>138750.42000000001</v>
+        <v>157750.42000000001</v>
       </c>
       <c r="N60" s="159">
         <f t="shared" si="6"/>
-        <v>147075.42000000001</v>
+        <v>167215.42000000001</v>
       </c>
       <c r="O60" s="141">
         <f t="shared" si="8"/>
         <v>0.42000000000000021</v>
       </c>
       <c r="P60" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="114" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B61" s="35"/>
       <c r="C61" s="35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D61" s="114" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E61" s="143"/>
       <c r="F61" s="146">
@@ -8719,18 +8719,18 @@
       </c>
       <c r="K61" s="157">
         <f t="shared" si="12"/>
-        <v>205000.00000000003</v>
+        <v>237800.00000000003</v>
       </c>
       <c r="L61" s="189">
         <v>0</v>
       </c>
       <c r="M61" s="159">
         <f t="shared" si="7"/>
-        <v>205000.43</v>
+        <v>237800.43</v>
       </c>
       <c r="N61" s="159">
         <f t="shared" si="6"/>
-        <v>217300.43</v>
+        <v>252068.43</v>
       </c>
       <c r="O61" s="141">
         <f t="shared" si="8"/>
@@ -8739,14 +8739,14 @@
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="114" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B62" s="35"/>
       <c r="C62" s="35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D62" s="114" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E62" s="143"/>
       <c r="F62" s="146">
@@ -8769,18 +8769,18 @@
       </c>
       <c r="K62" s="157">
         <f t="shared" si="12"/>
-        <v>90000</v>
+        <v>104400</v>
       </c>
       <c r="L62" s="189">
         <v>0</v>
       </c>
       <c r="M62" s="159">
         <f t="shared" si="7"/>
-        <v>90000.44</v>
+        <v>104400.44</v>
       </c>
       <c r="N62" s="159">
         <f t="shared" si="6"/>
-        <v>95400.44</v>
+        <v>110664.44</v>
       </c>
       <c r="O62" s="141">
         <f t="shared" si="8"/>
@@ -8789,14 +8789,14 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D63" s="114" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E63" s="143"/>
       <c r="F63" s="146">
@@ -8819,18 +8819,18 @@
       </c>
       <c r="K63" s="157">
         <f t="shared" si="12"/>
-        <v>216250</v>
+        <v>250850</v>
       </c>
       <c r="L63" s="189">
         <v>0</v>
       </c>
       <c r="M63" s="159">
         <f t="shared" si="7"/>
-        <v>216250.45</v>
+        <v>250850.45</v>
       </c>
       <c r="N63" s="159">
         <f t="shared" si="6"/>
-        <v>229225.45</v>
+        <v>265901.45</v>
       </c>
       <c r="O63" s="141">
         <f t="shared" si="8"/>
@@ -8839,17 +8839,17 @@
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B64" s="6"/>
       <c r="C64" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D64" s="114" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E64" s="143" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F64" s="146">
         <v>9.4000000000000004E-3</v>
@@ -8871,18 +8871,18 @@
       </c>
       <c r="K64" s="157">
         <f t="shared" si="12"/>
-        <v>117500</v>
+        <v>136300</v>
       </c>
       <c r="L64" s="189">
         <v>0</v>
       </c>
       <c r="M64" s="159">
         <f t="shared" si="7"/>
-        <v>117500.46</v>
+        <v>136300.46</v>
       </c>
       <c r="N64" s="159">
         <f t="shared" si="6"/>
-        <v>124550.46</v>
+        <v>144478.46</v>
       </c>
       <c r="O64" s="211">
         <f t="shared" si="8"/>
@@ -8891,14 +8891,14 @@
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B65" s="6"/>
       <c r="C65" s="35" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D65" s="114" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E65" s="143"/>
       <c r="F65" s="146">
@@ -8921,18 +8921,18 @@
       </c>
       <c r="K65" s="157">
         <f t="shared" si="12"/>
-        <v>108749.99999999999</v>
+        <v>126149.99999999999</v>
       </c>
       <c r="L65" s="189">
         <v>0</v>
       </c>
       <c r="M65" s="159">
         <f t="shared" si="7"/>
-        <v>108750.47</v>
+        <v>126150.47</v>
       </c>
       <c r="N65" s="159">
         <f t="shared" si="6"/>
-        <v>115275.47</v>
+        <v>133719.47</v>
       </c>
       <c r="O65" s="211">
         <f t="shared" si="8"/>
@@ -8941,14 +8941,14 @@
     </row>
     <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B66" s="6"/>
       <c r="C66" s="35" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D66" s="114" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E66" s="143"/>
       <c r="F66" s="146">
@@ -8971,18 +8971,18 @@
       </c>
       <c r="K66" s="157">
         <f t="shared" si="12"/>
-        <v>118750</v>
+        <v>137750</v>
       </c>
       <c r="L66" s="189">
         <v>0</v>
       </c>
       <c r="M66" s="159">
         <f t="shared" si="7"/>
-        <v>137750.48000000001</v>
+        <v>156750.48000000001</v>
       </c>
       <c r="N66" s="159">
         <f t="shared" si="6"/>
-        <v>146016.48000000001</v>
+        <v>166156.48000000001</v>
       </c>
       <c r="O66" s="211">
         <f t="shared" si="8"/>
@@ -8992,14 +8992,14 @@
     </row>
     <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B67" s="6"/>
       <c r="C67" s="35" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D67" s="114" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E67" s="143"/>
       <c r="F67" s="146">
@@ -9022,18 +9022,18 @@
       </c>
       <c r="K67" s="157">
         <f t="shared" si="12"/>
-        <v>205000.00000000003</v>
+        <v>237800.00000000003</v>
       </c>
       <c r="L67" s="189">
         <v>0</v>
       </c>
       <c r="M67" s="159">
         <f t="shared" si="7"/>
-        <v>205000.49</v>
+        <v>237800.49</v>
       </c>
       <c r="N67" s="159">
         <f t="shared" si="6"/>
-        <v>217301.49</v>
+        <v>252069.49</v>
       </c>
       <c r="O67" s="141">
         <f t="shared" si="8"/>
@@ -9043,14 +9043,14 @@
     </row>
     <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="149" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B68" s="148"/>
       <c r="C68" s="35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D68" s="114" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E68" s="143"/>
       <c r="F68" s="146">
@@ -9070,18 +9070,18 @@
       </c>
       <c r="K68" s="157">
         <f t="shared" si="12"/>
-        <v>90000</v>
+        <v>104400</v>
       </c>
       <c r="L68" s="189">
         <v>0</v>
       </c>
       <c r="M68" s="159">
         <f t="shared" si="7"/>
-        <v>429432.5</v>
+        <v>443832.5</v>
       </c>
       <c r="N68" s="159">
         <f t="shared" si="6"/>
-        <v>455198.5</v>
+        <v>470462.5</v>
       </c>
       <c r="O68" s="141">
         <f t="shared" si="8"/>
@@ -9090,14 +9090,14 @@
     </row>
     <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B69" s="6"/>
       <c r="C69" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D69" s="114" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E69" s="143"/>
       <c r="F69" s="146">
@@ -9117,18 +9117,18 @@
       </c>
       <c r="K69" s="157">
         <f t="shared" si="12"/>
-        <v>216250</v>
+        <v>250850</v>
       </c>
       <c r="L69" s="189">
         <v>0</v>
       </c>
       <c r="M69" s="159">
         <f t="shared" si="7"/>
-        <v>423851.51</v>
+        <v>458451.51</v>
       </c>
       <c r="N69" s="159">
         <f t="shared" si="6"/>
-        <v>449283.51</v>
+        <v>485959.51</v>
       </c>
       <c r="O69" s="141">
         <f t="shared" si="8"/>
@@ -9137,14 +9137,14 @@
     </row>
     <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B70" s="6"/>
       <c r="C70" s="35" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D70" s="114" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E70" s="143"/>
       <c r="F70" s="146">
@@ -9164,18 +9164,18 @@
       </c>
       <c r="K70" s="157">
         <f t="shared" si="12"/>
-        <v>117500</v>
+        <v>136300</v>
       </c>
       <c r="L70" s="189">
         <v>0</v>
       </c>
       <c r="M70" s="159">
         <f t="shared" si="7"/>
-        <v>229547.51999999999</v>
+        <v>248347.51999999999</v>
       </c>
       <c r="N70" s="159">
         <f t="shared" si="6"/>
-        <v>243320.52</v>
+        <v>263248.52</v>
       </c>
       <c r="O70" s="141">
         <f t="shared" si="8"/>
@@ -9184,14 +9184,14 @@
     </row>
     <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="35" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D71" s="114" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E71" s="143"/>
       <c r="F71" s="146">
@@ -9214,37 +9214,37 @@
       </c>
       <c r="K71" s="157">
         <f t="shared" si="12"/>
-        <v>108749.99999999999</v>
+        <v>126149.99999999999</v>
       </c>
       <c r="L71" s="189">
         <v>0</v>
       </c>
       <c r="M71" s="159">
         <f t="shared" si="7"/>
-        <v>108750.53</v>
+        <v>126150.53</v>
       </c>
       <c r="N71" s="159">
         <f t="shared" si="6"/>
-        <v>115276.53</v>
+        <v>133720.53</v>
       </c>
       <c r="O71" s="141">
         <f t="shared" si="8"/>
         <v>0.53000000000000025</v>
       </c>
       <c r="Q71" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="35" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D72" s="114" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E72" s="143"/>
       <c r="F72" s="146">
@@ -9267,18 +9267,18 @@
       </c>
       <c r="K72" s="157">
         <f t="shared" si="12"/>
-        <v>118750</v>
+        <v>137750</v>
       </c>
       <c r="L72" s="189">
         <v>0</v>
       </c>
       <c r="M72" s="159">
         <f t="shared" si="7"/>
-        <v>118750.54</v>
+        <v>137750.54</v>
       </c>
       <c r="N72" s="159">
         <f t="shared" si="6"/>
-        <v>125876.54</v>
+        <v>146016.54</v>
       </c>
       <c r="O72" s="141">
         <f t="shared" si="8"/>
@@ -9287,14 +9287,14 @@
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="57" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D73" s="114" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E73" s="143"/>
       <c r="F73" s="146">
@@ -9317,37 +9317,37 @@
       </c>
       <c r="K73" s="157">
         <f t="shared" si="12"/>
-        <v>293750</v>
+        <v>340750</v>
       </c>
       <c r="L73" s="189">
         <v>0</v>
       </c>
       <c r="M73" s="159">
         <f t="shared" si="7"/>
-        <v>293750.55</v>
+        <v>340750.55</v>
       </c>
       <c r="N73" s="159">
         <f t="shared" si="6"/>
-        <v>311376.55</v>
+        <v>361196.55</v>
       </c>
       <c r="O73" s="141">
         <f t="shared" si="8"/>
         <v>0.55000000000000027</v>
       </c>
       <c r="P73" s="213" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="35" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D74" s="114" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E74" s="143"/>
       <c r="F74" s="146">
@@ -9370,18 +9370,18 @@
       </c>
       <c r="K74" s="157">
         <f t="shared" si="12"/>
-        <v>216250</v>
+        <v>250850</v>
       </c>
       <c r="L74" s="189">
         <v>0</v>
       </c>
       <c r="M74" s="159">
         <f t="shared" si="7"/>
-        <v>216250.56</v>
+        <v>250850.56</v>
       </c>
       <c r="N74" s="159">
         <f t="shared" si="6"/>
-        <v>229226.56</v>
+        <v>265902.56</v>
       </c>
       <c r="O74" s="141">
         <f t="shared" si="8"/>
@@ -9390,14 +9390,14 @@
     </row>
     <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B75" s="6"/>
       <c r="C75" s="35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D75" s="114" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E75" s="143"/>
       <c r="F75" s="146">
@@ -9420,18 +9420,18 @@
       </c>
       <c r="K75" s="157">
         <f t="shared" si="12"/>
-        <v>117500</v>
+        <v>136300</v>
       </c>
       <c r="L75" s="189">
         <v>0</v>
       </c>
       <c r="M75" s="159">
         <f t="shared" si="7"/>
-        <v>117500.57</v>
+        <v>136300.57</v>
       </c>
       <c r="N75" s="159">
         <f t="shared" si="6"/>
-        <v>124551.57</v>
+        <v>144479.57</v>
       </c>
       <c r="O75" s="141">
         <f t="shared" si="8"/>
@@ -9440,17 +9440,17 @@
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B76" s="6"/>
       <c r="C76" s="35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D76" s="114" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E76" s="143" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F76" s="146">
         <v>8.6999999999999994E-3</v>
@@ -9469,18 +9469,18 @@
       </c>
       <c r="K76" s="157">
         <f t="shared" si="12"/>
-        <v>108749.99999999999</v>
+        <v>126149.99999999999</v>
       </c>
       <c r="L76" s="189">
         <v>0</v>
       </c>
       <c r="M76" s="159">
         <f t="shared" si="7"/>
-        <v>225151.58</v>
+        <v>242551.58</v>
       </c>
       <c r="N76" s="159">
         <f t="shared" si="6"/>
-        <v>238661.58</v>
+        <v>257105.58</v>
       </c>
       <c r="O76" s="141">
         <f t="shared" si="8"/>
@@ -9489,14 +9489,14 @@
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B77" s="6"/>
       <c r="C77" s="35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D77" s="114" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E77" s="143"/>
       <c r="F77" s="146">
@@ -9519,18 +9519,18 @@
       </c>
       <c r="K77" s="157">
         <f t="shared" si="12"/>
-        <v>118750</v>
+        <v>137750</v>
       </c>
       <c r="L77" s="189">
         <v>0</v>
       </c>
       <c r="M77" s="159">
         <f t="shared" si="7"/>
-        <v>118750.59</v>
+        <v>137750.59</v>
       </c>
       <c r="N77" s="159">
         <f t="shared" si="6"/>
-        <v>125876.59</v>
+        <v>146016.59</v>
       </c>
       <c r="O77" s="141">
         <f t="shared" si="8"/>
@@ -9539,14 +9539,14 @@
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="57" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B78" s="6"/>
       <c r="C78" s="35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D78" s="114" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E78" s="143"/>
       <c r="F78" s="146">
@@ -9569,18 +9569,18 @@
       </c>
       <c r="K78" s="157">
         <f t="shared" si="12"/>
-        <v>293750</v>
+        <v>340750</v>
       </c>
       <c r="L78" s="189">
         <v>0</v>
       </c>
       <c r="M78" s="159">
         <f t="shared" si="7"/>
-        <v>293750.59999999998</v>
+        <v>340750.6</v>
       </c>
       <c r="N78" s="159">
         <f t="shared" si="6"/>
-        <v>311376.59999999998</v>
+        <v>361196.6</v>
       </c>
       <c r="O78" s="141">
         <f t="shared" si="8"/>
@@ -9589,14 +9589,14 @@
     </row>
     <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B79" s="6"/>
       <c r="C79" s="35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D79" s="114" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E79" s="143"/>
       <c r="F79" s="146">
@@ -9619,18 +9619,18 @@
       </c>
       <c r="K79" s="157">
         <f t="shared" si="12"/>
-        <v>216250</v>
+        <v>250850</v>
       </c>
       <c r="L79" s="189">
         <v>0</v>
       </c>
       <c r="M79" s="159">
         <f t="shared" si="7"/>
-        <v>216250.61</v>
+        <v>250850.61</v>
       </c>
       <c r="N79" s="159">
         <f t="shared" si="6"/>
-        <v>229226.61</v>
+        <v>265902.61</v>
       </c>
       <c r="O79" s="141">
         <f t="shared" si="8"/>
@@ -9639,14 +9639,14 @@
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B80" s="6"/>
       <c r="C80" s="35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D80" s="114" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E80" s="143"/>
       <c r="F80" s="146">
@@ -9668,18 +9668,18 @@
       </c>
       <c r="K80" s="157">
         <f t="shared" si="12"/>
-        <v>117500</v>
+        <v>136300</v>
       </c>
       <c r="L80" s="189">
         <v>0</v>
       </c>
       <c r="M80" s="159">
         <f t="shared" si="7"/>
-        <v>242300.62</v>
+        <v>261100.62</v>
       </c>
       <c r="N80" s="159">
         <f t="shared" si="6"/>
-        <v>256839.62</v>
+        <v>276767.62</v>
       </c>
       <c r="O80" s="141">
         <f t="shared" si="8"/>
@@ -9688,17 +9688,17 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B81" s="6"/>
       <c r="C81" s="35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D81" s="114" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E81" s="143" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F81" s="146">
         <v>8.6999999999999994E-3</v>
@@ -9720,18 +9720,18 @@
       </c>
       <c r="K81" s="157">
         <f t="shared" si="12"/>
-        <v>108749.99999999999</v>
+        <v>126149.99999999999</v>
       </c>
       <c r="L81" s="189">
         <v>0</v>
       </c>
       <c r="M81" s="159">
         <f t="shared" si="7"/>
-        <v>108750.63</v>
+        <v>126150.63</v>
       </c>
       <c r="N81" s="159">
         <f t="shared" si="6"/>
-        <v>115276.63</v>
+        <v>133720.63</v>
       </c>
       <c r="O81" s="141">
         <f t="shared" si="8"/>
@@ -9740,14 +9740,14 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B82" s="6"/>
       <c r="C82" s="35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D82" s="114" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E82" s="143"/>
       <c r="F82" s="146">
@@ -9770,37 +9770,37 @@
       </c>
       <c r="K82" s="157">
         <f t="shared" si="12"/>
-        <v>118750</v>
+        <v>137750</v>
       </c>
       <c r="L82" s="189">
         <v>0</v>
       </c>
       <c r="M82" s="159">
         <f t="shared" si="7"/>
-        <v>118750.64</v>
+        <v>137750.64000000001</v>
       </c>
       <c r="N82" s="159">
         <f t="shared" si="6"/>
-        <v>125876.64</v>
+        <v>146016.64000000001</v>
       </c>
       <c r="O82" s="141">
         <f t="shared" si="8"/>
         <v>0.64000000000000035</v>
       </c>
       <c r="P82" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="57" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B83" s="6"/>
       <c r="C83" s="35" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D83" s="114" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E83" s="143"/>
       <c r="F83" s="146">
@@ -9823,18 +9823,18 @@
       </c>
       <c r="K83" s="157">
         <f t="shared" ref="K83:K114" si="17">M$2*F83</f>
-        <v>293750</v>
+        <v>340750</v>
       </c>
       <c r="L83" s="189">
         <v>0</v>
       </c>
       <c r="M83" s="159">
         <f t="shared" si="7"/>
-        <v>293750.65000000002</v>
+        <v>340750.65</v>
       </c>
       <c r="N83" s="159">
         <f t="shared" si="6"/>
-        <v>311376.65000000002</v>
+        <v>361196.65</v>
       </c>
       <c r="O83" s="141">
         <f t="shared" si="8"/>
@@ -9843,14 +9843,14 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="57" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B84" s="6"/>
       <c r="C84" s="35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D84" s="114" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E84" s="143"/>
       <c r="F84" s="146">
@@ -9873,18 +9873,18 @@
       </c>
       <c r="K84" s="157">
         <f t="shared" si="17"/>
-        <v>216250</v>
+        <v>250850</v>
       </c>
       <c r="L84" s="189">
         <v>0</v>
       </c>
       <c r="M84" s="159">
         <f t="shared" ref="M84:M131" si="19">ROUND((K84+J84+I84+L84),0) + O84</f>
-        <v>216250.66</v>
+        <v>250850.66</v>
       </c>
       <c r="N84" s="159">
         <f t="shared" ref="N84:N131" si="20">ROUND((M84*6% + M84 ),0) + O84</f>
-        <v>229226.66</v>
+        <v>265902.65999999997</v>
       </c>
       <c r="O84" s="141">
         <f t="shared" si="8"/>
@@ -9893,14 +9893,14 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D85" s="114" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E85" s="143"/>
       <c r="F85" s="146">
@@ -9923,18 +9923,18 @@
       </c>
       <c r="K85" s="157">
         <f t="shared" si="17"/>
-        <v>117500</v>
+        <v>136300</v>
       </c>
       <c r="L85" s="189">
         <v>12000</v>
       </c>
       <c r="M85" s="159">
         <f t="shared" si="19"/>
-        <v>129500.67</v>
+        <v>148300.67000000001</v>
       </c>
       <c r="N85" s="159">
         <f t="shared" si="20"/>
-        <v>137271.67000000001</v>
+        <v>157199.67000000001</v>
       </c>
       <c r="O85" s="141">
         <f t="shared" ref="O85:O131" si="21">O84+0.01</f>
@@ -9943,14 +9943,14 @@
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="57" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B86" s="6"/>
       <c r="C86" s="35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D86" s="114" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E86" s="143"/>
       <c r="F86" s="146">
@@ -9973,18 +9973,18 @@
       </c>
       <c r="K86" s="157">
         <f t="shared" si="17"/>
-        <v>108749.99999999999</v>
+        <v>126149.99999999999</v>
       </c>
       <c r="L86" s="189">
         <v>0</v>
       </c>
       <c r="M86" s="159">
         <f t="shared" si="19"/>
-        <v>108750.68</v>
+        <v>126150.68</v>
       </c>
       <c r="N86" s="159">
         <f t="shared" si="20"/>
-        <v>115276.68</v>
+        <v>133720.68</v>
       </c>
       <c r="O86" s="141">
         <f t="shared" si="21"/>
@@ -9993,14 +9993,14 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B87" s="35"/>
       <c r="C87" s="35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D87" s="114" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E87" s="143"/>
       <c r="F87" s="146">
@@ -10023,18 +10023,18 @@
       </c>
       <c r="K87" s="157">
         <f t="shared" si="17"/>
-        <v>118750</v>
+        <v>137750</v>
       </c>
       <c r="L87" s="189">
         <v>0</v>
       </c>
       <c r="M87" s="159">
         <f t="shared" si="19"/>
-        <v>118750.69</v>
+        <v>137750.69</v>
       </c>
       <c r="N87" s="159">
         <f t="shared" si="20"/>
-        <v>125876.69</v>
+        <v>146016.69</v>
       </c>
       <c r="O87" s="141">
         <f t="shared" si="21"/>
@@ -10045,10 +10045,10 @@
       <c r="A88" s="114"/>
       <c r="B88" s="35"/>
       <c r="C88" s="35" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D88" s="114" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E88" s="114"/>
       <c r="F88" s="155">
@@ -10071,18 +10071,18 @@
       </c>
       <c r="K88" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L88" s="189">
         <v>0</v>
       </c>
       <c r="M88" s="159">
         <f t="shared" si="19"/>
-        <v>28750.7</v>
+        <v>33350.699999999997</v>
       </c>
       <c r="N88" s="159">
         <f t="shared" si="20"/>
-        <v>30476.7</v>
+        <v>35352.699999999997</v>
       </c>
       <c r="O88" s="141">
         <f t="shared" si="21"/>
@@ -10093,10 +10093,10 @@
       <c r="A89" s="114"/>
       <c r="B89" s="35"/>
       <c r="C89" s="35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D89" s="114" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E89" s="114"/>
       <c r="F89" s="155">
@@ -10119,18 +10119,18 @@
       </c>
       <c r="K89" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L89" s="189">
         <v>0</v>
       </c>
       <c r="M89" s="159">
         <f t="shared" si="19"/>
-        <v>28750.71</v>
+        <v>33350.71</v>
       </c>
       <c r="N89" s="159">
         <f t="shared" si="20"/>
-        <v>30476.71</v>
+        <v>35352.71</v>
       </c>
       <c r="O89" s="141">
         <f t="shared" si="21"/>
@@ -10141,10 +10141,10 @@
       <c r="A90" s="114"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D90" s="114" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E90" s="114"/>
       <c r="F90" s="155">
@@ -10167,18 +10167,18 @@
       </c>
       <c r="K90" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L90" s="189">
         <v>0</v>
       </c>
       <c r="M90" s="159">
         <f t="shared" si="19"/>
-        <v>28750.720000000001</v>
+        <v>33350.720000000001</v>
       </c>
       <c r="N90" s="159">
         <f t="shared" si="20"/>
-        <v>30476.720000000001</v>
+        <v>35352.720000000001</v>
       </c>
       <c r="O90" s="141">
         <f t="shared" si="21"/>
@@ -10189,10 +10189,10 @@
       <c r="A91" s="114"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D91" s="114" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E91" s="114"/>
       <c r="F91" s="155">
@@ -10215,18 +10215,18 @@
       </c>
       <c r="K91" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L91" s="189">
         <v>0</v>
       </c>
       <c r="M91" s="159">
         <f t="shared" si="19"/>
-        <v>28750.73</v>
+        <v>33350.730000000003</v>
       </c>
       <c r="N91" s="159">
         <f t="shared" si="20"/>
-        <v>30476.73</v>
+        <v>35352.730000000003</v>
       </c>
       <c r="O91" s="141">
         <f t="shared" si="21"/>
@@ -10237,10 +10237,10 @@
       <c r="A92" s="114"/>
       <c r="B92" s="35"/>
       <c r="C92" s="224" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D92" s="225" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E92" s="225"/>
       <c r="F92" s="226">
@@ -10263,35 +10263,35 @@
       </c>
       <c r="K92" s="228">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L92" s="229">
         <v>0</v>
       </c>
       <c r="M92" s="230">
         <f t="shared" si="19"/>
-        <v>28750.74</v>
+        <v>33350.74</v>
       </c>
       <c r="N92" s="230">
         <f t="shared" si="20"/>
-        <v>30476.74</v>
+        <v>35352.74</v>
       </c>
       <c r="O92" s="141">
         <f t="shared" si="21"/>
         <v>0.74000000000000044</v>
       </c>
       <c r="P92" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="114"/>
       <c r="B93" s="35"/>
       <c r="C93" s="35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D93" s="114" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E93" s="114"/>
       <c r="F93" s="155">
@@ -10314,18 +10314,18 @@
       </c>
       <c r="K93" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L93" s="189">
         <v>0</v>
       </c>
       <c r="M93" s="159">
         <f t="shared" si="19"/>
-        <v>28750.75</v>
+        <v>33350.75</v>
       </c>
       <c r="N93" s="159">
         <f t="shared" si="20"/>
-        <v>30476.75</v>
+        <v>35352.75</v>
       </c>
       <c r="O93" s="141">
         <f t="shared" si="21"/>
@@ -10336,10 +10336,10 @@
       <c r="A94" s="114"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D94" s="114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E94" s="114"/>
       <c r="F94" s="155">
@@ -10362,18 +10362,18 @@
       </c>
       <c r="K94" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L94" s="189">
         <v>0</v>
       </c>
       <c r="M94" s="159">
         <f t="shared" si="19"/>
-        <v>28750.76</v>
+        <v>33350.76</v>
       </c>
       <c r="N94" s="159">
         <f t="shared" si="20"/>
-        <v>30476.76</v>
+        <v>35352.76</v>
       </c>
       <c r="O94" s="141">
         <f t="shared" si="21"/>
@@ -10384,10 +10384,10 @@
       <c r="A95" s="114"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D95" s="114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E95" s="114"/>
       <c r="F95" s="155">
@@ -10410,18 +10410,18 @@
       </c>
       <c r="K95" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L95" s="189">
         <v>0</v>
       </c>
       <c r="M95" s="159">
         <f t="shared" si="19"/>
-        <v>28750.77</v>
+        <v>33350.769999999997</v>
       </c>
       <c r="N95" s="159">
         <f t="shared" si="20"/>
-        <v>30476.77</v>
+        <v>35352.769999999997</v>
       </c>
       <c r="O95" s="141">
         <f t="shared" si="21"/>
@@ -10432,10 +10432,10 @@
       <c r="A96" s="114"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D96" s="114" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E96" s="114"/>
       <c r="F96" s="155">
@@ -10458,18 +10458,18 @@
       </c>
       <c r="K96" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L96" s="189">
         <v>0</v>
       </c>
       <c r="M96" s="159">
         <f t="shared" si="19"/>
-        <v>28750.78</v>
+        <v>33350.78</v>
       </c>
       <c r="N96" s="159">
         <f t="shared" si="20"/>
-        <v>30476.78</v>
+        <v>35352.78</v>
       </c>
       <c r="O96" s="141">
         <f t="shared" si="21"/>
@@ -10480,10 +10480,10 @@
       <c r="A97" s="114"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D97" s="114" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E97" s="114"/>
       <c r="F97" s="155">
@@ -10503,18 +10503,18 @@
       </c>
       <c r="K97" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L97" s="189">
         <v>0</v>
       </c>
       <c r="M97" s="159">
         <f t="shared" si="19"/>
-        <v>137183.79</v>
+        <v>141783.79</v>
       </c>
       <c r="N97" s="159">
         <f t="shared" si="20"/>
-        <v>145415.79</v>
+        <v>150291.79</v>
       </c>
       <c r="O97" s="141">
         <f t="shared" si="21"/>
@@ -10525,10 +10525,10 @@
       <c r="A98" s="114"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D98" s="114" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E98" s="114"/>
       <c r="F98" s="155">
@@ -10551,18 +10551,18 @@
       </c>
       <c r="K98" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L98" s="189">
         <v>0</v>
       </c>
       <c r="M98" s="159">
         <f t="shared" si="19"/>
-        <v>28750.799999999999</v>
+        <v>33350.800000000003</v>
       </c>
       <c r="N98" s="159">
         <f t="shared" si="20"/>
-        <v>30476.799999999999</v>
+        <v>35352.800000000003</v>
       </c>
       <c r="O98" s="141">
         <f t="shared" si="21"/>
@@ -10573,10 +10573,10 @@
       <c r="A99" s="114"/>
       <c r="B99" s="35"/>
       <c r="C99" s="35" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D99" s="114" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E99" s="114"/>
       <c r="F99" s="94">
@@ -10596,18 +10596,18 @@
       </c>
       <c r="K99" s="26">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L99" s="189">
         <v>0</v>
       </c>
       <c r="M99" s="8">
         <f t="shared" si="19"/>
-        <v>56351.81</v>
+        <v>60951.81</v>
       </c>
       <c r="N99" s="8">
         <f t="shared" si="20"/>
-        <v>59733.81</v>
+        <v>64609.81</v>
       </c>
       <c r="O99" s="141">
         <f t="shared" si="21"/>
@@ -10618,10 +10618,10 @@
       <c r="A100" s="114"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D100" s="114" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E100" s="114"/>
       <c r="F100" s="94">
@@ -10644,18 +10644,18 @@
       </c>
       <c r="K100" s="26">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L100" s="189">
         <v>0</v>
       </c>
       <c r="M100" s="8">
         <f t="shared" si="19"/>
-        <v>28750.82</v>
+        <v>33350.82</v>
       </c>
       <c r="N100" s="8">
         <f t="shared" si="20"/>
-        <v>30476.82</v>
+        <v>35352.82</v>
       </c>
       <c r="O100" s="141">
         <f t="shared" si="21"/>
@@ -10666,10 +10666,10 @@
       <c r="A101" s="114"/>
       <c r="B101" s="35"/>
       <c r="C101" s="35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D101" s="114" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E101" s="114"/>
       <c r="F101" s="94">
@@ -10692,18 +10692,18 @@
       </c>
       <c r="K101" s="26">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L101" s="189">
         <v>0</v>
       </c>
       <c r="M101" s="8">
         <f t="shared" si="19"/>
-        <v>28750.83</v>
+        <v>33350.83</v>
       </c>
       <c r="N101" s="8">
         <f t="shared" si="20"/>
-        <v>30476.83</v>
+        <v>35352.83</v>
       </c>
       <c r="O101" s="141">
         <f t="shared" si="21"/>
@@ -10714,10 +10714,10 @@
       <c r="A102" s="114"/>
       <c r="B102" s="35"/>
       <c r="C102" s="35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D102" s="114" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E102" s="114"/>
       <c r="F102" s="155">
@@ -10740,18 +10740,18 @@
       </c>
       <c r="K102" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L102" s="189">
         <v>0</v>
       </c>
       <c r="M102" s="159">
         <f t="shared" si="19"/>
-        <v>28750.84</v>
+        <v>33350.839999999997</v>
       </c>
       <c r="N102" s="159">
         <f t="shared" si="20"/>
-        <v>30476.84</v>
+        <v>35352.839999999997</v>
       </c>
       <c r="O102" s="141">
         <f t="shared" si="21"/>
@@ -10762,10 +10762,10 @@
       <c r="A103" s="114"/>
       <c r="B103" s="35"/>
       <c r="C103" s="35" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D103" s="114" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E103" s="114"/>
       <c r="F103" s="155">
@@ -10788,18 +10788,18 @@
       </c>
       <c r="K103" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L103" s="189">
         <v>0</v>
       </c>
       <c r="M103" s="159">
         <f t="shared" si="19"/>
-        <v>28750.85</v>
+        <v>33350.85</v>
       </c>
       <c r="N103" s="159">
         <f t="shared" si="20"/>
-        <v>30476.85</v>
+        <v>35352.85</v>
       </c>
       <c r="O103" s="141">
         <f t="shared" si="21"/>
@@ -10810,10 +10810,10 @@
       <c r="A104" s="114"/>
       <c r="B104" s="35"/>
       <c r="C104" s="35" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D104" s="114" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E104" s="114"/>
       <c r="F104" s="94">
@@ -10833,18 +10833,18 @@
       </c>
       <c r="K104" s="26">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L104" s="189">
         <v>0</v>
       </c>
       <c r="M104" s="8">
         <f t="shared" si="19"/>
-        <v>56351.86</v>
+        <v>60951.86</v>
       </c>
       <c r="N104" s="8">
         <f t="shared" si="20"/>
-        <v>59733.86</v>
+        <v>64609.86</v>
       </c>
       <c r="O104" s="141">
         <f t="shared" si="21"/>
@@ -10855,10 +10855,10 @@
       <c r="A105" s="114"/>
       <c r="B105" s="35"/>
       <c r="C105" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D105" s="114" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E105" s="114"/>
       <c r="F105" s="94">
@@ -10881,18 +10881,18 @@
       </c>
       <c r="K105" s="26">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L105" s="189">
         <v>0</v>
       </c>
       <c r="M105" s="8">
         <f t="shared" si="19"/>
-        <v>28750.87</v>
+        <v>33350.870000000003</v>
       </c>
       <c r="N105" s="8">
         <f t="shared" si="20"/>
-        <v>30476.87</v>
+        <v>35352.870000000003</v>
       </c>
       <c r="O105" s="141">
         <f t="shared" si="21"/>
@@ -10903,10 +10903,10 @@
       <c r="A106" s="114"/>
       <c r="B106" s="35"/>
       <c r="C106" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D106" s="114" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E106" s="114"/>
       <c r="F106" s="94">
@@ -10929,18 +10929,18 @@
       </c>
       <c r="K106" s="26">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L106" s="189">
         <v>0</v>
       </c>
       <c r="M106" s="8">
         <f t="shared" si="19"/>
-        <v>28750.880000000001</v>
+        <v>33350.879999999997</v>
       </c>
       <c r="N106" s="8">
         <f t="shared" si="20"/>
-        <v>30476.880000000001</v>
+        <v>35352.879999999997</v>
       </c>
       <c r="O106" s="141">
         <f t="shared" si="21"/>
@@ -10951,10 +10951,10 @@
       <c r="A107" s="114"/>
       <c r="B107" s="35"/>
       <c r="C107" s="35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D107" s="114" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E107" s="114"/>
       <c r="F107" s="94">
@@ -10976,18 +10976,18 @@
       </c>
       <c r="K107" s="26">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L107" s="189">
         <v>0</v>
       </c>
       <c r="M107" s="8">
         <f t="shared" si="19"/>
-        <v>33350.89</v>
+        <v>37950.89</v>
       </c>
       <c r="N107" s="8">
         <f t="shared" si="20"/>
-        <v>35352.89</v>
+        <v>40228.89</v>
       </c>
       <c r="O107" s="141">
         <f t="shared" si="21"/>
@@ -10998,10 +10998,10 @@
       <c r="A108" s="114"/>
       <c r="B108" s="35"/>
       <c r="C108" s="35" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D108" s="114" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E108" s="114"/>
       <c r="F108" s="94">
@@ -11024,18 +11024,18 @@
       </c>
       <c r="K108" s="26">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L108" s="189">
         <v>0</v>
       </c>
       <c r="M108" s="8">
         <f t="shared" si="19"/>
-        <v>28750.9</v>
+        <v>33350.9</v>
       </c>
       <c r="N108" s="8">
         <f t="shared" si="20"/>
-        <v>30476.9</v>
+        <v>35352.9</v>
       </c>
       <c r="O108" s="141">
         <f t="shared" si="21"/>
@@ -11046,10 +11046,10 @@
       <c r="A109" s="114"/>
       <c r="B109" s="35"/>
       <c r="C109" s="35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D109" s="114" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E109" s="114"/>
       <c r="F109" s="94">
@@ -11072,18 +11072,18 @@
       </c>
       <c r="K109" s="26">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L109" s="189">
         <v>0</v>
       </c>
       <c r="M109" s="8">
         <f t="shared" si="19"/>
-        <v>28750.91</v>
+        <v>33350.910000000003</v>
       </c>
       <c r="N109" s="8">
         <f t="shared" si="20"/>
-        <v>30476.91</v>
+        <v>35352.910000000003</v>
       </c>
       <c r="O109" s="141">
         <f t="shared" si="21"/>
@@ -11094,10 +11094,10 @@
       <c r="A110" s="114"/>
       <c r="B110" s="35"/>
       <c r="C110" s="35" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D110" s="114" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E110" s="114"/>
       <c r="F110" s="155">
@@ -11120,18 +11120,18 @@
       </c>
       <c r="K110" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L110" s="189">
         <v>0</v>
       </c>
       <c r="M110" s="159">
         <f t="shared" si="19"/>
-        <v>28750.92</v>
+        <v>33350.92</v>
       </c>
       <c r="N110" s="159">
         <f t="shared" si="20"/>
-        <v>30476.92</v>
+        <v>35352.92</v>
       </c>
       <c r="O110" s="141">
         <f t="shared" si="21"/>
@@ -11142,10 +11142,10 @@
       <c r="A111" s="114"/>
       <c r="B111" s="35"/>
       <c r="C111" s="35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D111" s="114" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E111" s="114"/>
       <c r="F111" s="155">
@@ -11168,18 +11168,18 @@
       </c>
       <c r="K111" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L111" s="189">
         <v>0</v>
       </c>
       <c r="M111" s="159">
         <f t="shared" si="19"/>
-        <v>28750.93</v>
+        <v>33350.93</v>
       </c>
       <c r="N111" s="159">
         <f t="shared" si="20"/>
-        <v>30476.93</v>
+        <v>35352.93</v>
       </c>
       <c r="O111" s="141">
         <f t="shared" si="21"/>
@@ -11190,10 +11190,10 @@
       <c r="A112" s="114"/>
       <c r="B112" s="35"/>
       <c r="C112" s="35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D112" s="114" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E112" s="114"/>
       <c r="F112" s="155">
@@ -11216,18 +11216,18 @@
       </c>
       <c r="K112" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L112" s="189">
         <v>0</v>
       </c>
       <c r="M112" s="159">
         <f t="shared" si="19"/>
-        <v>28750.94</v>
+        <v>33350.94</v>
       </c>
       <c r="N112" s="159">
         <f t="shared" si="20"/>
-        <v>30476.94</v>
+        <v>35352.94</v>
       </c>
       <c r="O112" s="141">
         <f t="shared" si="21"/>
@@ -11238,10 +11238,10 @@
       <c r="A113" s="114"/>
       <c r="B113" s="35"/>
       <c r="C113" s="35" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D113" s="114" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E113" s="114"/>
       <c r="F113" s="155">
@@ -11264,18 +11264,18 @@
       </c>
       <c r="K113" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L113" s="189">
         <v>0</v>
       </c>
       <c r="M113" s="159">
         <f t="shared" si="19"/>
-        <v>28750.95</v>
+        <v>33350.949999999997</v>
       </c>
       <c r="N113" s="159">
         <f t="shared" si="20"/>
-        <v>30476.95</v>
+        <v>35352.949999999997</v>
       </c>
       <c r="O113" s="141">
         <f t="shared" si="21"/>
@@ -11286,10 +11286,10 @@
       <c r="A114" s="114"/>
       <c r="B114" s="35"/>
       <c r="C114" s="35" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D114" s="114" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E114" s="114"/>
       <c r="F114" s="155">
@@ -11312,18 +11312,18 @@
       </c>
       <c r="K114" s="157">
         <f t="shared" si="17"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L114" s="189">
         <v>0</v>
       </c>
       <c r="M114" s="159">
         <f t="shared" si="19"/>
-        <v>28750.959999999999</v>
+        <v>33350.959999999999</v>
       </c>
       <c r="N114" s="159">
         <f t="shared" si="20"/>
-        <v>30476.959999999999</v>
+        <v>35352.959999999999</v>
       </c>
       <c r="O114" s="141">
         <f t="shared" si="21"/>
@@ -11334,10 +11334,10 @@
       <c r="A115" s="114"/>
       <c r="B115" s="35"/>
       <c r="C115" s="35" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D115" s="114" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E115" s="114"/>
       <c r="F115" s="155">
@@ -11360,18 +11360,18 @@
       </c>
       <c r="K115" s="157">
         <f t="shared" ref="K115:K131" si="25">M$2*F115</f>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L115" s="189">
         <v>0</v>
       </c>
       <c r="M115" s="159">
         <f t="shared" si="19"/>
-        <v>28750.97</v>
+        <v>33350.97</v>
       </c>
       <c r="N115" s="159">
         <f t="shared" si="20"/>
-        <v>30476.97</v>
+        <v>35352.97</v>
       </c>
       <c r="O115" s="141">
         <f t="shared" si="21"/>
@@ -11382,13 +11382,13 @@
       <c r="A116" s="114"/>
       <c r="B116" s="35"/>
       <c r="C116" s="191" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D116" s="192" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E116" s="192" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F116" s="200">
         <v>2.3E-3</v>
@@ -11409,18 +11409,18 @@
       </c>
       <c r="K116" s="197">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L116" s="198">
         <v>0</v>
       </c>
       <c r="M116" s="199">
         <f t="shared" si="19"/>
-        <v>54375.98</v>
+        <v>58975.98</v>
       </c>
       <c r="N116" s="199">
         <f t="shared" si="20"/>
-        <v>57639.98</v>
+        <v>62515.98</v>
       </c>
       <c r="O116" s="141">
         <f t="shared" si="21"/>
@@ -11431,10 +11431,10 @@
       <c r="A117" s="114"/>
       <c r="B117" s="35"/>
       <c r="C117" s="35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D117" s="114" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E117" s="114"/>
       <c r="F117" s="155">
@@ -11454,18 +11454,18 @@
       </c>
       <c r="K117" s="157">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L117" s="189">
         <v>0</v>
       </c>
       <c r="M117" s="159">
         <f t="shared" si="19"/>
-        <v>100053.99</v>
+        <v>104653.99</v>
       </c>
       <c r="N117" s="159">
         <f t="shared" si="20"/>
-        <v>106057.99</v>
+        <v>110933.99</v>
       </c>
       <c r="O117" s="141">
         <f t="shared" si="21"/>
@@ -11476,10 +11476,10 @@
       <c r="A118" s="114"/>
       <c r="B118" s="35"/>
       <c r="C118" s="191" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D118" s="192" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E118" s="192"/>
       <c r="F118" s="200">
@@ -11502,35 +11502,35 @@
       </c>
       <c r="K118" s="197">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L118" s="198">
         <v>0</v>
       </c>
       <c r="M118" s="199">
         <f t="shared" si="19"/>
-        <v>28751</v>
+        <v>33351</v>
       </c>
       <c r="N118" s="199">
         <f t="shared" si="20"/>
-        <v>30477</v>
+        <v>35353</v>
       </c>
       <c r="O118" s="141">
         <f t="shared" si="21"/>
         <v>1.0000000000000007</v>
       </c>
       <c r="P118" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="135"/>
       <c r="B119" s="35"/>
       <c r="C119" s="35" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D119" s="114" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E119" s="114"/>
       <c r="F119" s="155">
@@ -11553,18 +11553,18 @@
       </c>
       <c r="K119" s="157">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L119" s="189">
         <v>0</v>
       </c>
       <c r="M119" s="159">
         <f t="shared" si="19"/>
-        <v>28751.01</v>
+        <v>33351.01</v>
       </c>
       <c r="N119" s="159">
         <f t="shared" si="20"/>
-        <v>30477.01</v>
+        <v>35353.01</v>
       </c>
       <c r="O119" s="141">
         <f t="shared" si="21"/>
@@ -11575,10 +11575,10 @@
       <c r="A120" s="135"/>
       <c r="B120" s="35"/>
       <c r="C120" s="35" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D120" s="114" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E120" s="114"/>
       <c r="F120" s="155">
@@ -11601,18 +11601,18 @@
       </c>
       <c r="K120" s="157">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L120" s="189">
         <v>0</v>
       </c>
       <c r="M120" s="159">
         <f t="shared" si="19"/>
-        <v>28751.02</v>
+        <v>33351.019999999997</v>
       </c>
       <c r="N120" s="159">
         <f t="shared" si="20"/>
-        <v>30477.02</v>
+        <v>35353.019999999997</v>
       </c>
       <c r="O120" s="141">
         <f t="shared" si="21"/>
@@ -11623,10 +11623,10 @@
       <c r="A121" s="135"/>
       <c r="B121" s="35"/>
       <c r="C121" s="35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D121" s="114" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E121" s="114"/>
       <c r="F121" s="155">
@@ -11648,18 +11648,18 @@
       </c>
       <c r="K121" s="157">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L121" s="189">
         <v>0</v>
       </c>
       <c r="M121" s="159">
         <f t="shared" si="19"/>
-        <v>77054.03</v>
+        <v>81654.03</v>
       </c>
       <c r="N121" s="159">
         <f t="shared" si="20"/>
-        <v>81678.03</v>
+        <v>86554.03</v>
       </c>
       <c r="O121" s="141">
         <f t="shared" si="21"/>
@@ -11670,10 +11670,10 @@
       <c r="A122" s="135"/>
       <c r="B122" s="35"/>
       <c r="C122" s="35" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D122" s="114" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E122" s="114"/>
       <c r="F122" s="94">
@@ -11696,18 +11696,18 @@
       </c>
       <c r="K122" s="26">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L122" s="189">
         <v>0</v>
       </c>
       <c r="M122" s="8">
         <f t="shared" si="19"/>
-        <v>28751.040000000001</v>
+        <v>33351.040000000001</v>
       </c>
       <c r="N122" s="8">
         <f t="shared" si="20"/>
-        <v>30477.040000000001</v>
+        <v>35353.040000000001</v>
       </c>
       <c r="O122" s="141">
         <f t="shared" si="21"/>
@@ -11718,10 +11718,10 @@
       <c r="A123" s="135"/>
       <c r="B123" s="35"/>
       <c r="C123" s="35" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D123" s="114" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E123" s="114"/>
       <c r="F123" s="94">
@@ -11743,18 +11743,18 @@
       </c>
       <c r="K123" s="26">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L123" s="189">
         <v>0</v>
       </c>
       <c r="M123" s="8">
         <f t="shared" si="19"/>
-        <v>30739.05</v>
+        <v>35339.050000000003</v>
       </c>
       <c r="N123" s="8">
         <f t="shared" si="20"/>
-        <v>32584.05</v>
+        <v>37460.050000000003</v>
       </c>
       <c r="O123" s="141">
         <f t="shared" si="21"/>
@@ -11765,10 +11765,10 @@
       <c r="A124" s="135"/>
       <c r="B124" s="35"/>
       <c r="C124" s="35" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D124" s="114" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E124" s="114"/>
       <c r="F124" s="94">
@@ -11788,18 +11788,18 @@
       </c>
       <c r="K124" s="26">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L124" s="189">
         <v>0</v>
       </c>
       <c r="M124" s="8">
         <f t="shared" si="19"/>
-        <v>100054.06</v>
+        <v>104654.06</v>
       </c>
       <c r="N124" s="8">
         <f t="shared" si="20"/>
-        <v>106058.06</v>
+        <v>110934.06</v>
       </c>
       <c r="O124" s="141">
         <f t="shared" si="21"/>
@@ -11810,10 +11810,10 @@
       <c r="A125" s="223"/>
       <c r="B125" s="191"/>
       <c r="C125" s="191" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D125" s="192" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E125" s="192"/>
       <c r="F125" s="200">
@@ -11835,18 +11835,18 @@
       </c>
       <c r="K125" s="197">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L125" s="198">
         <v>0</v>
       </c>
       <c r="M125" s="199">
         <f t="shared" si="19"/>
-        <v>72454.070000000007</v>
+        <v>77054.070000000007</v>
       </c>
       <c r="N125" s="199">
         <f t="shared" si="20"/>
-        <v>76802.070000000007</v>
+        <v>81678.070000000007</v>
       </c>
       <c r="O125" s="141">
         <f t="shared" si="21"/>
@@ -11857,10 +11857,10 @@
       <c r="A126" s="223"/>
       <c r="B126" s="191"/>
       <c r="C126" s="35" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D126" s="114" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E126" s="114"/>
       <c r="F126" s="155">
@@ -11883,18 +11883,18 @@
       </c>
       <c r="K126" s="157">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L126" s="189">
         <v>0</v>
       </c>
       <c r="M126" s="159">
         <f t="shared" si="19"/>
-        <v>28751.08</v>
+        <v>33351.08</v>
       </c>
       <c r="N126" s="159">
         <f t="shared" si="20"/>
-        <v>30477.08</v>
+        <v>35353.08</v>
       </c>
       <c r="O126" s="141">
         <f t="shared" si="21"/>
@@ -11905,10 +11905,10 @@
       <c r="A127" s="135"/>
       <c r="B127" s="35"/>
       <c r="C127" s="35" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D127" s="114" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E127" s="114"/>
       <c r="F127" s="155">
@@ -11931,18 +11931,18 @@
       </c>
       <c r="K127" s="157">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L127" s="189">
         <v>0</v>
       </c>
       <c r="M127" s="159">
         <f t="shared" si="19"/>
-        <v>28751.09</v>
+        <v>33351.089999999997</v>
       </c>
       <c r="N127" s="159">
         <f t="shared" si="20"/>
-        <v>30477.09</v>
+        <v>35353.089999999997</v>
       </c>
       <c r="O127" s="141">
         <f t="shared" si="21"/>
@@ -11953,10 +11953,10 @@
       <c r="A128" s="135"/>
       <c r="B128" s="35"/>
       <c r="C128" s="35" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D128" s="114" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E128" s="114"/>
       <c r="F128" s="94">
@@ -11979,18 +11979,18 @@
       </c>
       <c r="K128" s="26">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L128" s="189">
         <v>0</v>
       </c>
       <c r="M128" s="8">
         <f t="shared" si="19"/>
-        <v>28751.1</v>
+        <v>33351.1</v>
       </c>
       <c r="N128" s="8">
         <f t="shared" si="20"/>
-        <v>30477.1</v>
+        <v>35353.1</v>
       </c>
       <c r="O128" s="141">
         <f t="shared" si="21"/>
@@ -12001,10 +12001,10 @@
       <c r="A129" s="135"/>
       <c r="B129" s="35"/>
       <c r="C129" s="35" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D129" s="114" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E129" s="114"/>
       <c r="F129" s="94">
@@ -12027,18 +12027,18 @@
       </c>
       <c r="K129" s="26">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L129" s="189">
         <v>0</v>
       </c>
       <c r="M129" s="8">
         <f t="shared" si="19"/>
-        <v>28751.11</v>
+        <v>33351.11</v>
       </c>
       <c r="N129" s="8">
         <f t="shared" si="20"/>
-        <v>30477.11</v>
+        <v>35353.11</v>
       </c>
       <c r="O129" s="141">
         <f t="shared" si="21"/>
@@ -12051,10 +12051,10 @@
       </c>
       <c r="B130" s="35"/>
       <c r="C130" s="35" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D130" s="114" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E130" s="114"/>
       <c r="F130" s="94">
@@ -12077,18 +12077,18 @@
       </c>
       <c r="K130" s="26">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L130" s="189">
         <v>0</v>
       </c>
       <c r="M130" s="8">
         <f t="shared" si="19"/>
-        <v>28751.119999999999</v>
+        <v>33351.120000000003</v>
       </c>
       <c r="N130" s="8">
         <f t="shared" si="20"/>
-        <v>30477.119999999999</v>
+        <v>35353.120000000003</v>
       </c>
       <c r="O130" s="141">
         <f t="shared" si="21"/>
@@ -12101,10 +12101,10 @@
       </c>
       <c r="B131" s="35"/>
       <c r="C131" s="35" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D131" s="114" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E131" s="114"/>
       <c r="F131" s="94">
@@ -12127,18 +12127,18 @@
       </c>
       <c r="K131" s="26">
         <f t="shared" si="25"/>
-        <v>28750</v>
+        <v>33350</v>
       </c>
       <c r="L131" s="189">
         <v>0</v>
       </c>
       <c r="M131" s="8">
         <f t="shared" si="19"/>
-        <v>28751.13</v>
+        <v>33351.129999999997</v>
       </c>
       <c r="N131" s="8">
         <f t="shared" si="20"/>
-        <v>30477.13</v>
+        <v>35353.129999999997</v>
       </c>
       <c r="O131" s="141">
         <f t="shared" si="21"/>
@@ -12188,7 +12188,7 @@
       </c>
       <c r="K133" s="28">
         <f>SUM(K14:K132)</f>
-        <v>12452661.692639999</v>
+        <v>14312661.692639999</v>
       </c>
       <c r="L133" s="212">
         <f>SUM(L14:L132)</f>
@@ -12196,47 +12196,47 @@
       </c>
       <c r="M133" s="29">
         <f>SUM(M14:M132)</f>
-        <v>16664609.202639999</v>
+        <v>18524609.202640001</v>
       </c>
       <c r="N133" s="28">
         <f>SUM(N14:N132)</f>
-        <v>17664545.450198397</v>
+        <v>19636145.450198401</v>
       </c>
       <c r="P133" s="59"/>
     </row>
     <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="K134" s="61">
         <f>K133-L1</f>
-        <v>1784929.4026400018</v>
+        <v>3644929.4026400018</v>
       </c>
     </row>
     <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="257"/>
-      <c r="D135" s="257"/>
-      <c r="E135" s="257"/>
-      <c r="F135" s="257"/>
-      <c r="G135" s="257"/>
-      <c r="H135" s="257"/>
-      <c r="I135" s="257"/>
-      <c r="J135" s="257"/>
-      <c r="K135" s="257"/>
-      <c r="L135" s="257"/>
-      <c r="M135" s="257"/>
-      <c r="N135" s="257"/>
+      <c r="C135" s="253"/>
+      <c r="D135" s="253"/>
+      <c r="E135" s="253"/>
+      <c r="F135" s="253"/>
+      <c r="G135" s="253"/>
+      <c r="H135" s="253"/>
+      <c r="I135" s="253"/>
+      <c r="J135" s="253"/>
+      <c r="K135" s="253"/>
+      <c r="L135" s="253"/>
+      <c r="M135" s="253"/>
+      <c r="N135" s="253"/>
     </row>
     <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="257"/>
-      <c r="D136" s="257"/>
-      <c r="E136" s="257"/>
-      <c r="F136" s="257"/>
-      <c r="G136" s="257"/>
-      <c r="H136" s="257"/>
-      <c r="I136" s="257"/>
-      <c r="J136" s="257"/>
-      <c r="K136" s="257"/>
-      <c r="L136" s="257"/>
-      <c r="M136" s="257"/>
-      <c r="N136" s="257"/>
+      <c r="C136" s="253"/>
+      <c r="D136" s="253"/>
+      <c r="E136" s="253"/>
+      <c r="F136" s="253"/>
+      <c r="G136" s="253"/>
+      <c r="H136" s="253"/>
+      <c r="I136" s="253"/>
+      <c r="J136" s="253"/>
+      <c r="K136" s="253"/>
+      <c r="L136" s="253"/>
+      <c r="M136" s="253"/>
+      <c r="N136" s="253"/>
     </row>
     <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="79"/>
@@ -12253,118 +12253,118 @@
       <c r="N137" s="79"/>
     </row>
     <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C138" s="257" t="s">
-        <v>265</v>
-      </c>
-      <c r="D138" s="257"/>
-      <c r="E138" s="257"/>
-      <c r="F138" s="257"/>
-      <c r="G138" s="257"/>
-      <c r="H138" s="257"/>
-      <c r="I138" s="257"/>
-      <c r="J138" s="257"/>
-      <c r="K138" s="257"/>
-      <c r="L138" s="257"/>
-      <c r="M138" s="257"/>
-      <c r="N138" s="257"/>
+      <c r="C138" s="253" t="s">
+        <v>264</v>
+      </c>
+      <c r="D138" s="253"/>
+      <c r="E138" s="253"/>
+      <c r="F138" s="253"/>
+      <c r="G138" s="253"/>
+      <c r="H138" s="253"/>
+      <c r="I138" s="253"/>
+      <c r="J138" s="253"/>
+      <c r="K138" s="253"/>
+      <c r="L138" s="253"/>
+      <c r="M138" s="253"/>
+      <c r="N138" s="253"/>
     </row>
     <row r="139" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C139" s="257"/>
-      <c r="D139" s="257"/>
-      <c r="E139" s="257"/>
-      <c r="F139" s="257"/>
-      <c r="G139" s="257"/>
-      <c r="H139" s="257"/>
-      <c r="I139" s="257"/>
-      <c r="J139" s="257"/>
-      <c r="K139" s="257"/>
-      <c r="L139" s="257"/>
-      <c r="M139" s="257"/>
-      <c r="N139" s="257"/>
+      <c r="C139" s="253"/>
+      <c r="D139" s="253"/>
+      <c r="E139" s="253"/>
+      <c r="F139" s="253"/>
+      <c r="G139" s="253"/>
+      <c r="H139" s="253"/>
+      <c r="I139" s="253"/>
+      <c r="J139" s="253"/>
+      <c r="K139" s="253"/>
+      <c r="L139" s="253"/>
+      <c r="M139" s="253"/>
+      <c r="N139" s="253"/>
     </row>
     <row r="140" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C140" s="257"/>
-      <c r="D140" s="257"/>
-      <c r="E140" s="257"/>
-      <c r="F140" s="257"/>
-      <c r="G140" s="257"/>
-      <c r="H140" s="257"/>
-      <c r="I140" s="257"/>
-      <c r="J140" s="257"/>
-      <c r="K140" s="257"/>
-      <c r="L140" s="257"/>
-      <c r="M140" s="257"/>
-      <c r="N140" s="257"/>
+      <c r="C140" s="253"/>
+      <c r="D140" s="253"/>
+      <c r="E140" s="253"/>
+      <c r="F140" s="253"/>
+      <c r="G140" s="253"/>
+      <c r="H140" s="253"/>
+      <c r="I140" s="253"/>
+      <c r="J140" s="253"/>
+      <c r="K140" s="253"/>
+      <c r="L140" s="253"/>
+      <c r="M140" s="253"/>
+      <c r="N140" s="253"/>
     </row>
     <row r="141" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C141" s="257"/>
-      <c r="D141" s="257"/>
-      <c r="E141" s="257"/>
-      <c r="F141" s="257"/>
-      <c r="G141" s="257"/>
-      <c r="H141" s="257"/>
-      <c r="I141" s="257"/>
-      <c r="J141" s="257"/>
-      <c r="K141" s="257"/>
-      <c r="L141" s="257"/>
-      <c r="M141" s="257"/>
-      <c r="N141" s="257"/>
+      <c r="C141" s="253"/>
+      <c r="D141" s="253"/>
+      <c r="E141" s="253"/>
+      <c r="F141" s="253"/>
+      <c r="G141" s="253"/>
+      <c r="H141" s="253"/>
+      <c r="I141" s="253"/>
+      <c r="J141" s="253"/>
+      <c r="K141" s="253"/>
+      <c r="L141" s="253"/>
+      <c r="M141" s="253"/>
+      <c r="N141" s="253"/>
     </row>
     <row r="142" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C142" s="257"/>
-      <c r="D142" s="257"/>
-      <c r="E142" s="257"/>
-      <c r="F142" s="257"/>
-      <c r="G142" s="257"/>
-      <c r="H142" s="257"/>
-      <c r="I142" s="257"/>
-      <c r="J142" s="257"/>
-      <c r="K142" s="257"/>
-      <c r="L142" s="257"/>
-      <c r="M142" s="257"/>
-      <c r="N142" s="257"/>
+      <c r="C142" s="253"/>
+      <c r="D142" s="253"/>
+      <c r="E142" s="253"/>
+      <c r="F142" s="253"/>
+      <c r="G142" s="253"/>
+      <c r="H142" s="253"/>
+      <c r="I142" s="253"/>
+      <c r="J142" s="253"/>
+      <c r="K142" s="253"/>
+      <c r="L142" s="253"/>
+      <c r="M142" s="253"/>
+      <c r="N142" s="253"/>
     </row>
     <row r="143" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C143" s="257"/>
-      <c r="D143" s="257"/>
-      <c r="E143" s="257"/>
-      <c r="F143" s="257"/>
-      <c r="G143" s="257"/>
-      <c r="H143" s="257"/>
-      <c r="I143" s="257"/>
-      <c r="J143" s="257"/>
-      <c r="K143" s="257"/>
-      <c r="L143" s="257"/>
-      <c r="M143" s="257"/>
-      <c r="N143" s="257"/>
+      <c r="C143" s="253"/>
+      <c r="D143" s="253"/>
+      <c r="E143" s="253"/>
+      <c r="F143" s="253"/>
+      <c r="G143" s="253"/>
+      <c r="H143" s="253"/>
+      <c r="I143" s="253"/>
+      <c r="J143" s="253"/>
+      <c r="K143" s="253"/>
+      <c r="L143" s="253"/>
+      <c r="M143" s="253"/>
+      <c r="N143" s="253"/>
     </row>
     <row r="144" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C144" s="257"/>
-      <c r="D144" s="257"/>
-      <c r="E144" s="257"/>
-      <c r="F144" s="257"/>
-      <c r="G144" s="257"/>
-      <c r="H144" s="257"/>
-      <c r="I144" s="257"/>
-      <c r="J144" s="257"/>
-      <c r="K144" s="257"/>
-      <c r="L144" s="257"/>
-      <c r="M144" s="257"/>
-      <c r="N144" s="257"/>
+      <c r="C144" s="253"/>
+      <c r="D144" s="253"/>
+      <c r="E144" s="253"/>
+      <c r="F144" s="253"/>
+      <c r="G144" s="253"/>
+      <c r="H144" s="253"/>
+      <c r="I144" s="253"/>
+      <c r="J144" s="253"/>
+      <c r="K144" s="253"/>
+      <c r="L144" s="253"/>
+      <c r="M144" s="253"/>
+      <c r="N144" s="253"/>
     </row>
     <row r="145" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C145" s="257"/>
-      <c r="D145" s="257"/>
-      <c r="E145" s="257"/>
-      <c r="F145" s="257"/>
-      <c r="G145" s="257"/>
-      <c r="H145" s="257"/>
-      <c r="I145" s="257"/>
-      <c r="J145" s="257"/>
-      <c r="K145" s="257"/>
-      <c r="L145" s="257"/>
-      <c r="M145" s="257"/>
-      <c r="N145" s="257"/>
+      <c r="C145" s="253"/>
+      <c r="D145" s="253"/>
+      <c r="E145" s="253"/>
+      <c r="F145" s="253"/>
+      <c r="G145" s="253"/>
+      <c r="H145" s="253"/>
+      <c r="I145" s="253"/>
+      <c r="J145" s="253"/>
+      <c r="K145" s="253"/>
+      <c r="L145" s="253"/>
+      <c r="M145" s="253"/>
+      <c r="N145" s="253"/>
     </row>
     <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="79"/>
@@ -12395,111 +12395,117 @@
       <c r="N147" s="79"/>
     </row>
     <row r="148" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C148" s="256" t="s">
-        <v>264</v>
-      </c>
-      <c r="D148" s="256"/>
-      <c r="E148" s="256"/>
-      <c r="F148" s="256"/>
-      <c r="G148" s="256"/>
-      <c r="H148" s="256"/>
-      <c r="I148" s="256"/>
-      <c r="J148" s="256"/>
-      <c r="K148" s="256"/>
-      <c r="L148" s="256"/>
-      <c r="M148" s="256"/>
-      <c r="N148" s="256"/>
+      <c r="C148" s="252" t="s">
+        <v>263</v>
+      </c>
+      <c r="D148" s="252"/>
+      <c r="E148" s="252"/>
+      <c r="F148" s="252"/>
+      <c r="G148" s="252"/>
+      <c r="H148" s="252"/>
+      <c r="I148" s="252"/>
+      <c r="J148" s="252"/>
+      <c r="K148" s="252"/>
+      <c r="L148" s="252"/>
+      <c r="M148" s="252"/>
+      <c r="N148" s="252"/>
     </row>
     <row r="149" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C149" s="256"/>
-      <c r="D149" s="256"/>
-      <c r="E149" s="256"/>
-      <c r="F149" s="256"/>
-      <c r="G149" s="256"/>
-      <c r="H149" s="256"/>
-      <c r="I149" s="256"/>
-      <c r="J149" s="256"/>
-      <c r="K149" s="256"/>
-      <c r="L149" s="256"/>
-      <c r="M149" s="256"/>
-      <c r="N149" s="256"/>
+      <c r="C149" s="252"/>
+      <c r="D149" s="252"/>
+      <c r="E149" s="252"/>
+      <c r="F149" s="252"/>
+      <c r="G149" s="252"/>
+      <c r="H149" s="252"/>
+      <c r="I149" s="252"/>
+      <c r="J149" s="252"/>
+      <c r="K149" s="252"/>
+      <c r="L149" s="252"/>
+      <c r="M149" s="252"/>
+      <c r="N149" s="252"/>
     </row>
     <row r="150" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C150" s="256"/>
-      <c r="D150" s="256"/>
-      <c r="E150" s="256"/>
-      <c r="F150" s="256"/>
-      <c r="G150" s="256"/>
-      <c r="H150" s="256"/>
-      <c r="I150" s="256"/>
-      <c r="J150" s="256"/>
-      <c r="K150" s="256"/>
-      <c r="L150" s="256"/>
-      <c r="M150" s="256"/>
-      <c r="N150" s="256"/>
+      <c r="C150" s="252"/>
+      <c r="D150" s="252"/>
+      <c r="E150" s="252"/>
+      <c r="F150" s="252"/>
+      <c r="G150" s="252"/>
+      <c r="H150" s="252"/>
+      <c r="I150" s="252"/>
+      <c r="J150" s="252"/>
+      <c r="K150" s="252"/>
+      <c r="L150" s="252"/>
+      <c r="M150" s="252"/>
+      <c r="N150" s="252"/>
       <c r="P150" s="86">
         <f>L1-K133</f>
-        <v>-1784929.4026400018</v>
+        <v>-3644929.4026400018</v>
       </c>
     </row>
     <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="256"/>
-      <c r="D151" s="256"/>
-      <c r="E151" s="256"/>
-      <c r="F151" s="256"/>
-      <c r="G151" s="256"/>
-      <c r="H151" s="256"/>
-      <c r="I151" s="256"/>
-      <c r="J151" s="256"/>
-      <c r="K151" s="256"/>
-      <c r="L151" s="256"/>
-      <c r="M151" s="256"/>
-      <c r="N151" s="256"/>
+      <c r="C151" s="252"/>
+      <c r="D151" s="252"/>
+      <c r="E151" s="252"/>
+      <c r="F151" s="252"/>
+      <c r="G151" s="252"/>
+      <c r="H151" s="252"/>
+      <c r="I151" s="252"/>
+      <c r="J151" s="252"/>
+      <c r="K151" s="252"/>
+      <c r="L151" s="252"/>
+      <c r="M151" s="252"/>
+      <c r="N151" s="252"/>
     </row>
     <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="256"/>
-      <c r="D152" s="256"/>
-      <c r="E152" s="256"/>
-      <c r="F152" s="256"/>
-      <c r="G152" s="256"/>
-      <c r="H152" s="256"/>
-      <c r="I152" s="256"/>
-      <c r="J152" s="256"/>
-      <c r="K152" s="256"/>
-      <c r="L152" s="256"/>
-      <c r="M152" s="256"/>
-      <c r="N152" s="256"/>
+      <c r="C152" s="252"/>
+      <c r="D152" s="252"/>
+      <c r="E152" s="252"/>
+      <c r="F152" s="252"/>
+      <c r="G152" s="252"/>
+      <c r="H152" s="252"/>
+      <c r="I152" s="252"/>
+      <c r="J152" s="252"/>
+      <c r="K152" s="252"/>
+      <c r="L152" s="252"/>
+      <c r="M152" s="252"/>
+      <c r="N152" s="252"/>
     </row>
     <row r="153" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="256"/>
-      <c r="D153" s="256"/>
-      <c r="E153" s="256"/>
-      <c r="F153" s="256"/>
-      <c r="G153" s="256"/>
-      <c r="H153" s="256"/>
-      <c r="I153" s="256"/>
-      <c r="J153" s="256"/>
-      <c r="K153" s="256"/>
-      <c r="L153" s="256"/>
-      <c r="M153" s="256"/>
-      <c r="N153" s="256"/>
+      <c r="C153" s="252"/>
+      <c r="D153" s="252"/>
+      <c r="E153" s="252"/>
+      <c r="F153" s="252"/>
+      <c r="G153" s="252"/>
+      <c r="H153" s="252"/>
+      <c r="I153" s="252"/>
+      <c r="J153" s="252"/>
+      <c r="K153" s="252"/>
+      <c r="L153" s="252"/>
+      <c r="M153" s="252"/>
+      <c r="N153" s="252"/>
     </row>
     <row r="154" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="256"/>
-      <c r="D154" s="256"/>
-      <c r="E154" s="256"/>
-      <c r="F154" s="256"/>
-      <c r="G154" s="256"/>
-      <c r="H154" s="256"/>
-      <c r="I154" s="256"/>
-      <c r="J154" s="256"/>
-      <c r="K154" s="256"/>
-      <c r="L154" s="256"/>
-      <c r="M154" s="256"/>
-      <c r="N154" s="256"/>
+      <c r="C154" s="252"/>
+      <c r="D154" s="252"/>
+      <c r="E154" s="252"/>
+      <c r="F154" s="252"/>
+      <c r="G154" s="252"/>
+      <c r="H154" s="252"/>
+      <c r="I154" s="252"/>
+      <c r="J154" s="252"/>
+      <c r="K154" s="252"/>
+      <c r="L154" s="252"/>
+      <c r="M154" s="252"/>
+      <c r="N154" s="252"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="Q14:R15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:N154"/>
@@ -12515,12 +12521,6 @@
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="C5:N8"/>
     <mergeCell ref="C9:N10"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="17" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12536,7 +12536,7 @@
   <sheetData>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="214" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C4" s="213"/>
       <c r="D4" s="213"/>
@@ -12589,7 +12589,7 @@
         <v>1042462</v>
       </c>
       <c r="H5" s="282" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I5" s="282"/>
       <c r="J5" s="283"/>
@@ -12604,7 +12604,7 @@
         <v>36382.699999999997</v>
       </c>
       <c r="H6" s="282" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I6" s="282"/>
       <c r="J6" s="283"/>
@@ -12643,7 +12643,7 @@
         <v>60810.3</v>
       </c>
       <c r="H9" s="282" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I9" s="282"/>
       <c r="J9" s="283"/>
@@ -12658,7 +12658,7 @@
         <v>50000</v>
       </c>
       <c r="H10" s="282" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I10" s="282"/>
       <c r="J10" s="283"/>
@@ -12717,7 +12717,7 @@
       <c r="C18" s="1"/>
       <c r="G18" s="43"/>
       <c r="H18" s="282" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I18" s="282"/>
       <c r="J18" s="283"/>
@@ -12732,7 +12732,7 @@
         <v>521231</v>
       </c>
       <c r="H19" s="282" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I19" s="282"/>
       <c r="J19" s="283"/>
@@ -12771,7 +12771,7 @@
         <v>126784</v>
       </c>
       <c r="H22" s="282" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I22" s="282"/>
       <c r="J22" s="283"/>
@@ -12786,7 +12786,7 @@
         <v>21627.4</v>
       </c>
       <c r="H23" s="282" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I23" s="282"/>
       <c r="J23" s="283"/>
@@ -12870,7 +12870,7 @@
   <sheetData>
     <row r="4" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C4" s="287" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D4" s="287"/>
     </row>
@@ -12879,7 +12879,7 @@
         <v>52141.08</v>
       </c>
       <c r="D5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="3:4" x14ac:dyDescent="0.25">
@@ -12887,7 +12887,7 @@
         <v>67140.100000000006</v>
       </c>
       <c r="D6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="3:4" x14ac:dyDescent="0.25">
@@ -12895,7 +12895,7 @@
         <v>52121.11</v>
       </c>
       <c r="D7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" spans="3:4" x14ac:dyDescent="0.25">
@@ -12903,7 +12903,7 @@
         <v>67885.119999999995</v>
       </c>
       <c r="D8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9" spans="3:4" x14ac:dyDescent="0.25">
@@ -12911,7 +12911,7 @@
         <v>67140.160000000003</v>
       </c>
       <c r="D9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="3:4" x14ac:dyDescent="0.25">
@@ -12919,7 +12919,7 @@
         <v>62141.17</v>
       </c>
       <c r="D10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="3:4" x14ac:dyDescent="0.25">
@@ -12927,7 +12927,7 @@
         <v>67855.179999999993</v>
       </c>
       <c r="D11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="12" spans="3:4" x14ac:dyDescent="0.25">
@@ -12935,7 +12935,7 @@
         <v>62141.23</v>
       </c>
       <c r="D12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="3:4" x14ac:dyDescent="0.25">
@@ -12943,7 +12943,7 @@
         <v>67855.240000000005</v>
       </c>
       <c r="D13" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="14" spans="3:4" x14ac:dyDescent="0.25">

--- a/EL MIRADOR/Noviembre/Noviembre - EL MIRADOR.xlsx
+++ b/EL MIRADOR/Noviembre/Noviembre - EL MIRADOR.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\EL MIRADOR\Noviembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\EL MIRADOR\Noviembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE29061-D4CC-4DA1-9D9B-ECD59DF8C453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D891B1-B80C-4FB7-8A01-87B1CF08E877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="369">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1032,9 +1032,6 @@
     <t>LEER LA ANOTACIOn</t>
   </si>
   <si>
-    <t>la uf 55 habia abonado el 14 de oct 235.000,55, NO la pusimos paga, revisar eso y en el banco esta marcada como que la pusimos (sin embargo en el excel no fue asi)</t>
-  </si>
-  <si>
     <t>Firma</t>
   </si>
   <si>
@@ -1130,6 +1127,27 @@
   </si>
   <si>
     <t xml:space="preserve">FONDO DE GASTOS ORDINARIOS - PARA EDESUR </t>
+  </si>
+  <si>
+    <t>El comprobante de $ 90.000.- corresponde a setiembre cochera 37 y 38 $. 20.700 cada una</t>
+  </si>
+  <si>
+    <t>Octubre cochera 29 $ 25.626 y cochera 34 $ 20.700 y el comprobante de $ 71.500 es de la cochera 30 saldo al 30/11</t>
+  </si>
+  <si>
+    <t>El pago de $166.000, es del Dto 2 D</t>
+  </si>
+  <si>
+    <t>El pago de $103.000. Es del Dto 3A</t>
+  </si>
+  <si>
+    <t>Y el pago de $ 730.000 es del Dto 3C</t>
+  </si>
+  <si>
+    <t>Jose ferraro pago con un monton de depositos el 10/12</t>
+  </si>
+  <si>
+    <t>Julieta damiano en septiembre pago $87,000 a la cuenta de carolina en MP - debe estar sin deuda ya que es un pago que se nos traspapelo. Hablamos con rocio soria x mail quien es la dueña del dpto</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1164,7 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1307,8 +1325,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1384,6 +1408,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1739,7 +1775,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="288">
+  <cellXfs count="312">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1946,11 +1982,6 @@
     <xf numFmtId="165" fontId="0" fillId="2" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
@@ -2000,7 +2031,6 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="11" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2022,11 +2052,30 @@
     <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="13" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="14" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="14" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="14" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2179,6 +2228,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="15" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="15" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="15" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="15" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="15" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2637,24 +2699,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R164"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="6" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="15.88671875" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="118"/>
       <c r="B1" s="127"/>
       <c r="C1" s="137" t="s">
@@ -2668,7 +2730,7 @@
       <c r="I1" s="116"/>
       <c r="J1" s="117"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="119"/>
       <c r="B2" s="128"/>
       <c r="C2" s="128" t="s">
@@ -2682,7 +2744,7 @@
       <c r="I2" s="129"/>
       <c r="J2" s="115"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="119"/>
       <c r="B3" s="128"/>
       <c r="C3" s="128" t="s">
@@ -2698,7 +2760,7 @@
       <c r="I3" s="129"/>
       <c r="J3" s="115"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="119"/>
       <c r="B4" s="128"/>
       <c r="C4" s="128" t="s">
@@ -2712,11 +2774,11 @@
       <c r="I4" s="129"/>
       <c r="J4" s="115"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="123"/>
       <c r="B5" s="128"/>
       <c r="C5" s="128" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D5" s="128"/>
       <c r="E5" s="128" t="s">
@@ -2728,7 +2790,7 @@
       <c r="I5" s="128"/>
       <c r="J5" s="124"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="123"/>
       <c r="B6" s="128"/>
       <c r="C6" s="128" t="s">
@@ -2742,7 +2804,7 @@
       <c r="I6" s="128"/>
       <c r="J6" s="124"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="125"/>
       <c r="B7" s="126"/>
       <c r="C7" s="126"/>
@@ -2754,118 +2816,118 @@
       <c r="I7" s="126"/>
       <c r="J7" s="130"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="237" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="250" t="s">
         <v>264</v>
       </c>
-      <c r="B14" s="237"/>
-      <c r="C14" s="237"/>
-      <c r="D14" s="237"/>
-      <c r="E14" s="237"/>
-      <c r="F14" s="237"/>
-      <c r="G14" s="237"/>
-      <c r="H14" s="237"/>
-      <c r="I14" s="237"/>
-      <c r="J14" s="237"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="237"/>
-      <c r="B15" s="237"/>
-      <c r="C15" s="237"/>
-      <c r="D15" s="237"/>
-      <c r="E15" s="237"/>
-      <c r="F15" s="237"/>
-      <c r="G15" s="237"/>
-      <c r="H15" s="237"/>
-      <c r="I15" s="237"/>
-      <c r="J15" s="237"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="237"/>
-      <c r="B16" s="237"/>
-      <c r="C16" s="237"/>
-      <c r="D16" s="237"/>
-      <c r="E16" s="237"/>
-      <c r="F16" s="237"/>
-      <c r="G16" s="237"/>
-      <c r="H16" s="237"/>
-      <c r="I16" s="237"/>
-      <c r="J16" s="237"/>
-    </row>
-    <row r="17" spans="1:10" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="237"/>
-      <c r="B17" s="237"/>
-      <c r="C17" s="237"/>
-      <c r="D17" s="237"/>
-      <c r="E17" s="237"/>
-      <c r="F17" s="237"/>
-      <c r="G17" s="237"/>
-      <c r="H17" s="237"/>
-      <c r="I17" s="237"/>
-      <c r="J17" s="237"/>
-    </row>
-    <row r="18" spans="1:10" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="237"/>
-      <c r="B18" s="237"/>
-      <c r="C18" s="237"/>
-      <c r="D18" s="237"/>
-      <c r="E18" s="237"/>
-      <c r="F18" s="237"/>
-      <c r="G18" s="237"/>
-      <c r="H18" s="237"/>
-      <c r="I18" s="237"/>
-      <c r="J18" s="237"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="250"/>
+      <c r="C14" s="250"/>
+      <c r="D14" s="250"/>
+      <c r="E14" s="250"/>
+      <c r="F14" s="250"/>
+      <c r="G14" s="250"/>
+      <c r="H14" s="250"/>
+      <c r="I14" s="250"/>
+      <c r="J14" s="250"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="250"/>
+      <c r="B15" s="250"/>
+      <c r="C15" s="250"/>
+      <c r="D15" s="250"/>
+      <c r="E15" s="250"/>
+      <c r="F15" s="250"/>
+      <c r="G15" s="250"/>
+      <c r="H15" s="250"/>
+      <c r="I15" s="250"/>
+      <c r="J15" s="250"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="250"/>
+      <c r="B16" s="250"/>
+      <c r="C16" s="250"/>
+      <c r="D16" s="250"/>
+      <c r="E16" s="250"/>
+      <c r="F16" s="250"/>
+      <c r="G16" s="250"/>
+      <c r="H16" s="250"/>
+      <c r="I16" s="250"/>
+      <c r="J16" s="250"/>
+    </row>
+    <row r="17" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="250"/>
+      <c r="B17" s="250"/>
+      <c r="C17" s="250"/>
+      <c r="D17" s="250"/>
+      <c r="E17" s="250"/>
+      <c r="F17" s="250"/>
+      <c r="G17" s="250"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="250"/>
+      <c r="J17" s="250"/>
+    </row>
+    <row r="18" spans="1:10" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="250"/>
+      <c r="B18" s="250"/>
+      <c r="C18" s="250"/>
+      <c r="D18" s="250"/>
+      <c r="E18" s="250"/>
+      <c r="F18" s="250"/>
+      <c r="G18" s="250"/>
+      <c r="H18" s="250"/>
+      <c r="I18" s="250"/>
+      <c r="J18" s="250"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="2"/>
       <c r="H19" s="100"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="246" t="s">
-        <v>334</v>
-      </c>
-      <c r="B20" s="246"/>
-      <c r="C20" s="246"/>
-      <c r="D20" s="246"/>
-      <c r="E20" s="246"/>
-      <c r="F20" s="246"/>
-      <c r="G20" s="246"/>
-      <c r="H20" s="246"/>
-      <c r="I20" s="246"/>
-      <c r="J20" s="246"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="246"/>
-      <c r="B21" s="246"/>
-      <c r="C21" s="246"/>
-      <c r="D21" s="246"/>
-      <c r="E21" s="246"/>
-      <c r="F21" s="246"/>
-      <c r="G21" s="246"/>
-      <c r="H21" s="246"/>
-      <c r="I21" s="246"/>
-      <c r="J21" s="246"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="246"/>
-      <c r="B22" s="246"/>
-      <c r="C22" s="246"/>
-      <c r="D22" s="246"/>
-      <c r="E22" s="246"/>
-      <c r="F22" s="246"/>
-      <c r="G22" s="246"/>
-      <c r="H22" s="246"/>
-      <c r="I22" s="246"/>
-      <c r="J22" s="246"/>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="259" t="s">
+        <v>333</v>
+      </c>
+      <c r="B20" s="259"/>
+      <c r="C20" s="259"/>
+      <c r="D20" s="259"/>
+      <c r="E20" s="259"/>
+      <c r="F20" s="259"/>
+      <c r="G20" s="259"/>
+      <c r="H20" s="259"/>
+      <c r="I20" s="259"/>
+      <c r="J20" s="259"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="259"/>
+      <c r="B21" s="259"/>
+      <c r="C21" s="259"/>
+      <c r="D21" s="259"/>
+      <c r="E21" s="259"/>
+      <c r="F21" s="259"/>
+      <c r="G21" s="259"/>
+      <c r="H21" s="259"/>
+      <c r="I21" s="259"/>
+      <c r="J21" s="259"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="259"/>
+      <c r="B22" s="259"/>
+      <c r="C22" s="259"/>
+      <c r="D22" s="259"/>
+      <c r="E22" s="259"/>
+      <c r="F22" s="259"/>
+      <c r="G22" s="259"/>
+      <c r="H22" s="259"/>
+      <c r="I22" s="259"/>
+      <c r="J22" s="259"/>
+    </row>
+    <row r="23" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="100"/>
     </row>
-    <row r="24" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="12" t="s">
         <v>19</v>
       </c>
@@ -2891,7 +2953,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="50" t="s">
         <v>237</v>
       </c>
@@ -2905,7 +2967,7 @@
       <c r="I25" s="101"/>
       <c r="J25" s="101"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>45</v>
       </c>
@@ -2921,7 +2983,7 @@
       <c r="I26" s="58"/>
       <c r="J26" s="58"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>240</v>
       </c>
@@ -2937,7 +2999,7 @@
       <c r="I27" s="58"/>
       <c r="J27" s="58"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>238</v>
       </c>
@@ -2954,7 +3016,7 @@
       <c r="I28" s="58"/>
       <c r="J28" s="58"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>239</v>
       </c>
@@ -2970,7 +3032,7 @@
       <c r="I29" s="58"/>
       <c r="J29" s="58"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>314</v>
       </c>
@@ -2986,7 +3048,7 @@
       <c r="I30" s="58"/>
       <c r="J30" s="58"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>241</v>
       </c>
@@ -3002,7 +3064,7 @@
       <c r="I31" s="58"/>
       <c r="J31" s="58"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="99" t="s">
         <v>170</v>
       </c>
@@ -3019,7 +3081,7 @@
       <c r="I32" s="98"/>
       <c r="J32" s="98"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="50" t="s">
         <v>236</v>
       </c>
@@ -3033,7 +3095,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>45</v>
       </c>
@@ -3049,7 +3111,7 @@
       <c r="I34" s="58"/>
       <c r="J34" s="58"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>310</v>
       </c>
@@ -3065,7 +3127,7 @@
       <c r="I35" s="58"/>
       <c r="J35" s="58"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>240</v>
       </c>
@@ -3082,7 +3144,7 @@
       <c r="I36" s="58"/>
       <c r="J36" s="58"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>238</v>
       </c>
@@ -3099,7 +3161,7 @@
       <c r="I37" s="58"/>
       <c r="J37" s="58"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>239</v>
       </c>
@@ -3116,7 +3178,7 @@
       <c r="I38" s="58"/>
       <c r="J38" s="58"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>314</v>
       </c>
@@ -3133,7 +3195,7 @@
       <c r="I39" s="58"/>
       <c r="J39" s="58"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>241</v>
       </c>
@@ -3149,7 +3211,7 @@
       <c r="I40" s="58"/>
       <c r="J40" s="58"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="99" t="s">
         <v>170</v>
       </c>
@@ -3166,7 +3228,7 @@
       <c r="I41" s="98"/>
       <c r="J41" s="98"/>
     </row>
-    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="33" t="s">
         <v>1</v>
       </c>
@@ -3209,7 +3271,7 @@
         <v>1655136.7999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="32" t="s">
         <v>34</v>
       </c>
@@ -3232,7 +3294,7 @@
       </c>
       <c r="L43" s="69"/>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="32"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -3253,7 +3315,7 @@
       </c>
       <c r="L44" s="69"/>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="32"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -3266,7 +3328,7 @@
       <c r="J45" s="6"/>
       <c r="L45" s="69"/>
     </row>
-    <row r="46" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="32"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -3279,7 +3341,7 @@
       <c r="J46" s="6"/>
       <c r="L46" s="69"/>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="33" t="s">
         <v>40</v>
       </c>
@@ -3310,7 +3372,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="32" t="s">
         <v>252</v>
       </c>
@@ -3331,7 +3393,7 @@
       </c>
       <c r="L48" s="69"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -3347,7 +3409,7 @@
       <c r="J49" s="58"/>
       <c r="L49" s="69"/>
     </row>
-    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -3363,7 +3425,7 @@
       <c r="J50" s="58"/>
       <c r="L50" s="69"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="32"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -3382,7 +3444,7 @@
       </c>
       <c r="L51" s="69"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="33" t="s">
         <v>35</v>
       </c>
@@ -3410,7 +3472,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="32" t="s">
         <v>246</v>
       </c>
@@ -3425,13 +3487,13 @@
       <c r="J53" s="49"/>
       <c r="L53" s="69"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="35" t="s">
         <v>249</v>
       </c>
       <c r="B54" s="35"/>
       <c r="C54" s="35" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D54" s="87">
         <v>278973.90000000002</v>
@@ -3444,13 +3506,13 @@
       <c r="J54" s="49"/>
       <c r="L54" s="69"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="35" t="s">
         <v>249</v>
       </c>
       <c r="B55" s="35"/>
       <c r="C55" s="35" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D55" s="87">
         <v>14032.9</v>
@@ -3463,12 +3525,12 @@
       <c r="J55" s="49"/>
       <c r="L55" s="69"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="35" t="s">
         <v>251</v>
       </c>
       <c r="B56" s="35" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C56" s="35"/>
       <c r="D56" s="87">
@@ -3482,12 +3544,12 @@
       <c r="J56" s="49"/>
       <c r="L56" s="69"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="35" t="s">
         <v>251</v>
       </c>
       <c r="B57" s="35" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C57" s="35"/>
       <c r="D57" s="87">
@@ -3501,12 +3563,12 @@
       <c r="J57" s="49"/>
       <c r="L57" s="69"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="35" t="s">
         <v>250</v>
       </c>
       <c r="B58" s="35" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C58" s="35"/>
       <c r="D58" s="87">
@@ -3520,12 +3582,12 @@
       <c r="J58" s="49"/>
       <c r="L58" s="69"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="35" t="s">
         <v>250</v>
       </c>
       <c r="B59" s="35" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C59" s="35"/>
       <c r="D59" s="87">
@@ -3539,7 +3601,7 @@
       <c r="J59" s="49"/>
       <c r="L59" s="69"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="33" t="s">
         <v>248</v>
       </c>
@@ -3582,7 +3644,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="32" t="s">
         <v>2</v>
       </c>
@@ -3597,13 +3659,13 @@
       <c r="J61" s="6"/>
       <c r="L61" s="69"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>242</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D62" s="44">
         <v>56231.41</v>
@@ -3616,13 +3678,13 @@
       <c r="J62" s="6"/>
       <c r="L62" s="69"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>296</v>
       </c>
       <c r="B63" s="6"/>
       <c r="C63" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D63" s="44">
         <v>64940.71</v>
@@ -3635,7 +3697,7 @@
       <c r="J63" s="6"/>
       <c r="L63" s="69"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="33" t="s">
         <v>247</v>
       </c>
@@ -3678,7 +3740,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="32" t="s">
         <v>229</v>
       </c>
@@ -3693,7 +3755,7 @@
       <c r="J65" s="36"/>
       <c r="L65" s="69"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>233</v>
       </c>
@@ -3732,7 +3794,7 @@
       </c>
       <c r="L66" s="69"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>234</v>
       </c>
@@ -3771,7 +3833,7 @@
       </c>
       <c r="L67" s="69"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>235</v>
       </c>
@@ -3810,7 +3872,7 @@
       </c>
       <c r="L68" s="69"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="33" t="s">
         <v>3</v>
       </c>
@@ -3853,7 +3915,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="32" t="s">
         <v>4</v>
       </c>
@@ -3868,15 +3930,15 @@
       <c r="J70" s="6"/>
       <c r="L70" s="69"/>
     </row>
-    <row r="71" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="71" t="s">
         <v>243</v>
       </c>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
-        <v>346</v>
-      </c>
-      <c r="D71" s="234">
+        <v>345</v>
+      </c>
+      <c r="D71" s="227">
         <v>839647.54</v>
       </c>
       <c r="E71" s="68">
@@ -3914,15 +3976,15 @@
       <c r="M71" s="86"/>
       <c r="N71" s="86"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>244</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="6" t="s">
-        <v>345</v>
-      </c>
-      <c r="D72" s="235">
+        <v>344</v>
+      </c>
+      <c r="D72" s="228">
         <v>2334594.12</v>
       </c>
       <c r="E72" s="68">
@@ -3960,13 +4022,13 @@
       <c r="M72" s="86"/>
       <c r="N72" s="86"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>245</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D73" s="44">
         <v>118908</v>
@@ -3997,9 +4059,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B74" s="6"/>
       <c r="C74" s="35"/>
@@ -4026,7 +4088,7 @@
       <c r="M74" s="86"/>
       <c r="N74" s="86"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="35" t="s">
         <v>299</v>
       </c>
@@ -4061,7 +4123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="35" t="s">
         <v>281</v>
       </c>
@@ -4111,7 +4173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="35" t="s">
         <v>282</v>
       </c>
@@ -4161,13 +4223,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="154" t="s">
         <v>280</v>
       </c>
       <c r="B78" s="152"/>
       <c r="C78" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D78" s="44">
         <v>100000</v>
@@ -4213,13 +4275,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" s="244" t="s">
-        <v>353</v>
-      </c>
-      <c r="B79" s="248"/>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A79" s="257" t="s">
+        <v>352</v>
+      </c>
+      <c r="B79" s="261"/>
       <c r="C79" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D79" s="44">
         <v>25000</v>
@@ -4244,13 +4306,13 @@
       <c r="M79" s="86"/>
       <c r="N79" s="86"/>
     </row>
-    <row r="80" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="244" t="s">
-        <v>347</v>
-      </c>
-      <c r="B80" s="248"/>
+    <row r="80" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="257" t="s">
+        <v>346</v>
+      </c>
+      <c r="B80" s="261"/>
       <c r="C80" s="152" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D80" s="44">
         <v>60000</v>
@@ -4278,7 +4340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="144"/>
       <c r="B81" s="144"/>
       <c r="C81" s="153"/>
@@ -4306,7 +4368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="71"/>
       <c r="B82" s="72"/>
       <c r="C82" s="72"/>
@@ -4324,7 +4386,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="33" t="s">
         <v>5</v>
       </c>
@@ -4371,7 +4433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -4384,7 +4446,7 @@
       <c r="J84" s="6"/>
       <c r="L84" s="69"/>
     </row>
-    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -4397,7 +4459,7 @@
       <c r="J85" s="6"/>
       <c r="L85" s="69"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A86" s="32" t="s">
         <v>230</v>
       </c>
@@ -4412,13 +4474,13 @@
       <c r="J86" s="6"/>
       <c r="L86" s="69"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B87" s="35"/>
       <c r="C87" s="35" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D87" s="44">
         <v>442900</v>
@@ -4450,13 +4512,13 @@
       <c r="K87" s="74"/>
       <c r="L87" s="69"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B88" s="35"/>
       <c r="C88" s="35" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D88" s="44">
         <v>90000</v>
@@ -4473,13 +4535,13 @@
       <c r="K88" s="74"/>
       <c r="L88" s="69"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B89" s="35"/>
       <c r="C89" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D89" s="44">
         <v>34596.519999999997</v>
@@ -4496,13 +4558,13 @@
       <c r="K89" s="74"/>
       <c r="L89" s="69"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B90" s="35"/>
       <c r="C90" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D90" s="44">
         <v>60000</v>
@@ -4519,13 +4581,13 @@
       <c r="K90" s="74"/>
       <c r="L90" s="69"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B91" s="35"/>
       <c r="C91" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D91" s="44">
         <v>60000</v>
@@ -4542,7 +4604,7 @@
       <c r="K91" s="74"/>
       <c r="L91" s="69"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -4556,7 +4618,7 @@
       <c r="L92" s="69"/>
       <c r="M92" s="43"/>
     </row>
-    <row r="93" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="33" t="s">
         <v>231</v>
       </c>
@@ -4600,7 +4662,7 @@
       </c>
       <c r="N93" s="43"/>
     </row>
-    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -4613,7 +4675,7 @@
       <c r="J94" s="6"/>
       <c r="L94" s="69"/>
     </row>
-    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -4626,7 +4688,7 @@
       <c r="J95" s="6"/>
       <c r="L95" s="69"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A96" s="32" t="s">
         <v>6</v>
       </c>
@@ -4641,7 +4703,7 @@
       <c r="J96" s="6"/>
       <c r="L96" s="69"/>
     </row>
-    <row r="97" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
         <v>7</v>
       </c>
@@ -4680,7 +4742,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="32"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -4694,7 +4756,7 @@
       <c r="L98" s="69"/>
       <c r="N98" s="44"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -4708,7 +4770,7 @@
       <c r="L99" s="69"/>
       <c r="N99" s="43"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="33" t="s">
         <v>8</v>
       </c>
@@ -4752,7 +4814,7 @@
       </c>
       <c r="N100" s="43"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
         <v>28</v>
       </c>
@@ -4787,7 +4849,7 @@
       </c>
       <c r="L101" s="69"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>29</v>
       </c>
@@ -4820,7 +4882,7 @@
       </c>
       <c r="L102" s="69"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A103" s="33" t="s">
         <v>232</v>
       </c>
@@ -4863,7 +4925,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="104"/>
       <c r="B104" s="104"/>
       <c r="C104" s="104"/>
@@ -4876,9 +4938,9 @@
       <c r="J104" s="104"/>
       <c r="L104" s="69"/>
     </row>
-    <row r="105" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="106" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B105" s="107"/>
       <c r="C105" s="107"/>
@@ -4919,7 +4981,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="109"/>
       <c r="B106" s="110"/>
       <c r="C106" s="110"/>
@@ -4933,7 +4995,7 @@
       <c r="K106" s="43"/>
       <c r="L106" s="69"/>
     </row>
-    <row r="107" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A107" s="3" t="s">
         <v>30</v>
       </c>
@@ -4980,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D108" s="89"/>
       <c r="E108" s="43"/>
       <c r="F108" s="43"/>
@@ -4988,7 +5050,7 @@
       <c r="H108" s="43"/>
       <c r="I108" s="43"/>
     </row>
-    <row r="109" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A109" s="64" t="s">
         <v>41</v>
       </c>
@@ -5000,9 +5062,9 @@
       <c r="H109" s="43"/>
       <c r="I109" s="43"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B110" t="s">
         <v>287</v>
@@ -5016,12 +5078,12 @@
       <c r="H110" s="43"/>
       <c r="I110" s="43"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B111" t="s">
         <v>358</v>
-      </c>
-      <c r="B111" t="s">
-        <v>359</v>
       </c>
       <c r="C111" s="136">
         <v>12000</v>
@@ -5032,7 +5094,7 @@
       <c r="H111" s="43"/>
       <c r="I111" s="43"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A112" s="1"/>
       <c r="C112" s="136"/>
       <c r="E112" s="43"/>
@@ -5041,7 +5103,7 @@
       <c r="H112" s="43"/>
       <c r="I112" s="43"/>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A113" s="1"/>
       <c r="C113" s="136"/>
       <c r="E113" s="43"/>
@@ -5050,7 +5112,7 @@
       <c r="H113" s="43"/>
       <c r="I113" s="43"/>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A114" s="1"/>
       <c r="C114" s="136"/>
       <c r="E114" s="43"/>
@@ -5059,7 +5121,7 @@
       <c r="H114" s="43"/>
       <c r="I114" s="43"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A115" s="1"/>
       <c r="C115" s="136"/>
       <c r="E115" s="43"/>
@@ -5068,7 +5130,7 @@
       <c r="H115" s="43"/>
       <c r="I115" s="43"/>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A116" s="1"/>
       <c r="C116" s="136"/>
       <c r="E116" s="43"/>
@@ -5077,7 +5139,7 @@
       <c r="H116" s="43"/>
       <c r="I116" s="43"/>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A117" s="1"/>
       <c r="C117" s="136"/>
       <c r="E117" s="43"/>
@@ -5086,7 +5148,7 @@
       <c r="H117" s="43"/>
       <c r="I117" s="43"/>
     </row>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A118" s="1"/>
       <c r="C118" s="136"/>
       <c r="E118" s="43"/>
@@ -5095,7 +5157,7 @@
       <c r="H118" s="43"/>
       <c r="I118" s="43"/>
     </row>
-    <row r="119" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="1"/>
       <c r="C119" s="136"/>
       <c r="E119" s="43"/>
@@ -5104,7 +5166,7 @@
       <c r="H119" s="43"/>
       <c r="I119" s="43"/>
     </row>
-    <row r="120" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A120" s="65" t="s">
         <v>17</v>
       </c>
@@ -5119,27 +5181,27 @@
       <c r="H120" s="43"/>
       <c r="I120" s="43"/>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E121" s="43"/>
       <c r="F121" s="43"/>
       <c r="G121" s="43"/>
       <c r="H121" s="43"/>
       <c r="I121" s="43"/>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
       <c r="E122" s="60"/>
       <c r="F122" s="60"/>
       <c r="G122" s="60"/>
       <c r="H122" s="60"/>
       <c r="I122" s="60"/>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A123" s="242" t="s">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A123" s="255" t="s">
         <v>36</v>
       </c>
-      <c r="B123" s="243"/>
-      <c r="C123" s="243"/>
-      <c r="D123" s="243"/>
+      <c r="B123" s="256"/>
+      <c r="C123" s="256"/>
+      <c r="D123" s="256"/>
       <c r="E123" s="82" t="s">
         <v>11</v>
       </c>
@@ -5159,9 +5221,9 @@
         <v>176</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="244"/>
-      <c r="B124" s="245"/>
+    <row r="124" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="257"/>
+      <c r="B124" s="258"/>
       <c r="C124" s="84"/>
       <c r="D124" s="44"/>
       <c r="E124" s="68">
@@ -5174,9 +5236,9 @@
       <c r="I124" s="68"/>
       <c r="J124" s="58"/>
     </row>
-    <row r="125" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="244"/>
-      <c r="B125" s="245"/>
+    <row r="125" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="257"/>
+      <c r="B125" s="258"/>
       <c r="C125" s="84"/>
       <c r="D125" s="44"/>
       <c r="E125" s="68"/>
@@ -5186,12 +5248,12 @@
       <c r="I125" s="68"/>
       <c r="J125" s="58"/>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A126" s="239" t="s">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A126" s="252" t="s">
         <v>17</v>
       </c>
-      <c r="B126" s="240"/>
-      <c r="C126" s="241"/>
+      <c r="B126" s="253"/>
+      <c r="C126" s="254"/>
       <c r="D126" s="81">
         <f>SUM(D124:D125)</f>
         <v>0</v>
@@ -5217,14 +5279,14 @@
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E128" s="43"/>
       <c r="F128" s="43"/>
       <c r="G128" s="43"/>
       <c r="H128" s="43"/>
       <c r="I128" s="43"/>
     </row>
-    <row r="129" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="38" t="s">
         <v>31</v>
       </c>
@@ -5233,7 +5295,7 @@
         <v>14499999.999999998</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="40" t="s">
         <v>33</v>
       </c>
@@ -5241,37 +5303,37 @@
         <f>D107-D105</f>
         <v>10667732.289999997</v>
       </c>
-      <c r="D130" s="247" t="s">
+      <c r="D130" s="260" t="s">
         <v>321</v>
       </c>
-      <c r="E130" s="247"/>
-      <c r="F130" s="247"/>
-      <c r="G130" s="247"/>
-      <c r="H130" s="247"/>
-      <c r="I130" s="247"/>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D131" s="247"/>
-      <c r="E131" s="247"/>
-      <c r="F131" s="247"/>
-      <c r="G131" s="247"/>
-      <c r="H131" s="247"/>
-      <c r="I131" s="247"/>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="E130" s="260"/>
+      <c r="F130" s="260"/>
+      <c r="G130" s="260"/>
+      <c r="H130" s="260"/>
+      <c r="I130" s="260"/>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D131" s="260"/>
+      <c r="E131" s="260"/>
+      <c r="F131" s="260"/>
+      <c r="G131" s="260"/>
+      <c r="H131" s="260"/>
+      <c r="I131" s="260"/>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B132" s="17"/>
       <c r="C132" s="18"/>
-      <c r="D132" s="247"/>
-      <c r="E132" s="247"/>
-      <c r="F132" s="247"/>
-      <c r="G132" s="247"/>
-      <c r="H132" s="247"/>
-      <c r="I132" s="247"/>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D132" s="260"/>
+      <c r="E132" s="260"/>
+      <c r="F132" s="260"/>
+      <c r="G132" s="260"/>
+      <c r="H132" s="260"/>
+      <c r="I132" s="260"/>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" s="19" t="s">
         <v>21</v>
       </c>
@@ -5279,14 +5341,14 @@
         <v>-979600.31345474347</v>
       </c>
       <c r="C133" s="20"/>
-      <c r="D133" s="247"/>
-      <c r="E133" s="247"/>
-      <c r="F133" s="247"/>
-      <c r="G133" s="247"/>
-      <c r="H133" s="247"/>
-      <c r="I133" s="247"/>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D133" s="260"/>
+      <c r="E133" s="260"/>
+      <c r="F133" s="260"/>
+      <c r="G133" s="260"/>
+      <c r="H133" s="260"/>
+      <c r="I133" s="260"/>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" s="21" t="s">
         <v>22</v>
       </c>
@@ -5297,14 +5359,14 @@
       <c r="C134" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="D134" s="247"/>
-      <c r="E134" s="247"/>
-      <c r="F134" s="247"/>
-      <c r="G134" s="247"/>
-      <c r="H134" s="247"/>
-      <c r="I134" s="247"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D134" s="260"/>
+      <c r="E134" s="260"/>
+      <c r="F134" s="260"/>
+      <c r="G134" s="260"/>
+      <c r="H134" s="260"/>
+      <c r="I134" s="260"/>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" s="21" t="s">
         <v>38</v>
       </c>
@@ -5313,15 +5375,15 @@
         <v>-10667732.289999997</v>
       </c>
       <c r="C135" s="18"/>
-      <c r="D135" s="247"/>
-      <c r="E135" s="247"/>
-      <c r="F135" s="247"/>
-      <c r="G135" s="247"/>
-      <c r="H135" s="247"/>
-      <c r="I135" s="247"/>
+      <c r="D135" s="260"/>
+      <c r="E135" s="260"/>
+      <c r="F135" s="260"/>
+      <c r="G135" s="260"/>
+      <c r="H135" s="260"/>
+      <c r="I135" s="260"/>
       <c r="K135" s="44"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" s="21" t="s">
         <v>37</v>
       </c>
@@ -5330,15 +5392,15 @@
         <v>0</v>
       </c>
       <c r="C136" s="18"/>
-      <c r="D136" s="247"/>
-      <c r="E136" s="247"/>
-      <c r="F136" s="247"/>
-      <c r="G136" s="247"/>
-      <c r="H136" s="247"/>
-      <c r="I136" s="247"/>
+      <c r="D136" s="260"/>
+      <c r="E136" s="260"/>
+      <c r="F136" s="260"/>
+      <c r="G136" s="260"/>
+      <c r="H136" s="260"/>
+      <c r="I136" s="260"/>
       <c r="K136" s="52"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" s="21" t="s">
         <v>309</v>
       </c>
@@ -5347,15 +5409,15 @@
         <v>0</v>
       </c>
       <c r="C137" s="18"/>
-      <c r="D137" s="247"/>
-      <c r="E137" s="247"/>
-      <c r="F137" s="247"/>
-      <c r="G137" s="247"/>
-      <c r="H137" s="247"/>
-      <c r="I137" s="247"/>
+      <c r="D137" s="260"/>
+      <c r="E137" s="260"/>
+      <c r="F137" s="260"/>
+      <c r="G137" s="260"/>
+      <c r="H137" s="260"/>
+      <c r="I137" s="260"/>
       <c r="K137" s="52"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" s="21" t="s">
         <v>32</v>
       </c>
@@ -5364,14 +5426,14 @@
         <v>0</v>
       </c>
       <c r="C138" s="22"/>
-      <c r="D138" s="247"/>
-      <c r="E138" s="247"/>
-      <c r="F138" s="247"/>
-      <c r="G138" s="247"/>
-      <c r="H138" s="247"/>
-      <c r="I138" s="247"/>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D138" s="260"/>
+      <c r="E138" s="260"/>
+      <c r="F138" s="260"/>
+      <c r="G138" s="260"/>
+      <c r="H138" s="260"/>
+      <c r="I138" s="260"/>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" s="21" t="s">
         <v>307</v>
       </c>
@@ -5380,14 +5442,14 @@
         <v>-27340</v>
       </c>
       <c r="C139" s="22"/>
-      <c r="D139" s="247"/>
-      <c r="E139" s="247"/>
-      <c r="F139" s="247"/>
-      <c r="G139" s="247"/>
-      <c r="H139" s="247"/>
-      <c r="I139" s="247"/>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D139" s="260"/>
+      <c r="E139" s="260"/>
+      <c r="F139" s="260"/>
+      <c r="G139" s="260"/>
+      <c r="H139" s="260"/>
+      <c r="I139" s="260"/>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" s="21" t="s">
         <v>41</v>
       </c>
@@ -5396,25 +5458,25 @@
         <v>-36000</v>
       </c>
       <c r="C140" s="22"/>
-      <c r="D140" s="247"/>
-      <c r="E140" s="247"/>
-      <c r="F140" s="247"/>
-      <c r="G140" s="247"/>
-      <c r="H140" s="247"/>
-      <c r="I140" s="247"/>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D140" s="260"/>
+      <c r="E140" s="260"/>
+      <c r="F140" s="260"/>
+      <c r="G140" s="260"/>
+      <c r="H140" s="260"/>
+      <c r="I140" s="260"/>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" s="21"/>
-      <c r="B141" s="190"/>
+      <c r="B141" s="185"/>
       <c r="C141" s="22"/>
-      <c r="D141" s="247"/>
-      <c r="E141" s="247"/>
-      <c r="F141" s="247"/>
-      <c r="G141" s="247"/>
-      <c r="H141" s="247"/>
-      <c r="I141" s="247"/>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D141" s="260"/>
+      <c r="E141" s="260"/>
+      <c r="F141" s="260"/>
+      <c r="G141" s="260"/>
+      <c r="H141" s="260"/>
+      <c r="I141" s="260"/>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" s="19" t="s">
         <v>24</v>
       </c>
@@ -5423,43 +5485,43 @@
         <v>-1436020.4734547418</v>
       </c>
       <c r="C142" s="70"/>
-      <c r="D142" s="247"/>
-      <c r="E142" s="247"/>
-      <c r="F142" s="247"/>
-      <c r="G142" s="247"/>
-      <c r="H142" s="247"/>
-      <c r="I142" s="247"/>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D142" s="260"/>
+      <c r="E142" s="260"/>
+      <c r="F142" s="260"/>
+      <c r="G142" s="260"/>
+      <c r="H142" s="260"/>
+      <c r="I142" s="260"/>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" s="22"/>
       <c r="C143" s="18"/>
-      <c r="D143" s="247"/>
-      <c r="E143" s="247"/>
-      <c r="F143" s="247"/>
-      <c r="G143" s="247"/>
-      <c r="H143" s="247"/>
-      <c r="I143" s="247"/>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D143" s="260"/>
+      <c r="E143" s="260"/>
+      <c r="F143" s="260"/>
+      <c r="G143" s="260"/>
+      <c r="H143" s="260"/>
+      <c r="I143" s="260"/>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" s="16" t="s">
         <v>308</v>
       </c>
       <c r="B144" s="8"/>
       <c r="C144" s="18"/>
-      <c r="D144" s="247"/>
-      <c r="E144" s="247"/>
-      <c r="F144" s="247"/>
-      <c r="G144" s="247"/>
-      <c r="H144" s="247"/>
-      <c r="I144" s="247"/>
-    </row>
-    <row r="145" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D144" s="260"/>
+      <c r="E144" s="260"/>
+      <c r="F144" s="260"/>
+      <c r="G144" s="260"/>
+      <c r="H144" s="260"/>
+      <c r="I144" s="260"/>
+    </row>
+    <row r="145" spans="1:18" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="19"/>
       <c r="B145" s="30"/>
       <c r="C145" s="18"/>
       <c r="D145" s="25"/>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146" s="36" t="s">
         <v>17</v>
       </c>
@@ -5470,17 +5532,17 @@
       <c r="C146" s="18"/>
       <c r="D146" s="25"/>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147" s="22"/>
       <c r="C147" s="18"/>
       <c r="D147" s="25"/>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148" s="22"/>
       <c r="C148" s="18"/>
       <c r="D148" s="25"/>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C149" s="18"/>
       <c r="D149" s="43"/>
       <c r="E149" s="86"/>
@@ -5489,7 +5551,7 @@
       <c r="H149" s="86"/>
       <c r="I149" s="86"/>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A150" s="16" t="s">
         <v>25</v>
       </c>
@@ -5505,7 +5567,7 @@
       <c r="I150" s="86"/>
       <c r="J150" s="86"/>
     </row>
-    <row r="151" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="19" t="s">
         <v>259</v>
       </c>
@@ -5518,7 +5580,7 @@
       <c r="H151" s="93"/>
       <c r="I151" s="93"/>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152" s="19"/>
       <c r="B152" s="85"/>
       <c r="C152" s="24"/>
@@ -5528,7 +5590,7 @@
       <c r="H152" s="43"/>
       <c r="I152" s="43"/>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153" s="36" t="s">
         <v>17</v>
       </c>
@@ -5538,62 +5600,62 @@
       </c>
       <c r="C153" s="24"/>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C154" s="25"/>
       <c r="D154" s="86"/>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="B155" s="22"/>
       <c r="C155" s="18"/>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="R157" s="9"/>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B160" s="238"/>
-      <c r="C160" s="238"/>
-      <c r="D160" s="238"/>
-      <c r="E160" s="238"/>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B160" s="251"/>
+      <c r="C160" s="251"/>
+      <c r="D160" s="251"/>
+      <c r="E160" s="251"/>
       <c r="F160" s="95"/>
       <c r="G160" s="95"/>
       <c r="H160" s="95"/>
       <c r="I160" s="95"/>
     </row>
-    <row r="161" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B161" s="238"/>
-      <c r="C161" s="238"/>
-      <c r="D161" s="238"/>
-      <c r="E161" s="238"/>
+    <row r="161" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B161" s="251"/>
+      <c r="C161" s="251"/>
+      <c r="D161" s="251"/>
+      <c r="E161" s="251"/>
       <c r="F161" s="95"/>
       <c r="G161" s="95"/>
       <c r="H161" s="95"/>
       <c r="I161" s="95"/>
     </row>
-    <row r="162" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B162" s="238"/>
-      <c r="C162" s="238"/>
-      <c r="D162" s="238"/>
-      <c r="E162" s="238"/>
+    <row r="162" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B162" s="251"/>
+      <c r="C162" s="251"/>
+      <c r="D162" s="251"/>
+      <c r="E162" s="251"/>
       <c r="F162" s="95"/>
       <c r="G162" s="95"/>
       <c r="H162" s="95"/>
       <c r="I162" s="95"/>
     </row>
-    <row r="163" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B163" s="238"/>
-      <c r="C163" s="238"/>
-      <c r="D163" s="238"/>
-      <c r="E163" s="238"/>
+    <row r="163" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B163" s="251"/>
+      <c r="C163" s="251"/>
+      <c r="D163" s="251"/>
+      <c r="E163" s="251"/>
       <c r="F163" s="95"/>
       <c r="G163" s="95"/>
       <c r="H163" s="95"/>
       <c r="I163" s="95"/>
     </row>
-    <row r="164" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B164" s="238"/>
-      <c r="C164" s="238"/>
-      <c r="D164" s="238"/>
-      <c r="E164" s="238"/>
+    <row r="164" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B164" s="251"/>
+      <c r="C164" s="251"/>
+      <c r="D164" s="251"/>
+      <c r="E164" s="251"/>
       <c r="F164" s="95"/>
       <c r="G164" s="95"/>
       <c r="H164" s="95"/>
@@ -5621,52 +5683,52 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DI154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="175"/>
-      <c r="B1" s="176"/>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171" t="s">
         <v>312</v>
       </c>
-      <c r="G1" s="176"/>
-      <c r="H1" s="176"/>
-      <c r="I1" s="176"/>
-      <c r="J1" s="176"/>
-      <c r="K1" s="176" t="s">
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="254">
+      <c r="L1" s="267">
         <f>RESUMEN!D107-RESUMEN!D105</f>
         <v>10667732.289999997</v>
       </c>
-      <c r="M1" s="255"/>
-      <c r="N1" s="177"/>
+      <c r="M1" s="268"/>
+      <c r="N1" s="172"/>
       <c r="O1" s="59"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="178"/>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="173"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
       <c r="D2" s="7"/>
@@ -5682,14 +5744,14 @@
         <v>44</v>
       </c>
       <c r="L2" s="7"/>
-      <c r="M2" s="179">
+      <c r="M2" s="174">
         <v>14500000</v>
       </c>
-      <c r="N2" s="180"/>
+      <c r="N2" s="175"/>
       <c r="O2" s="59"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="178" t="str">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="173" t="str">
         <f>RESUMEN!C5</f>
         <v>PERÍODO: NOVIEMBRE</v>
       </c>
@@ -5703,212 +5765,212 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="181"/>
+      <c r="J3" s="176"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
-      <c r="M3" s="182"/>
-      <c r="N3" s="183"/>
+      <c r="M3" s="177"/>
+      <c r="N3" s="178"/>
       <c r="O3" s="15"/>
     </row>
-    <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="184"/>
-      <c r="B4" s="185"/>
-      <c r="C4" s="185"/>
-      <c r="D4" s="185"/>
-      <c r="E4" s="185"/>
-      <c r="F4" s="185"/>
-      <c r="G4" s="185"/>
-      <c r="H4" s="185"/>
-      <c r="I4" s="185"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="185"/>
-      <c r="L4" s="185"/>
-      <c r="M4" s="187"/>
-      <c r="N4" s="188"/>
+    <row r="4" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="179"/>
+      <c r="B4" s="180"/>
+      <c r="C4" s="180"/>
+      <c r="D4" s="180"/>
+      <c r="E4" s="180"/>
+      <c r="F4" s="180"/>
+      <c r="G4" s="180"/>
+      <c r="H4" s="180"/>
+      <c r="I4" s="180"/>
+      <c r="J4" s="181"/>
+      <c r="K4" s="180"/>
+      <c r="L4" s="180"/>
+      <c r="M4" s="182"/>
+      <c r="N4" s="183"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="263" t="s">
-        <v>355</v>
-      </c>
-      <c r="D5" s="264"/>
-      <c r="E5" s="264"/>
-      <c r="F5" s="264"/>
-      <c r="G5" s="264"/>
-      <c r="H5" s="264"/>
-      <c r="I5" s="264"/>
-      <c r="J5" s="264"/>
-      <c r="K5" s="264"/>
-      <c r="L5" s="264"/>
-      <c r="M5" s="264"/>
-      <c r="N5" s="265"/>
+      <c r="C5" s="276" t="s">
+        <v>354</v>
+      </c>
+      <c r="D5" s="277"/>
+      <c r="E5" s="277"/>
+      <c r="F5" s="277"/>
+      <c r="G5" s="277"/>
+      <c r="H5" s="277"/>
+      <c r="I5" s="277"/>
+      <c r="J5" s="277"/>
+      <c r="K5" s="277"/>
+      <c r="L5" s="277"/>
+      <c r="M5" s="277"/>
+      <c r="N5" s="278"/>
       <c r="O5" s="15"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
-      <c r="C6" s="266"/>
-      <c r="D6" s="267"/>
-      <c r="E6" s="267"/>
-      <c r="F6" s="267"/>
-      <c r="G6" s="267"/>
-      <c r="H6" s="267"/>
-      <c r="I6" s="267"/>
-      <c r="J6" s="267"/>
-      <c r="K6" s="267"/>
-      <c r="L6" s="267"/>
-      <c r="M6" s="267"/>
-      <c r="N6" s="268"/>
+      <c r="C6" s="279"/>
+      <c r="D6" s="280"/>
+      <c r="E6" s="280"/>
+      <c r="F6" s="280"/>
+      <c r="G6" s="280"/>
+      <c r="H6" s="280"/>
+      <c r="I6" s="280"/>
+      <c r="J6" s="280"/>
+      <c r="K6" s="280"/>
+      <c r="L6" s="280"/>
+      <c r="M6" s="280"/>
+      <c r="N6" s="281"/>
       <c r="O6" s="15"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
-      <c r="C7" s="266"/>
-      <c r="D7" s="267"/>
-      <c r="E7" s="267"/>
-      <c r="F7" s="267"/>
-      <c r="G7" s="267"/>
-      <c r="H7" s="267"/>
-      <c r="I7" s="267"/>
-      <c r="J7" s="267"/>
-      <c r="K7" s="267"/>
-      <c r="L7" s="267"/>
-      <c r="M7" s="267"/>
-      <c r="N7" s="268"/>
+      <c r="C7" s="279"/>
+      <c r="D7" s="280"/>
+      <c r="E7" s="280"/>
+      <c r="F7" s="280"/>
+      <c r="G7" s="280"/>
+      <c r="H7" s="280"/>
+      <c r="I7" s="280"/>
+      <c r="J7" s="280"/>
+      <c r="K7" s="280"/>
+      <c r="L7" s="280"/>
+      <c r="M7" s="280"/>
+      <c r="N7" s="281"/>
       <c r="O7" s="15"/>
     </row>
-    <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
-      <c r="C8" s="269"/>
-      <c r="D8" s="270"/>
-      <c r="E8" s="270"/>
-      <c r="F8" s="270"/>
-      <c r="G8" s="270"/>
-      <c r="H8" s="270"/>
-      <c r="I8" s="270"/>
-      <c r="J8" s="270"/>
-      <c r="K8" s="270"/>
-      <c r="L8" s="270"/>
-      <c r="M8" s="270"/>
-      <c r="N8" s="271"/>
+      <c r="C8" s="282"/>
+      <c r="D8" s="283"/>
+      <c r="E8" s="283"/>
+      <c r="F8" s="283"/>
+      <c r="G8" s="283"/>
+      <c r="H8" s="283"/>
+      <c r="I8" s="283"/>
+      <c r="J8" s="283"/>
+      <c r="K8" s="283"/>
+      <c r="L8" s="283"/>
+      <c r="M8" s="283"/>
+      <c r="N8" s="284"/>
       <c r="P8" s="86">
         <f>L1-K133</f>
         <v>-3644929.4026400018</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
-      <c r="C9" s="272" t="s">
+      <c r="C9" s="285" t="s">
         <v>328</v>
       </c>
-      <c r="D9" s="273"/>
-      <c r="E9" s="273"/>
-      <c r="F9" s="273"/>
-      <c r="G9" s="273"/>
-      <c r="H9" s="273"/>
-      <c r="I9" s="273"/>
-      <c r="J9" s="273"/>
-      <c r="K9" s="273"/>
-      <c r="L9" s="273"/>
-      <c r="M9" s="273"/>
-      <c r="N9" s="274"/>
+      <c r="D9" s="286"/>
+      <c r="E9" s="286"/>
+      <c r="F9" s="286"/>
+      <c r="G9" s="286"/>
+      <c r="H9" s="286"/>
+      <c r="I9" s="286"/>
+      <c r="J9" s="286"/>
+      <c r="K9" s="286"/>
+      <c r="L9" s="286"/>
+      <c r="M9" s="286"/>
+      <c r="N9" s="287"/>
       <c r="P9" s="86"/>
     </row>
-    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="275"/>
-      <c r="D10" s="276"/>
-      <c r="E10" s="276"/>
-      <c r="F10" s="276"/>
-      <c r="G10" s="276"/>
-      <c r="H10" s="276"/>
-      <c r="I10" s="276"/>
-      <c r="J10" s="276"/>
-      <c r="K10" s="276"/>
-      <c r="L10" s="276"/>
-      <c r="M10" s="276"/>
-      <c r="N10" s="277"/>
+      <c r="C10" s="288"/>
+      <c r="D10" s="289"/>
+      <c r="E10" s="289"/>
+      <c r="F10" s="289"/>
+      <c r="G10" s="289"/>
+      <c r="H10" s="289"/>
+      <c r="I10" s="289"/>
+      <c r="J10" s="289"/>
+      <c r="K10" s="289"/>
+      <c r="L10" s="289"/>
+      <c r="M10" s="289"/>
+      <c r="N10" s="290"/>
       <c r="P10" s="86"/>
     </row>
-    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="250" t="s">
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="263" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="278" t="s">
+      <c r="B11" s="291" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="250" t="s">
+      <c r="C11" s="263" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="280" t="s">
+      <c r="D11" s="293" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="280" t="s">
+      <c r="E11" s="293" t="s">
         <v>273</v>
       </c>
-      <c r="F11" s="250" t="s">
+      <c r="F11" s="263" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="250" t="s">
+      <c r="G11" s="263" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="250" t="s">
+      <c r="H11" s="263" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="256" t="s">
+      <c r="I11" s="269" t="s">
         <v>15</v>
       </c>
-      <c r="J11" s="258" t="s">
+      <c r="J11" s="271" t="s">
         <v>16</v>
       </c>
-      <c r="K11" s="258" t="s">
+      <c r="K11" s="271" t="s">
         <v>18</v>
       </c>
-      <c r="L11" s="261" t="s">
+      <c r="L11" s="274" t="s">
         <v>42</v>
       </c>
-      <c r="M11" s="258" t="s">
+      <c r="M11" s="271" t="s">
         <v>284</v>
       </c>
-      <c r="N11" s="258" t="s">
+      <c r="N11" s="271" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="251"/>
-      <c r="B12" s="279"/>
-      <c r="C12" s="251"/>
-      <c r="D12" s="281"/>
-      <c r="E12" s="281"/>
-      <c r="F12" s="251"/>
-      <c r="G12" s="251"/>
-      <c r="H12" s="251"/>
-      <c r="I12" s="257"/>
-      <c r="J12" s="259"/>
-      <c r="K12" s="259"/>
-      <c r="L12" s="262"/>
-      <c r="M12" s="259"/>
-      <c r="N12" s="259"/>
-    </row>
-    <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="251"/>
-      <c r="B13" s="279"/>
-      <c r="C13" s="251"/>
-      <c r="D13" s="281"/>
-      <c r="E13" s="281"/>
-      <c r="F13" s="251"/>
-      <c r="G13" s="251"/>
-      <c r="H13" s="251"/>
-      <c r="I13" s="257"/>
-      <c r="J13" s="259"/>
-      <c r="K13" s="260"/>
-      <c r="L13" s="262"/>
+    <row r="12" spans="1:18" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="264"/>
+      <c r="B12" s="292"/>
+      <c r="C12" s="264"/>
+      <c r="D12" s="294"/>
+      <c r="E12" s="294"/>
+      <c r="F12" s="264"/>
+      <c r="G12" s="264"/>
+      <c r="H12" s="264"/>
+      <c r="I12" s="270"/>
+      <c r="J12" s="272"/>
+      <c r="K12" s="272"/>
+      <c r="L12" s="275"/>
+      <c r="M12" s="272"/>
+      <c r="N12" s="272"/>
+    </row>
+    <row r="13" spans="1:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="264"/>
+      <c r="B13" s="292"/>
+      <c r="C13" s="264"/>
+      <c r="D13" s="294"/>
+      <c r="E13" s="294"/>
+      <c r="F13" s="264"/>
+      <c r="G13" s="264"/>
+      <c r="H13" s="264"/>
+      <c r="I13" s="270"/>
+      <c r="J13" s="272"/>
+      <c r="K13" s="273"/>
+      <c r="L13" s="275"/>
       <c r="M13" s="140" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 15/12</v>
@@ -5918,7 +5980,7 @@
         <v>VTO 15/12</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>120</v>
       </c>
@@ -5951,7 +6013,7 @@
       <c r="K14" s="157">
         <v>131452.15118400002</v>
       </c>
-      <c r="L14" s="189">
+      <c r="L14" s="184">
         <v>0</v>
       </c>
       <c r="M14" s="158">
@@ -5963,12 +6025,12 @@
         <v>139339.28025504001</v>
       </c>
       <c r="O14" s="121"/>
-      <c r="Q14" s="249" t="s">
+      <c r="Q14" s="262" t="s">
         <v>258</v>
       </c>
-      <c r="R14" s="249"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R14" s="262"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="35" t="s">
@@ -5998,7 +6060,7 @@
       <c r="K15" s="157">
         <v>155795.14214400001</v>
       </c>
-      <c r="L15" s="189">
+      <c r="L15" s="184">
         <v>0</v>
       </c>
       <c r="M15" s="158">
@@ -6010,10 +6072,10 @@
         <v>150267.97667264001</v>
       </c>
       <c r="O15" s="121"/>
-      <c r="Q15" s="249"/>
-      <c r="R15" s="249"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q15" s="262"/>
+      <c r="R15" s="262"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>120</v>
       </c>
@@ -6045,7 +6107,7 @@
       <c r="K16" s="157">
         <v>147275.09530799999</v>
       </c>
-      <c r="L16" s="189">
+      <c r="L16" s="184">
         <v>0</v>
       </c>
       <c r="M16" s="158">
@@ -6065,7 +6127,7 @@
         <v>151756.15118400005</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>120</v>
       </c>
@@ -6094,7 +6156,7 @@
       <c r="K17" s="157">
         <v>181355.28265200002</v>
       </c>
-      <c r="L17" s="189">
+      <c r="L17" s="184">
         <v>0</v>
       </c>
       <c r="M17" s="158">
@@ -6114,7 +6176,7 @@
         <v>179859.14214400004</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>120</v>
       </c>
@@ -6132,7 +6194,7 @@
       <c r="G18" s="163">
         <v>200908</v>
       </c>
-      <c r="H18" s="231">
+      <c r="H18" s="225">
         <f t="shared" si="3"/>
         <v>200908</v>
       </c>
@@ -6146,7 +6208,7 @@
       <c r="K18" s="165">
         <v>211784.02135200001</v>
       </c>
-      <c r="L18" s="189">
+      <c r="L18" s="184">
         <v>0</v>
       </c>
       <c r="M18" s="166">
@@ -6166,48 +6228,48 @@
         <v>170023.09530800002</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="57" t="s">
         <v>122</v>
       </c>
       <c r="B19" s="6"/>
-      <c r="C19" s="168" t="s">
+      <c r="C19" s="242" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="143" t="s">
+      <c r="D19" s="243" t="s">
         <v>179</v>
       </c>
-      <c r="E19" s="143"/>
-      <c r="F19" s="146">
+      <c r="E19" s="243"/>
+      <c r="F19" s="244">
         <v>1.8800000000000001E-2</v>
       </c>
-      <c r="G19" s="169">
+      <c r="G19" s="245">
         <v>225600.01</v>
       </c>
-      <c r="H19" s="232">
+      <c r="H19" s="246">
         <f t="shared" si="3"/>
         <v>225600.01</v>
       </c>
-      <c r="I19" s="170">
+      <c r="I19" s="247">
         <f>G19-H19</f>
         <v>0</v>
       </c>
-      <c r="J19" s="171">
+      <c r="J19" s="248">
         <f t="shared" ref="J19:J50" si="4">M$8*F19</f>
         <v>0</v>
       </c>
-      <c r="K19" s="171">
+      <c r="K19" s="248">
         <f>M$2*F19</f>
         <v>272600</v>
       </c>
-      <c r="L19" s="189">
-        <v>0</v>
-      </c>
-      <c r="M19" s="172">
+      <c r="L19" s="237">
+        <v>0</v>
+      </c>
+      <c r="M19" s="249">
         <f>ROUND((K19+J19+I19+L19),0) + O19</f>
         <v>272600.01</v>
       </c>
-      <c r="N19" s="172">
+      <c r="N19" s="249">
         <f>ROUND((M19*6% + M19 ),0) + O19</f>
         <v>288956.01</v>
       </c>
@@ -6222,7 +6284,7 @@
         <v>209367.28265200002</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="57" t="s">
         <v>123</v>
       </c>
@@ -6256,7 +6318,7 @@
         <f t="shared" ref="K20:K50" si="5">M$2*F20</f>
         <v>121799.99999999999</v>
       </c>
-      <c r="L20" s="189">
+      <c r="L20" s="184">
         <v>0</v>
       </c>
       <c r="M20" s="159">
@@ -6279,7 +6341,7 @@
         <v>244496.02135200001</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="57" t="s">
         <v>122</v>
       </c>
@@ -6313,7 +6375,7 @@
         <f t="shared" si="5"/>
         <v>291450</v>
       </c>
-      <c r="L21" s="189">
+      <c r="L21" s="184">
         <v>0</v>
       </c>
       <c r="M21" s="159">
@@ -6329,49 +6391,49 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="57" t="s">
         <v>124</v>
       </c>
       <c r="B22" s="6"/>
-      <c r="C22" s="191" t="s">
+      <c r="C22" s="186" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="192" t="s">
+      <c r="D22" s="187" t="s">
         <v>182</v>
       </c>
-      <c r="E22" s="193" t="s">
+      <c r="E22" s="188" t="s">
         <v>303</v>
       </c>
-      <c r="F22" s="194">
+      <c r="F22" s="189">
         <v>9.4000000000000004E-3</v>
       </c>
-      <c r="G22" s="195">
+      <c r="G22" s="190">
         <v>277972.03999999998</v>
       </c>
-      <c r="H22" s="233">
+      <c r="H22" s="226">
         <v>112800</v>
       </c>
-      <c r="I22" s="196">
+      <c r="I22" s="191">
         <f t="shared" si="0"/>
         <v>165172.03999999998</v>
       </c>
-      <c r="J22" s="197">
+      <c r="J22" s="192">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K22" s="197">
+      <c r="K22" s="192">
         <f t="shared" si="5"/>
         <v>136300</v>
       </c>
-      <c r="L22" s="198">
-        <v>0</v>
-      </c>
-      <c r="M22" s="199">
+      <c r="L22" s="193">
+        <v>0</v>
+      </c>
+      <c r="M22" s="194">
         <f t="shared" si="7"/>
         <v>301472.03999999998</v>
       </c>
-      <c r="N22" s="199">
+      <c r="N22" s="194">
         <f t="shared" si="6"/>
         <v>319560.03999999998</v>
       </c>
@@ -6383,50 +6445,50 @@
         <v>327</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="57" t="s">
         <v>124</v>
       </c>
       <c r="B23" s="6"/>
-      <c r="C23" s="35" t="s">
+      <c r="C23" s="301" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="114" t="s">
+      <c r="D23" s="302" t="s">
         <v>183</v>
       </c>
-      <c r="E23" s="143" t="s">
+      <c r="E23" s="303" t="s">
         <v>324</v>
       </c>
-      <c r="F23" s="146">
+      <c r="F23" s="304">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G23" s="147">
+      <c r="G23" s="305">
         <v>191400.05</v>
       </c>
-      <c r="H23" s="44">
+      <c r="H23" s="306">
         <f>104400.05</f>
         <v>104400.05</v>
       </c>
-      <c r="I23" s="156">
+      <c r="I23" s="307">
         <f t="shared" si="0"/>
         <v>86999.999999999985</v>
       </c>
-      <c r="J23" s="157">
+      <c r="J23" s="308">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K23" s="157">
+      <c r="K23" s="308">
         <f t="shared" si="5"/>
         <v>126149.99999999999</v>
       </c>
-      <c r="L23" s="189">
-        <v>0</v>
-      </c>
-      <c r="M23" s="159">
+      <c r="L23" s="309">
+        <v>0</v>
+      </c>
+      <c r="M23" s="310">
         <f t="shared" si="7"/>
         <v>213150.05</v>
       </c>
-      <c r="N23" s="159">
+      <c r="N23" s="310">
         <f t="shared" si="6"/>
         <v>225939.05</v>
       </c>
@@ -6435,7 +6497,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="57" t="s">
         <v>124</v>
       </c>
@@ -6471,7 +6533,7 @@
         <f t="shared" si="5"/>
         <v>137750</v>
       </c>
-      <c r="L24" s="189">
+      <c r="L24" s="184">
         <v>0</v>
       </c>
       <c r="M24" s="159">
@@ -6487,49 +6549,49 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="57" t="s">
         <v>122</v>
       </c>
       <c r="B25" s="6"/>
-      <c r="C25" s="191" t="s">
+      <c r="C25" s="230" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="192" t="s">
+      <c r="D25" s="231" t="s">
         <v>184</v>
       </c>
-      <c r="E25" s="193" t="s">
-        <v>354</v>
-      </c>
-      <c r="F25" s="194">
+      <c r="E25" s="243" t="s">
+        <v>353</v>
+      </c>
+      <c r="F25" s="244">
         <v>1.6500000000000001E-2</v>
       </c>
-      <c r="G25" s="195">
+      <c r="G25" s="233">
         <v>325977.07</v>
       </c>
-      <c r="H25" s="233">
+      <c r="H25" s="234">
         <v>198000</v>
       </c>
-      <c r="I25" s="196">
+      <c r="I25" s="235">
         <f t="shared" si="0"/>
         <v>127977.07</v>
       </c>
-      <c r="J25" s="197">
+      <c r="J25" s="236">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K25" s="197">
+      <c r="K25" s="236">
         <f t="shared" si="5"/>
         <v>239250</v>
       </c>
-      <c r="L25" s="198">
-        <v>0</v>
-      </c>
-      <c r="M25" s="199">
+      <c r="L25" s="237">
+        <v>0</v>
+      </c>
+      <c r="M25" s="238">
         <f t="shared" si="7"/>
         <v>367227.07</v>
       </c>
-      <c r="N25" s="199">
+      <c r="N25" s="238">
         <f t="shared" si="6"/>
         <v>389261.07</v>
       </c>
@@ -6538,7 +6600,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="57" t="s">
         <v>123</v>
       </c>
@@ -6572,7 +6634,7 @@
         <f t="shared" si="5"/>
         <v>105850</v>
       </c>
-      <c r="L26" s="189">
+      <c r="L26" s="184">
         <f>24000+20000</f>
         <v>44000</v>
       </c>
@@ -6589,45 +6651,45 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="114" t="s">
         <v>122</v>
       </c>
       <c r="B27" s="35"/>
-      <c r="C27" s="35" t="s">
+      <c r="C27" s="230" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="114" t="s">
+      <c r="D27" s="231" t="s">
         <v>184</v>
       </c>
-      <c r="E27" s="143"/>
-      <c r="F27" s="146">
+      <c r="E27" s="243"/>
+      <c r="F27" s="244">
         <v>1.78E-2</v>
       </c>
-      <c r="G27" s="147">
+      <c r="G27" s="233">
         <v>728372.09</v>
       </c>
-      <c r="H27" s="44"/>
-      <c r="I27" s="156">
+      <c r="H27" s="234"/>
+      <c r="I27" s="235">
         <f t="shared" si="0"/>
         <v>728372.09</v>
       </c>
-      <c r="J27" s="157">
+      <c r="J27" s="236">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K27" s="157">
+      <c r="K27" s="236">
         <f t="shared" si="5"/>
         <v>258100</v>
       </c>
-      <c r="L27" s="189">
-        <v>0</v>
-      </c>
-      <c r="M27" s="159">
+      <c r="L27" s="237">
+        <v>0</v>
+      </c>
+      <c r="M27" s="238">
         <f t="shared" si="7"/>
         <v>986472.09</v>
       </c>
-      <c r="N27" s="159">
+      <c r="N27" s="238">
         <f t="shared" si="6"/>
         <v>1045660.09</v>
       </c>
@@ -6636,7 +6698,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="114" t="s">
         <v>124</v>
       </c>
@@ -6667,7 +6729,7 @@
         <f t="shared" si="5"/>
         <v>136300</v>
       </c>
-      <c r="L28" s="189">
+      <c r="L28" s="184">
         <v>0</v>
       </c>
       <c r="M28" s="159">
@@ -6683,7 +6745,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="114" t="s">
         <v>124</v>
       </c>
@@ -6717,7 +6779,7 @@
         <f t="shared" si="5"/>
         <v>126149.99999999999</v>
       </c>
-      <c r="L29" s="189">
+      <c r="L29" s="184">
         <v>0</v>
       </c>
       <c r="M29" s="159">
@@ -6733,7 +6795,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="114" t="s">
         <v>124</v>
       </c>
@@ -6764,7 +6826,7 @@
         <f t="shared" si="5"/>
         <v>137750</v>
       </c>
-      <c r="L30" s="189">
+      <c r="L30" s="184">
         <v>0</v>
       </c>
       <c r="M30" s="159">
@@ -6780,7 +6842,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="114" t="s">
         <v>122</v>
       </c>
@@ -6814,7 +6876,7 @@
         <f t="shared" si="5"/>
         <v>237800.00000000003</v>
       </c>
-      <c r="L31" s="189">
+      <c r="L31" s="184">
         <v>0</v>
       </c>
       <c r="M31" s="159">
@@ -6830,7 +6892,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="57" t="s">
         <v>123</v>
       </c>
@@ -6866,7 +6928,7 @@
         <f t="shared" si="5"/>
         <v>104400</v>
       </c>
-      <c r="L32" s="189">
+      <c r="L32" s="184">
         <v>0</v>
       </c>
       <c r="M32" s="159">
@@ -6882,7 +6944,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A33" s="57" t="s">
         <v>122</v>
       </c>
@@ -6904,7 +6966,7 @@
         <f>G33</f>
         <v>207600.15</v>
       </c>
-      <c r="I33" s="173">
+      <c r="I33" s="168">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6916,7 +6978,7 @@
         <f t="shared" si="5"/>
         <v>250850</v>
       </c>
-      <c r="L33" s="189">
+      <c r="L33" s="184">
         <v>0</v>
       </c>
       <c r="M33" s="159">
@@ -6932,7 +6994,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A34" s="149" t="s">
         <v>124</v>
       </c>
@@ -6965,7 +7027,7 @@
         <f t="shared" si="5"/>
         <v>136300</v>
       </c>
-      <c r="L34" s="189">
+      <c r="L34" s="184">
         <v>0</v>
       </c>
       <c r="M34" s="159">
@@ -6981,7 +7043,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="35" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A35" s="57" t="s">
         <v>124</v>
       </c>
@@ -7016,7 +7078,7 @@
         <f t="shared" si="5"/>
         <v>126149.99999999999</v>
       </c>
-      <c r="L35" s="189">
+      <c r="L35" s="184">
         <v>0</v>
       </c>
       <c r="M35" s="159">
@@ -7032,7 +7094,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A36" s="57" t="s">
         <v>124</v>
       </c>
@@ -7051,7 +7113,7 @@
         <v>209000.18</v>
       </c>
       <c r="H36" s="44"/>
-      <c r="I36" s="173">
+      <c r="I36" s="168">
         <f t="shared" si="0"/>
         <v>209000.18</v>
       </c>
@@ -7063,7 +7125,7 @@
         <f t="shared" si="5"/>
         <v>137750</v>
       </c>
-      <c r="L36" s="189">
+      <c r="L36" s="184">
         <v>0</v>
       </c>
       <c r="M36" s="159">
@@ -7079,7 +7141,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A37" s="57" t="s">
         <v>122</v>
       </c>
@@ -7115,7 +7177,7 @@
         <f t="shared" si="5"/>
         <v>237800.00000000003</v>
       </c>
-      <c r="L37" s="189">
+      <c r="L37" s="184">
         <v>20000</v>
       </c>
       <c r="M37" s="159">
@@ -7131,7 +7193,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A38" s="57" t="s">
         <v>123</v>
       </c>
@@ -7165,7 +7227,7 @@
         <f t="shared" si="5"/>
         <v>104400</v>
       </c>
-      <c r="L38" s="189">
+      <c r="L38" s="184">
         <v>0</v>
       </c>
       <c r="M38" s="159">
@@ -7181,7 +7243,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="114" t="s">
         <v>122</v>
       </c>
@@ -7215,7 +7277,7 @@
         <f t="shared" si="5"/>
         <v>250850</v>
       </c>
-      <c r="L39" s="189">
+      <c r="L39" s="184">
         <v>0</v>
       </c>
       <c r="M39" s="159">
@@ -7226,7 +7288,7 @@
         <f t="shared" si="6"/>
         <v>265901.21000000002</v>
       </c>
-      <c r="O39" s="211">
+      <c r="O39" s="206">
         <f t="shared" si="8"/>
         <v>0.21000000000000005</v>
       </c>
@@ -7329,7 +7391,7 @@
       <c r="DH39" s="74"/>
       <c r="DI39" s="74"/>
     </row>
-    <row r="40" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="114" t="s">
         <v>124</v>
       </c>
@@ -7360,7 +7422,7 @@
         <f t="shared" si="5"/>
         <v>136300</v>
       </c>
-      <c r="L40" s="189">
+      <c r="L40" s="184">
         <v>0</v>
       </c>
       <c r="M40" s="159">
@@ -7371,7 +7433,7 @@
         <f t="shared" si="6"/>
         <v>363686.22</v>
       </c>
-      <c r="O40" s="211">
+      <c r="O40" s="206">
         <f t="shared" si="8"/>
         <v>0.22000000000000006</v>
       </c>
@@ -7474,7 +7536,7 @@
       <c r="DH40" s="74"/>
       <c r="DI40" s="74"/>
     </row>
-    <row r="41" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="114" t="s">
         <v>124</v>
       </c>
@@ -7508,7 +7570,7 @@
         <f t="shared" si="5"/>
         <v>126149.99999999999</v>
       </c>
-      <c r="L41" s="189">
+      <c r="L41" s="184">
         <v>0</v>
       </c>
       <c r="M41" s="159">
@@ -7519,7 +7581,7 @@
         <f t="shared" si="6"/>
         <v>133719.23000000001</v>
       </c>
-      <c r="O41" s="211">
+      <c r="O41" s="206">
         <f t="shared" si="8"/>
         <v>0.23000000000000007</v>
       </c>
@@ -7624,7 +7686,7 @@
       <c r="DH41" s="74"/>
       <c r="DI41" s="74"/>
     </row>
-    <row r="42" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:113" s="150" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="114" t="s">
         <v>124</v>
       </c>
@@ -7639,7 +7701,7 @@
       <c r="F42" s="146">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G42" s="174">
+      <c r="G42" s="169">
         <v>209000.24</v>
       </c>
       <c r="H42" s="44"/>
@@ -7655,7 +7717,7 @@
         <f t="shared" si="5"/>
         <v>137750</v>
       </c>
-      <c r="L42" s="189">
+      <c r="L42" s="184">
         <v>0</v>
       </c>
       <c r="M42" s="159">
@@ -7666,7 +7728,7 @@
         <f t="shared" si="6"/>
         <v>367555.24</v>
       </c>
-      <c r="O42" s="211">
+      <c r="O42" s="206">
         <f t="shared" si="8"/>
         <v>0.24000000000000007</v>
       </c>
@@ -7769,7 +7831,7 @@
       <c r="DH42" s="74"/>
       <c r="DI42" s="74"/>
     </row>
-    <row r="43" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A43" s="57" t="s">
         <v>122</v>
       </c>
@@ -7803,7 +7865,7 @@
         <f t="shared" si="5"/>
         <v>237800.00000000003</v>
       </c>
-      <c r="L43" s="189">
+      <c r="L43" s="184">
         <v>0</v>
       </c>
       <c r="M43" s="159">
@@ -7819,7 +7881,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A44" s="57" t="s">
         <v>123</v>
       </c>
@@ -7855,7 +7917,7 @@
         <f t="shared" si="5"/>
         <v>104400</v>
       </c>
-      <c r="L44" s="189">
+      <c r="L44" s="184">
         <v>0</v>
       </c>
       <c r="M44" s="159">
@@ -7871,7 +7933,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A45" s="57" t="s">
         <v>122</v>
       </c>
@@ -7905,7 +7967,7 @@
         <f t="shared" si="5"/>
         <v>250850</v>
       </c>
-      <c r="L45" s="189">
+      <c r="L45" s="184">
         <v>0</v>
       </c>
       <c r="M45" s="159">
@@ -7927,7 +7989,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="46" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A46" s="57" t="s">
         <v>124</v>
       </c>
@@ -7961,7 +8023,7 @@
         <f t="shared" si="5"/>
         <v>136300</v>
       </c>
-      <c r="L46" s="189">
+      <c r="L46" s="184">
         <v>0</v>
       </c>
       <c r="M46" s="159">
@@ -7980,7 +8042,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="47" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A47" s="57" t="s">
         <v>124</v>
       </c>
@@ -8013,7 +8075,7 @@
         <f t="shared" si="5"/>
         <v>126149.99999999999</v>
       </c>
-      <c r="L47" s="189">
+      <c r="L47" s="184">
         <v>0</v>
       </c>
       <c r="M47" s="159">
@@ -8029,7 +8091,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:113" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:113" x14ac:dyDescent="0.3">
       <c r="A48" s="57" t="s">
         <v>124</v>
       </c>
@@ -8063,7 +8125,7 @@
         <f t="shared" si="5"/>
         <v>137750</v>
       </c>
-      <c r="L48" s="189">
+      <c r="L48" s="184">
         <v>0</v>
       </c>
       <c r="M48" s="159">
@@ -8079,7 +8141,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" s="57" t="s">
         <v>122</v>
       </c>
@@ -8113,7 +8175,7 @@
         <f t="shared" si="5"/>
         <v>237800.00000000003</v>
       </c>
-      <c r="L49" s="189">
+      <c r="L49" s="184">
         <v>0</v>
       </c>
       <c r="M49" s="159">
@@ -8129,7 +8191,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" s="57" t="s">
         <v>123</v>
       </c>
@@ -8160,7 +8222,7 @@
         <f t="shared" si="5"/>
         <v>104400</v>
       </c>
-      <c r="L50" s="189">
+      <c r="L50" s="184">
         <v>20000</v>
       </c>
       <c r="M50" s="159">
@@ -8177,7 +8239,7 @@
       </c>
       <c r="P50" s="43"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" s="57" t="s">
         <v>122</v>
       </c>
@@ -8211,7 +8273,7 @@
         <f t="shared" ref="K51:K82" si="12">M$2*F51</f>
         <v>250850</v>
       </c>
-      <c r="L51" s="189">
+      <c r="L51" s="184">
         <v>0</v>
       </c>
       <c r="M51" s="159">
@@ -8228,7 +8290,7 @@
       </c>
       <c r="P51" s="43"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" s="57" t="s">
         <v>124</v>
       </c>
@@ -8262,7 +8324,7 @@
         <f t="shared" si="12"/>
         <v>136300</v>
       </c>
-      <c r="L52" s="189">
+      <c r="L52" s="184">
         <v>20000</v>
       </c>
       <c r="M52" s="159">
@@ -8281,7 +8343,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" s="57" t="s">
         <v>124</v>
       </c>
@@ -8315,7 +8377,7 @@
         <f t="shared" si="12"/>
         <v>126149.99999999999</v>
       </c>
-      <c r="L53" s="189">
+      <c r="L53" s="184">
         <v>0</v>
       </c>
       <c r="M53" s="159">
@@ -8331,7 +8393,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" s="57" t="s">
         <v>124</v>
       </c>
@@ -8362,7 +8424,7 @@
         <f t="shared" si="12"/>
         <v>137750</v>
       </c>
-      <c r="L54" s="189">
+      <c r="L54" s="184">
         <v>0</v>
       </c>
       <c r="M54" s="159">
@@ -8378,7 +8440,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" s="57" t="s">
         <v>122</v>
       </c>
@@ -8412,7 +8474,7 @@
         <f t="shared" si="12"/>
         <v>237800.00000000003</v>
       </c>
-      <c r="L55" s="189">
+      <c r="L55" s="184">
         <v>0</v>
       </c>
       <c r="M55" s="159">
@@ -8429,7 +8491,7 @@
       </c>
       <c r="Q55" s="59"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" s="57" t="s">
         <v>123</v>
       </c>
@@ -8465,7 +8527,7 @@
         <f t="shared" si="12"/>
         <v>104400</v>
       </c>
-      <c r="L56" s="189">
+      <c r="L56" s="184">
         <v>0</v>
       </c>
       <c r="M56" s="159">
@@ -8481,7 +8543,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" s="57" t="s">
         <v>122</v>
       </c>
@@ -8515,7 +8577,7 @@
         <f t="shared" si="12"/>
         <v>250850</v>
       </c>
-      <c r="L57" s="189">
+      <c r="L57" s="184">
         <v>0</v>
       </c>
       <c r="M57" s="159">
@@ -8531,7 +8593,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" s="57" t="s">
         <v>124</v>
       </c>
@@ -8565,7 +8627,7 @@
         <f t="shared" si="12"/>
         <v>136300</v>
       </c>
-      <c r="L58" s="189">
+      <c r="L58" s="184">
         <v>0</v>
       </c>
       <c r="M58" s="159">
@@ -8581,48 +8643,48 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" s="114" t="s">
         <v>124</v>
       </c>
       <c r="B59" s="35"/>
-      <c r="C59" s="201" t="s">
+      <c r="C59" s="196" t="s">
         <v>86</v>
       </c>
-      <c r="D59" s="202" t="s">
+      <c r="D59" s="197" t="s">
         <v>121</v>
       </c>
-      <c r="E59" s="203"/>
-      <c r="F59" s="204">
+      <c r="E59" s="198"/>
+      <c r="F59" s="199">
         <v>8.6999999999999994E-3</v>
       </c>
-      <c r="G59" s="205">
+      <c r="G59" s="200">
         <v>104400.41</v>
       </c>
-      <c r="H59" s="210">
+      <c r="H59" s="205">
         <f>G59</f>
         <v>104400.41</v>
       </c>
-      <c r="I59" s="206">
+      <c r="I59" s="201">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J59" s="207">
+      <c r="J59" s="202">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="K59" s="207">
+      <c r="K59" s="202">
         <f t="shared" si="12"/>
         <v>126149.99999999999</v>
       </c>
-      <c r="L59" s="208">
-        <v>0</v>
-      </c>
-      <c r="M59" s="209">
+      <c r="L59" s="203">
+        <v>0</v>
+      </c>
+      <c r="M59" s="204">
         <f t="shared" si="7"/>
         <v>126150.41</v>
       </c>
-      <c r="N59" s="209">
+      <c r="N59" s="204">
         <f t="shared" si="6"/>
         <v>133719.41</v>
       </c>
@@ -8634,7 +8696,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" s="114" t="s">
         <v>124</v>
       </c>
@@ -8668,7 +8730,7 @@
         <f t="shared" si="12"/>
         <v>137750</v>
       </c>
-      <c r="L60" s="189">
+      <c r="L60" s="184">
         <v>20000</v>
       </c>
       <c r="M60" s="159">
@@ -8687,7 +8749,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" s="114" t="s">
         <v>122</v>
       </c>
@@ -8721,7 +8783,7 @@
         <f t="shared" si="12"/>
         <v>237800.00000000003</v>
       </c>
-      <c r="L61" s="189">
+      <c r="L61" s="184">
         <v>0</v>
       </c>
       <c r="M61" s="159">
@@ -8737,7 +8799,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" s="114" t="s">
         <v>123</v>
       </c>
@@ -8771,7 +8833,7 @@
         <f t="shared" si="12"/>
         <v>104400</v>
       </c>
-      <c r="L62" s="189">
+      <c r="L62" s="184">
         <v>0</v>
       </c>
       <c r="M62" s="159">
@@ -8787,7 +8849,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" s="57" t="s">
         <v>122</v>
       </c>
@@ -8821,7 +8883,7 @@
         <f t="shared" si="12"/>
         <v>250850</v>
       </c>
-      <c r="L63" s="189">
+      <c r="L63" s="184">
         <v>0</v>
       </c>
       <c r="M63" s="159">
@@ -8837,7 +8899,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" s="57" t="s">
         <v>124</v>
       </c>
@@ -8873,7 +8935,7 @@
         <f t="shared" si="12"/>
         <v>136300</v>
       </c>
-      <c r="L64" s="189">
+      <c r="L64" s="184">
         <v>0</v>
       </c>
       <c r="M64" s="159">
@@ -8884,12 +8946,12 @@
         <f t="shared" si="6"/>
         <v>144478.46</v>
       </c>
-      <c r="O64" s="211">
+      <c r="O64" s="206">
         <f t="shared" si="8"/>
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="57" t="s">
         <v>124</v>
       </c>
@@ -8923,7 +8985,7 @@
         <f t="shared" si="12"/>
         <v>126149.99999999999</v>
       </c>
-      <c r="L65" s="189">
+      <c r="L65" s="184">
         <v>0</v>
       </c>
       <c r="M65" s="159">
@@ -8934,12 +8996,12 @@
         <f t="shared" si="6"/>
         <v>133719.47</v>
       </c>
-      <c r="O65" s="211">
+      <c r="O65" s="206">
         <f t="shared" si="8"/>
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="57" t="s">
         <v>124</v>
       </c>
@@ -8973,7 +9035,7 @@
         <f t="shared" si="12"/>
         <v>137750</v>
       </c>
-      <c r="L66" s="189">
+      <c r="L66" s="184">
         <v>0</v>
       </c>
       <c r="M66" s="159">
@@ -8984,13 +9046,13 @@
         <f t="shared" si="6"/>
         <v>166156.48000000001</v>
       </c>
-      <c r="O66" s="211">
+      <c r="O66" s="206">
         <f t="shared" si="8"/>
         <v>0.48000000000000026</v>
       </c>
-      <c r="R66" s="236"/>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R66" s="229"/>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="57" t="s">
         <v>122</v>
       </c>
@@ -9024,7 +9086,7 @@
         <f t="shared" si="12"/>
         <v>237800.00000000003</v>
       </c>
-      <c r="L67" s="189">
+      <c r="L67" s="184">
         <v>0</v>
       </c>
       <c r="M67" s="159">
@@ -9041,7 +9103,7 @@
       </c>
       <c r="R67" s="43"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="149" t="s">
         <v>123</v>
       </c>
@@ -9072,7 +9134,7 @@
         <f t="shared" si="12"/>
         <v>104400</v>
       </c>
-      <c r="L68" s="189">
+      <c r="L68" s="184">
         <v>0</v>
       </c>
       <c r="M68" s="159">
@@ -9088,7 +9150,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="57" t="s">
         <v>122</v>
       </c>
@@ -9119,7 +9181,7 @@
         <f t="shared" si="12"/>
         <v>250850</v>
       </c>
-      <c r="L69" s="189">
+      <c r="L69" s="184">
         <v>0</v>
       </c>
       <c r="M69" s="159">
@@ -9135,7 +9197,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="57" t="s">
         <v>124</v>
       </c>
@@ -9166,7 +9228,7 @@
         <f t="shared" si="12"/>
         <v>136300</v>
       </c>
-      <c r="L70" s="189">
+      <c r="L70" s="184">
         <v>0</v>
       </c>
       <c r="M70" s="159">
@@ -9182,7 +9244,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" s="57" t="s">
         <v>124</v>
       </c>
@@ -9216,7 +9278,7 @@
         <f t="shared" si="12"/>
         <v>126149.99999999999</v>
       </c>
-      <c r="L71" s="189">
+      <c r="L71" s="184">
         <v>0</v>
       </c>
       <c r="M71" s="159">
@@ -9235,7 +9297,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="57" t="s">
         <v>124</v>
       </c>
@@ -9269,7 +9331,7 @@
         <f t="shared" si="12"/>
         <v>137750</v>
       </c>
-      <c r="L72" s="189">
+      <c r="L72" s="184">
         <v>0</v>
       </c>
       <c r="M72" s="159">
@@ -9285,7 +9347,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" s="57" t="s">
         <v>125</v>
       </c>
@@ -9319,7 +9381,7 @@
         <f t="shared" si="12"/>
         <v>340750</v>
       </c>
-      <c r="L73" s="189">
+      <c r="L73" s="184">
         <v>0</v>
       </c>
       <c r="M73" s="159">
@@ -9334,11 +9396,11 @@
         <f t="shared" si="8"/>
         <v>0.55000000000000027</v>
       </c>
-      <c r="P73" s="213" t="s">
+      <c r="P73" s="208" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="57" t="s">
         <v>122</v>
       </c>
@@ -9372,7 +9434,7 @@
         <f t="shared" si="12"/>
         <v>250850</v>
       </c>
-      <c r="L74" s="189">
+      <c r="L74" s="184">
         <v>0</v>
       </c>
       <c r="M74" s="159">
@@ -9388,7 +9450,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="57" t="s">
         <v>124</v>
       </c>
@@ -9422,7 +9484,7 @@
         <f t="shared" si="12"/>
         <v>136300</v>
       </c>
-      <c r="L75" s="189">
+      <c r="L75" s="184">
         <v>0</v>
       </c>
       <c r="M75" s="159">
@@ -9438,7 +9500,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="57" t="s">
         <v>124</v>
       </c>
@@ -9471,7 +9533,7 @@
         <f t="shared" si="12"/>
         <v>126149.99999999999</v>
       </c>
-      <c r="L76" s="189">
+      <c r="L76" s="184">
         <v>0</v>
       </c>
       <c r="M76" s="159">
@@ -9487,7 +9549,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="57" t="s">
         <v>124</v>
       </c>
@@ -9521,7 +9583,7 @@
         <f t="shared" si="12"/>
         <v>137750</v>
       </c>
-      <c r="L77" s="189">
+      <c r="L77" s="184">
         <v>0</v>
       </c>
       <c r="M77" s="159">
@@ -9537,7 +9599,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="57" t="s">
         <v>125</v>
       </c>
@@ -9571,7 +9633,7 @@
         <f t="shared" si="12"/>
         <v>340750</v>
       </c>
-      <c r="L78" s="189">
+      <c r="L78" s="184">
         <v>0</v>
       </c>
       <c r="M78" s="159">
@@ -9587,7 +9649,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="57" t="s">
         <v>122</v>
       </c>
@@ -9621,7 +9683,7 @@
         <f t="shared" si="12"/>
         <v>250850</v>
       </c>
-      <c r="L79" s="189">
+      <c r="L79" s="184">
         <v>0</v>
       </c>
       <c r="M79" s="159">
@@ -9637,7 +9699,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" s="57" t="s">
         <v>124</v>
       </c>
@@ -9670,7 +9732,7 @@
         <f t="shared" si="12"/>
         <v>136300</v>
       </c>
-      <c r="L80" s="189">
+      <c r="L80" s="184">
         <v>0</v>
       </c>
       <c r="M80" s="159">
@@ -9686,7 +9748,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A81" s="57" t="s">
         <v>124</v>
       </c>
@@ -9722,7 +9784,7 @@
         <f t="shared" si="12"/>
         <v>126149.99999999999</v>
       </c>
-      <c r="L81" s="189">
+      <c r="L81" s="184">
         <v>0</v>
       </c>
       <c r="M81" s="159">
@@ -9738,7 +9800,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="57" t="s">
         <v>124</v>
       </c>
@@ -9772,7 +9834,7 @@
         <f t="shared" si="12"/>
         <v>137750</v>
       </c>
-      <c r="L82" s="189">
+      <c r="L82" s="184">
         <v>0</v>
       </c>
       <c r="M82" s="159">
@@ -9791,7 +9853,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A83" s="57" t="s">
         <v>125</v>
       </c>
@@ -9825,7 +9887,7 @@
         <f t="shared" ref="K83:K114" si="17">M$2*F83</f>
         <v>340750</v>
       </c>
-      <c r="L83" s="189">
+      <c r="L83" s="184">
         <v>0</v>
       </c>
       <c r="M83" s="159">
@@ -9841,7 +9903,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="57" t="s">
         <v>122</v>
       </c>
@@ -9875,7 +9937,7 @@
         <f t="shared" si="17"/>
         <v>250850</v>
       </c>
-      <c r="L84" s="189">
+      <c r="L84" s="184">
         <v>0</v>
       </c>
       <c r="M84" s="159">
@@ -9891,7 +9953,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="57" t="s">
         <v>124</v>
       </c>
@@ -9925,7 +9987,7 @@
         <f t="shared" si="17"/>
         <v>136300</v>
       </c>
-      <c r="L85" s="189">
+      <c r="L85" s="184">
         <v>12000</v>
       </c>
       <c r="M85" s="159">
@@ -9941,7 +10003,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="57" t="s">
         <v>124</v>
       </c>
@@ -9975,7 +10037,7 @@
         <f t="shared" si="17"/>
         <v>126149.99999999999</v>
       </c>
-      <c r="L86" s="189">
+      <c r="L86" s="184">
         <v>0</v>
       </c>
       <c r="M86" s="159">
@@ -9991,7 +10053,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="114" t="s">
         <v>124</v>
       </c>
@@ -10025,7 +10087,7 @@
         <f t="shared" si="17"/>
         <v>137750</v>
       </c>
-      <c r="L87" s="189">
+      <c r="L87" s="184">
         <v>0</v>
       </c>
       <c r="M87" s="159">
@@ -10041,7 +10103,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="114"/>
       <c r="B88" s="35"/>
       <c r="C88" s="35" t="s">
@@ -10073,7 +10135,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L88" s="189">
+      <c r="L88" s="184">
         <v>0</v>
       </c>
       <c r="M88" s="159">
@@ -10089,7 +10151,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="114"/>
       <c r="B89" s="35"/>
       <c r="C89" s="35" t="s">
@@ -10121,7 +10183,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L89" s="189">
+      <c r="L89" s="184">
         <v>0</v>
       </c>
       <c r="M89" s="159">
@@ -10137,7 +10199,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="114"/>
       <c r="B90" s="35"/>
       <c r="C90" s="35" t="s">
@@ -10169,7 +10231,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L90" s="189">
+      <c r="L90" s="184">
         <v>0</v>
       </c>
       <c r="M90" s="159">
@@ -10185,7 +10247,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="114"/>
       <c r="B91" s="35"/>
       <c r="C91" s="35" t="s">
@@ -10217,7 +10279,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L91" s="189">
+      <c r="L91" s="184">
         <v>0</v>
       </c>
       <c r="M91" s="159">
@@ -10233,17 +10295,17 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="114"/>
       <c r="B92" s="35"/>
-      <c r="C92" s="224" t="s">
+      <c r="C92" s="218" t="s">
         <v>130</v>
       </c>
-      <c r="D92" s="225" t="s">
+      <c r="D92" s="219" t="s">
         <v>201</v>
       </c>
-      <c r="E92" s="225"/>
-      <c r="F92" s="226">
+      <c r="E92" s="219"/>
+      <c r="F92" s="220">
         <v>2.3E-3</v>
       </c>
       <c r="G92" s="44">
@@ -10253,26 +10315,26 @@
         <f t="shared" si="18"/>
         <v>27600.74</v>
       </c>
-      <c r="I92" s="227">
+      <c r="I92" s="221">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J92" s="228">
+      <c r="J92" s="222">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K92" s="228">
+      <c r="K92" s="222">
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L92" s="229">
-        <v>0</v>
-      </c>
-      <c r="M92" s="230">
+      <c r="L92" s="223">
+        <v>0</v>
+      </c>
+      <c r="M92" s="224">
         <f t="shared" si="19"/>
         <v>33350.74</v>
       </c>
-      <c r="N92" s="230">
+      <c r="N92" s="224">
         <f t="shared" si="20"/>
         <v>35352.74</v>
       </c>
@@ -10284,7 +10346,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="114"/>
       <c r="B93" s="35"/>
       <c r="C93" s="35" t="s">
@@ -10316,7 +10378,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L93" s="189">
+      <c r="L93" s="184">
         <v>0</v>
       </c>
       <c r="M93" s="159">
@@ -10332,7 +10394,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="114"/>
       <c r="B94" s="35"/>
       <c r="C94" s="35" t="s">
@@ -10364,7 +10426,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L94" s="189">
+      <c r="L94" s="184">
         <v>0</v>
       </c>
       <c r="M94" s="159">
@@ -10380,7 +10442,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="114"/>
       <c r="B95" s="35"/>
       <c r="C95" s="35" t="s">
@@ -10412,7 +10474,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L95" s="189">
+      <c r="L95" s="184">
         <v>0</v>
       </c>
       <c r="M95" s="159">
@@ -10428,7 +10490,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="114"/>
       <c r="B96" s="35"/>
       <c r="C96" s="35" t="s">
@@ -10460,7 +10522,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L96" s="189">
+      <c r="L96" s="184">
         <v>0</v>
       </c>
       <c r="M96" s="159">
@@ -10476,7 +10538,7 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="114"/>
       <c r="B97" s="35"/>
       <c r="C97" s="35" t="s">
@@ -10505,7 +10567,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L97" s="189">
+      <c r="L97" s="184">
         <v>0</v>
       </c>
       <c r="M97" s="159">
@@ -10521,7 +10583,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="114"/>
       <c r="B98" s="35"/>
       <c r="C98" s="35" t="s">
@@ -10553,7 +10615,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L98" s="189">
+      <c r="L98" s="184">
         <v>0</v>
       </c>
       <c r="M98" s="159">
@@ -10569,7 +10631,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="114"/>
       <c r="B99" s="35"/>
       <c r="C99" s="35" t="s">
@@ -10598,7 +10660,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L99" s="189">
+      <c r="L99" s="184">
         <v>0</v>
       </c>
       <c r="M99" s="8">
@@ -10614,7 +10676,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A100" s="114"/>
       <c r="B100" s="35"/>
       <c r="C100" s="35" t="s">
@@ -10646,7 +10708,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L100" s="189">
+      <c r="L100" s="184">
         <v>0</v>
       </c>
       <c r="M100" s="8">
@@ -10662,7 +10724,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="114"/>
       <c r="B101" s="35"/>
       <c r="C101" s="35" t="s">
@@ -10694,7 +10756,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L101" s="189">
+      <c r="L101" s="184">
         <v>0</v>
       </c>
       <c r="M101" s="8">
@@ -10710,7 +10772,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="114"/>
       <c r="B102" s="35"/>
       <c r="C102" s="35" t="s">
@@ -10742,7 +10804,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L102" s="189">
+      <c r="L102" s="184">
         <v>0</v>
       </c>
       <c r="M102" s="159">
@@ -10758,7 +10820,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="114"/>
       <c r="B103" s="35"/>
       <c r="C103" s="35" t="s">
@@ -10790,7 +10852,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L103" s="189">
+      <c r="L103" s="184">
         <v>0</v>
       </c>
       <c r="M103" s="159">
@@ -10806,7 +10868,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="114"/>
       <c r="B104" s="35"/>
       <c r="C104" s="35" t="s">
@@ -10835,7 +10897,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L104" s="189">
+      <c r="L104" s="184">
         <v>0</v>
       </c>
       <c r="M104" s="8">
@@ -10851,7 +10913,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="114"/>
       <c r="B105" s="35"/>
       <c r="C105" s="35" t="s">
@@ -10883,7 +10945,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L105" s="189">
+      <c r="L105" s="184">
         <v>0</v>
       </c>
       <c r="M105" s="8">
@@ -10899,7 +10961,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="114"/>
       <c r="B106" s="35"/>
       <c r="C106" s="35" t="s">
@@ -10931,7 +10993,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L106" s="189">
+      <c r="L106" s="184">
         <v>0</v>
       </c>
       <c r="M106" s="8">
@@ -10947,7 +11009,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="114"/>
       <c r="B107" s="35"/>
       <c r="C107" s="35" t="s">
@@ -10978,7 +11040,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L107" s="189">
+      <c r="L107" s="184">
         <v>0</v>
       </c>
       <c r="M107" s="8">
@@ -10994,7 +11056,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="114"/>
       <c r="B108" s="35"/>
       <c r="C108" s="35" t="s">
@@ -11026,7 +11088,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L108" s="189">
+      <c r="L108" s="184">
         <v>0</v>
       </c>
       <c r="M108" s="8">
@@ -11042,7 +11104,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="114"/>
       <c r="B109" s="35"/>
       <c r="C109" s="35" t="s">
@@ -11074,7 +11136,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L109" s="189">
+      <c r="L109" s="184">
         <v>0</v>
       </c>
       <c r="M109" s="8">
@@ -11090,7 +11152,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="114"/>
       <c r="B110" s="35"/>
       <c r="C110" s="35" t="s">
@@ -11122,7 +11184,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L110" s="189">
+      <c r="L110" s="184">
         <v>0</v>
       </c>
       <c r="M110" s="159">
@@ -11138,7 +11200,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="114"/>
       <c r="B111" s="35"/>
       <c r="C111" s="35" t="s">
@@ -11170,7 +11232,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L111" s="189">
+      <c r="L111" s="184">
         <v>0</v>
       </c>
       <c r="M111" s="159">
@@ -11186,7 +11248,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="114"/>
       <c r="B112" s="35"/>
       <c r="C112" s="35" t="s">
@@ -11218,7 +11280,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L112" s="189">
+      <c r="L112" s="184">
         <v>0</v>
       </c>
       <c r="M112" s="159">
@@ -11234,7 +11296,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A113" s="114"/>
       <c r="B113" s="35"/>
       <c r="C113" s="35" t="s">
@@ -11266,7 +11328,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L113" s="189">
+      <c r="L113" s="184">
         <v>0</v>
       </c>
       <c r="M113" s="159">
@@ -11282,7 +11344,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A114" s="114"/>
       <c r="B114" s="35"/>
       <c r="C114" s="35" t="s">
@@ -11314,7 +11376,7 @@
         <f t="shared" si="17"/>
         <v>33350</v>
       </c>
-      <c r="L114" s="189">
+      <c r="L114" s="184">
         <v>0</v>
       </c>
       <c r="M114" s="159">
@@ -11330,7 +11392,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A115" s="114"/>
       <c r="B115" s="35"/>
       <c r="C115" s="35" t="s">
@@ -11362,7 +11424,7 @@
         <f t="shared" ref="K115:K131" si="25">M$2*F115</f>
         <v>33350</v>
       </c>
-      <c r="L115" s="189">
+      <c r="L115" s="184">
         <v>0</v>
       </c>
       <c r="M115" s="159">
@@ -11378,47 +11440,47 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A116" s="114"/>
       <c r="B116" s="35"/>
-      <c r="C116" s="191" t="s">
+      <c r="C116" s="230" t="s">
         <v>154</v>
       </c>
-      <c r="D116" s="192" t="s">
+      <c r="D116" s="231" t="s">
         <v>184</v>
       </c>
-      <c r="E116" s="192" t="s">
-        <v>354</v>
-      </c>
-      <c r="F116" s="200">
+      <c r="E116" s="231" t="s">
+        <v>353</v>
+      </c>
+      <c r="F116" s="232">
         <v>2.3E-3</v>
       </c>
-      <c r="G116" s="195">
+      <c r="G116" s="233">
         <v>53224.98</v>
       </c>
-      <c r="H116" s="233">
+      <c r="H116" s="234">
         <v>27600</v>
       </c>
-      <c r="I116" s="196">
+      <c r="I116" s="235">
         <f t="shared" si="0"/>
         <v>25624.980000000003</v>
       </c>
-      <c r="J116" s="197">
+      <c r="J116" s="236">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K116" s="197">
+      <c r="K116" s="236">
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L116" s="198">
-        <v>0</v>
-      </c>
-      <c r="M116" s="199">
+      <c r="L116" s="237">
+        <v>0</v>
+      </c>
+      <c r="M116" s="238">
         <f t="shared" si="19"/>
         <v>58975.98</v>
       </c>
-      <c r="N116" s="199">
+      <c r="N116" s="238">
         <f t="shared" si="20"/>
         <v>62515.98</v>
       </c>
@@ -11427,43 +11489,43 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A117" s="114"/>
       <c r="B117" s="35"/>
-      <c r="C117" s="35" t="s">
+      <c r="C117" s="230" t="s">
         <v>155</v>
       </c>
-      <c r="D117" s="114" t="s">
+      <c r="D117" s="231" t="s">
         <v>184</v>
       </c>
-      <c r="E117" s="114"/>
-      <c r="F117" s="155">
+      <c r="E117" s="231"/>
+      <c r="F117" s="232">
         <v>2.3E-3</v>
       </c>
-      <c r="G117" s="147">
+      <c r="G117" s="233">
         <v>71302.990000000005</v>
       </c>
-      <c r="H117" s="44"/>
-      <c r="I117" s="156">
+      <c r="H117" s="234"/>
+      <c r="I117" s="235">
         <f t="shared" si="0"/>
         <v>71302.990000000005</v>
       </c>
-      <c r="J117" s="157">
+      <c r="J117" s="236">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K117" s="157">
+      <c r="K117" s="236">
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L117" s="189">
-        <v>0</v>
-      </c>
-      <c r="M117" s="159">
+      <c r="L117" s="237">
+        <v>0</v>
+      </c>
+      <c r="M117" s="238">
         <f t="shared" si="19"/>
         <v>104653.99</v>
       </c>
-      <c r="N117" s="159">
+      <c r="N117" s="238">
         <f t="shared" si="20"/>
         <v>110933.99</v>
       </c>
@@ -11472,46 +11534,46 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A118" s="114"/>
       <c r="B118" s="35"/>
-      <c r="C118" s="191" t="s">
+      <c r="C118" s="186" t="s">
         <v>156</v>
       </c>
-      <c r="D118" s="192" t="s">
+      <c r="D118" s="187" t="s">
         <v>185</v>
       </c>
-      <c r="E118" s="192"/>
-      <c r="F118" s="200">
+      <c r="E118" s="187"/>
+      <c r="F118" s="195">
         <v>2.3E-3</v>
       </c>
-      <c r="G118" s="195">
+      <c r="G118" s="190">
         <v>27601</v>
       </c>
-      <c r="H118" s="233">
+      <c r="H118" s="226">
         <f t="shared" ref="H118" si="26">G118</f>
         <v>27601</v>
       </c>
-      <c r="I118" s="196">
+      <c r="I118" s="191">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J118" s="197">
+      <c r="J118" s="192">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K118" s="197">
+      <c r="K118" s="192">
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L118" s="198">
-        <v>0</v>
-      </c>
-      <c r="M118" s="199">
+      <c r="L118" s="193">
+        <v>0</v>
+      </c>
+      <c r="M118" s="194">
         <f t="shared" si="19"/>
         <v>33351</v>
       </c>
-      <c r="N118" s="199">
+      <c r="N118" s="194">
         <f t="shared" si="20"/>
         <v>35353</v>
       </c>
@@ -11523,7 +11585,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A119" s="135"/>
       <c r="B119" s="35"/>
       <c r="C119" s="35" t="s">
@@ -11555,7 +11617,7 @@
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L119" s="189">
+      <c r="L119" s="184">
         <v>0</v>
       </c>
       <c r="M119" s="159">
@@ -11571,7 +11633,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A120" s="135"/>
       <c r="B120" s="35"/>
       <c r="C120" s="35" t="s">
@@ -11603,7 +11665,7 @@
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L120" s="189">
+      <c r="L120" s="184">
         <v>0</v>
       </c>
       <c r="M120" s="159">
@@ -11619,45 +11681,45 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A121" s="135"/>
       <c r="B121" s="35"/>
-      <c r="C121" s="35" t="s">
+      <c r="C121" s="230" t="s">
         <v>159</v>
       </c>
-      <c r="D121" s="114" t="s">
+      <c r="D121" s="231" t="s">
         <v>184</v>
       </c>
-      <c r="E121" s="114"/>
-      <c r="F121" s="155">
+      <c r="E121" s="231"/>
+      <c r="F121" s="232">
         <v>2.3E-3</v>
       </c>
-      <c r="G121" s="147">
+      <c r="G121" s="233">
         <v>48303.03</v>
       </c>
-      <c r="H121" s="44">
-        <v>0</v>
-      </c>
-      <c r="I121" s="156">
+      <c r="H121" s="234">
+        <v>0</v>
+      </c>
+      <c r="I121" s="235">
         <f t="shared" si="0"/>
         <v>48303.03</v>
       </c>
-      <c r="J121" s="157">
+      <c r="J121" s="236">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K121" s="157">
+      <c r="K121" s="236">
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L121" s="189">
-        <v>0</v>
-      </c>
-      <c r="M121" s="159">
+      <c r="L121" s="237">
+        <v>0</v>
+      </c>
+      <c r="M121" s="238">
         <f t="shared" si="19"/>
         <v>81654.03</v>
       </c>
-      <c r="N121" s="159">
+      <c r="N121" s="238">
         <f t="shared" si="20"/>
         <v>86554.03</v>
       </c>
@@ -11666,7 +11728,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A122" s="135"/>
       <c r="B122" s="35"/>
       <c r="C122" s="35" t="s">
@@ -11698,7 +11760,7 @@
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L122" s="189">
+      <c r="L122" s="184">
         <v>0</v>
       </c>
       <c r="M122" s="8">
@@ -11714,7 +11776,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A123" s="135"/>
       <c r="B123" s="35"/>
       <c r="C123" s="35" t="s">
@@ -11745,7 +11807,7 @@
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L123" s="189">
+      <c r="L123" s="184">
         <v>0</v>
       </c>
       <c r="M123" s="8">
@@ -11761,43 +11823,43 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A124" s="135"/>
       <c r="B124" s="35"/>
-      <c r="C124" s="35" t="s">
+      <c r="C124" s="230" t="s">
         <v>162</v>
       </c>
-      <c r="D124" s="114" t="s">
+      <c r="D124" s="231" t="s">
         <v>184</v>
       </c>
-      <c r="E124" s="114"/>
-      <c r="F124" s="94">
+      <c r="E124" s="231"/>
+      <c r="F124" s="232">
         <v>2.3E-3</v>
       </c>
-      <c r="G124" s="142">
+      <c r="G124" s="233">
         <v>71303.06</v>
       </c>
-      <c r="H124" s="90"/>
-      <c r="I124" s="56">
+      <c r="H124" s="234"/>
+      <c r="I124" s="235">
         <f t="shared" si="0"/>
         <v>71303.06</v>
       </c>
-      <c r="J124" s="26">
+      <c r="J124" s="236">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K124" s="26">
+      <c r="K124" s="236">
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L124" s="189">
-        <v>0</v>
-      </c>
-      <c r="M124" s="8">
+      <c r="L124" s="237">
+        <v>0</v>
+      </c>
+      <c r="M124" s="238">
         <f t="shared" si="19"/>
         <v>104654.06</v>
       </c>
-      <c r="N124" s="8">
+      <c r="N124" s="238">
         <f t="shared" si="20"/>
         <v>110934.06</v>
       </c>
@@ -11806,45 +11868,45 @@
         <v>1.0600000000000007</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A125" s="223"/>
-      <c r="B125" s="191"/>
-      <c r="C125" s="191" t="s">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A125" s="217"/>
+      <c r="B125" s="186"/>
+      <c r="C125" s="230" t="s">
         <v>163</v>
       </c>
-      <c r="D125" s="192" t="s">
+      <c r="D125" s="231" t="s">
         <v>184</v>
       </c>
-      <c r="E125" s="192"/>
-      <c r="F125" s="200">
+      <c r="E125" s="231"/>
+      <c r="F125" s="232">
         <v>2.3E-3</v>
       </c>
-      <c r="G125" s="195">
+      <c r="G125" s="233">
         <v>71303.070000000007</v>
       </c>
-      <c r="H125" s="233">
+      <c r="H125" s="234">
         <v>27600</v>
       </c>
-      <c r="I125" s="196">
+      <c r="I125" s="235">
         <f t="shared" si="0"/>
         <v>43703.070000000007</v>
       </c>
-      <c r="J125" s="197">
+      <c r="J125" s="236">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K125" s="197">
+      <c r="K125" s="236">
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L125" s="198">
-        <v>0</v>
-      </c>
-      <c r="M125" s="199">
+      <c r="L125" s="237">
+        <v>0</v>
+      </c>
+      <c r="M125" s="238">
         <f t="shared" si="19"/>
         <v>77054.070000000007</v>
       </c>
-      <c r="N125" s="199">
+      <c r="N125" s="238">
         <f t="shared" si="20"/>
         <v>81678.070000000007</v>
       </c>
@@ -11853,9 +11915,9 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A126" s="223"/>
-      <c r="B126" s="191"/>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A126" s="217"/>
+      <c r="B126" s="186"/>
       <c r="C126" s="35" t="s">
         <v>164</v>
       </c>
@@ -11885,7 +11947,7 @@
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L126" s="189">
+      <c r="L126" s="184">
         <v>0</v>
       </c>
       <c r="M126" s="159">
@@ -11901,7 +11963,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A127" s="135"/>
       <c r="B127" s="35"/>
       <c r="C127" s="35" t="s">
@@ -11933,7 +11995,7 @@
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L127" s="189">
+      <c r="L127" s="184">
         <v>0</v>
       </c>
       <c r="M127" s="159">
@@ -11949,7 +12011,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A128" s="135"/>
       <c r="B128" s="35"/>
       <c r="C128" s="35" t="s">
@@ -11981,7 +12043,7 @@
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L128" s="189">
+      <c r="L128" s="184">
         <v>0</v>
       </c>
       <c r="M128" s="8">
@@ -11997,7 +12059,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A129" s="135"/>
       <c r="B129" s="35"/>
       <c r="C129" s="35" t="s">
@@ -12029,7 +12091,7 @@
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L129" s="189">
+      <c r="L129" s="184">
         <v>0</v>
       </c>
       <c r="M129" s="8">
@@ -12045,7 +12107,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A130" s="135" t="s">
         <v>26</v>
       </c>
@@ -12079,7 +12141,7 @@
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L130" s="189">
+      <c r="L130" s="184">
         <v>0</v>
       </c>
       <c r="M130" s="8">
@@ -12095,7 +12157,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A131" s="135" t="s">
         <v>26</v>
       </c>
@@ -12129,7 +12191,7 @@
         <f t="shared" si="25"/>
         <v>33350</v>
       </c>
-      <c r="L131" s="189">
+      <c r="L131" s="184">
         <v>0</v>
       </c>
       <c r="M131" s="8">
@@ -12145,7 +12207,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A132" s="53" t="s">
         <v>26</v>
       </c>
@@ -12163,7 +12225,7 @@
       <c r="M132" s="5"/>
       <c r="N132" s="8"/>
     </row>
-    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="27"/>
       <c r="B133" s="27"/>
       <c r="C133" s="27"/>
@@ -12190,7 +12252,7 @@
         <f>SUM(K14:K132)</f>
         <v>14312661.692639999</v>
       </c>
-      <c r="L133" s="212">
+      <c r="L133" s="207">
         <f>SUM(L14:L132)</f>
         <v>136000</v>
       </c>
@@ -12204,41 +12266,41 @@
       </c>
       <c r="P133" s="59"/>
     </row>
-    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K134" s="61">
         <f>K133-L1</f>
         <v>3644929.4026400018</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="253"/>
-      <c r="D135" s="253"/>
-      <c r="E135" s="253"/>
-      <c r="F135" s="253"/>
-      <c r="G135" s="253"/>
-      <c r="H135" s="253"/>
-      <c r="I135" s="253"/>
-      <c r="J135" s="253"/>
-      <c r="K135" s="253"/>
-      <c r="L135" s="253"/>
-      <c r="M135" s="253"/>
-      <c r="N135" s="253"/>
-    </row>
-    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="253"/>
-      <c r="D136" s="253"/>
-      <c r="E136" s="253"/>
-      <c r="F136" s="253"/>
-      <c r="G136" s="253"/>
-      <c r="H136" s="253"/>
-      <c r="I136" s="253"/>
-      <c r="J136" s="253"/>
-      <c r="K136" s="253"/>
-      <c r="L136" s="253"/>
-      <c r="M136" s="253"/>
-      <c r="N136" s="253"/>
-    </row>
-    <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C135" s="266"/>
+      <c r="D135" s="266"/>
+      <c r="E135" s="266"/>
+      <c r="F135" s="266"/>
+      <c r="G135" s="266"/>
+      <c r="H135" s="266"/>
+      <c r="I135" s="266"/>
+      <c r="J135" s="266"/>
+      <c r="K135" s="266"/>
+      <c r="L135" s="266"/>
+      <c r="M135" s="266"/>
+      <c r="N135" s="266"/>
+    </row>
+    <row r="136" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C136" s="266"/>
+      <c r="D136" s="266"/>
+      <c r="E136" s="266"/>
+      <c r="F136" s="266"/>
+      <c r="G136" s="266"/>
+      <c r="H136" s="266"/>
+      <c r="I136" s="266"/>
+      <c r="J136" s="266"/>
+      <c r="K136" s="266"/>
+      <c r="L136" s="266"/>
+      <c r="M136" s="266"/>
+      <c r="N136" s="266"/>
+    </row>
+    <row r="137" spans="1:16" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="79"/>
       <c r="D137" s="79"/>
       <c r="E137" s="79"/>
@@ -12252,121 +12314,121 @@
       <c r="M137" s="79"/>
       <c r="N137" s="79"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C138" s="253" t="s">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C138" s="266" t="s">
         <v>264</v>
       </c>
-      <c r="D138" s="253"/>
-      <c r="E138" s="253"/>
-      <c r="F138" s="253"/>
-      <c r="G138" s="253"/>
-      <c r="H138" s="253"/>
-      <c r="I138" s="253"/>
-      <c r="J138" s="253"/>
-      <c r="K138" s="253"/>
-      <c r="L138" s="253"/>
-      <c r="M138" s="253"/>
-      <c r="N138" s="253"/>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C139" s="253"/>
-      <c r="D139" s="253"/>
-      <c r="E139" s="253"/>
-      <c r="F139" s="253"/>
-      <c r="G139" s="253"/>
-      <c r="H139" s="253"/>
-      <c r="I139" s="253"/>
-      <c r="J139" s="253"/>
-      <c r="K139" s="253"/>
-      <c r="L139" s="253"/>
-      <c r="M139" s="253"/>
-      <c r="N139" s="253"/>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C140" s="253"/>
-      <c r="D140" s="253"/>
-      <c r="E140" s="253"/>
-      <c r="F140" s="253"/>
-      <c r="G140" s="253"/>
-      <c r="H140" s="253"/>
-      <c r="I140" s="253"/>
-      <c r="J140" s="253"/>
-      <c r="K140" s="253"/>
-      <c r="L140" s="253"/>
-      <c r="M140" s="253"/>
-      <c r="N140" s="253"/>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C141" s="253"/>
-      <c r="D141" s="253"/>
-      <c r="E141" s="253"/>
-      <c r="F141" s="253"/>
-      <c r="G141" s="253"/>
-      <c r="H141" s="253"/>
-      <c r="I141" s="253"/>
-      <c r="J141" s="253"/>
-      <c r="K141" s="253"/>
-      <c r="L141" s="253"/>
-      <c r="M141" s="253"/>
-      <c r="N141" s="253"/>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C142" s="253"/>
-      <c r="D142" s="253"/>
-      <c r="E142" s="253"/>
-      <c r="F142" s="253"/>
-      <c r="G142" s="253"/>
-      <c r="H142" s="253"/>
-      <c r="I142" s="253"/>
-      <c r="J142" s="253"/>
-      <c r="K142" s="253"/>
-      <c r="L142" s="253"/>
-      <c r="M142" s="253"/>
-      <c r="N142" s="253"/>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C143" s="253"/>
-      <c r="D143" s="253"/>
-      <c r="E143" s="253"/>
-      <c r="F143" s="253"/>
-      <c r="G143" s="253"/>
-      <c r="H143" s="253"/>
-      <c r="I143" s="253"/>
-      <c r="J143" s="253"/>
-      <c r="K143" s="253"/>
-      <c r="L143" s="253"/>
-      <c r="M143" s="253"/>
-      <c r="N143" s="253"/>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C144" s="253"/>
-      <c r="D144" s="253"/>
-      <c r="E144" s="253"/>
-      <c r="F144" s="253"/>
-      <c r="G144" s="253"/>
-      <c r="H144" s="253"/>
-      <c r="I144" s="253"/>
-      <c r="J144" s="253"/>
-      <c r="K144" s="253"/>
-      <c r="L144" s="253"/>
-      <c r="M144" s="253"/>
-      <c r="N144" s="253"/>
-    </row>
-    <row r="145" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C145" s="253"/>
-      <c r="D145" s="253"/>
-      <c r="E145" s="253"/>
-      <c r="F145" s="253"/>
-      <c r="G145" s="253"/>
-      <c r="H145" s="253"/>
-      <c r="I145" s="253"/>
-      <c r="J145" s="253"/>
-      <c r="K145" s="253"/>
-      <c r="L145" s="253"/>
-      <c r="M145" s="253"/>
-      <c r="N145" s="253"/>
-    </row>
-    <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D138" s="266"/>
+      <c r="E138" s="266"/>
+      <c r="F138" s="266"/>
+      <c r="G138" s="266"/>
+      <c r="H138" s="266"/>
+      <c r="I138" s="266"/>
+      <c r="J138" s="266"/>
+      <c r="K138" s="266"/>
+      <c r="L138" s="266"/>
+      <c r="M138" s="266"/>
+      <c r="N138" s="266"/>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C139" s="266"/>
+      <c r="D139" s="266"/>
+      <c r="E139" s="266"/>
+      <c r="F139" s="266"/>
+      <c r="G139" s="266"/>
+      <c r="H139" s="266"/>
+      <c r="I139" s="266"/>
+      <c r="J139" s="266"/>
+      <c r="K139" s="266"/>
+      <c r="L139" s="266"/>
+      <c r="M139" s="266"/>
+      <c r="N139" s="266"/>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C140" s="266"/>
+      <c r="D140" s="266"/>
+      <c r="E140" s="266"/>
+      <c r="F140" s="266"/>
+      <c r="G140" s="266"/>
+      <c r="H140" s="266"/>
+      <c r="I140" s="266"/>
+      <c r="J140" s="266"/>
+      <c r="K140" s="266"/>
+      <c r="L140" s="266"/>
+      <c r="M140" s="266"/>
+      <c r="N140" s="266"/>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C141" s="266"/>
+      <c r="D141" s="266"/>
+      <c r="E141" s="266"/>
+      <c r="F141" s="266"/>
+      <c r="G141" s="266"/>
+      <c r="H141" s="266"/>
+      <c r="I141" s="266"/>
+      <c r="J141" s="266"/>
+      <c r="K141" s="266"/>
+      <c r="L141" s="266"/>
+      <c r="M141" s="266"/>
+      <c r="N141" s="266"/>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C142" s="266"/>
+      <c r="D142" s="266"/>
+      <c r="E142" s="266"/>
+      <c r="F142" s="266"/>
+      <c r="G142" s="266"/>
+      <c r="H142" s="266"/>
+      <c r="I142" s="266"/>
+      <c r="J142" s="266"/>
+      <c r="K142" s="266"/>
+      <c r="L142" s="266"/>
+      <c r="M142" s="266"/>
+      <c r="N142" s="266"/>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C143" s="266"/>
+      <c r="D143" s="266"/>
+      <c r="E143" s="266"/>
+      <c r="F143" s="266"/>
+      <c r="G143" s="266"/>
+      <c r="H143" s="266"/>
+      <c r="I143" s="266"/>
+      <c r="J143" s="266"/>
+      <c r="K143" s="266"/>
+      <c r="L143" s="266"/>
+      <c r="M143" s="266"/>
+      <c r="N143" s="266"/>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C144" s="266"/>
+      <c r="D144" s="266"/>
+      <c r="E144" s="266"/>
+      <c r="F144" s="266"/>
+      <c r="G144" s="266"/>
+      <c r="H144" s="266"/>
+      <c r="I144" s="266"/>
+      <c r="J144" s="266"/>
+      <c r="K144" s="266"/>
+      <c r="L144" s="266"/>
+      <c r="M144" s="266"/>
+      <c r="N144" s="266"/>
+    </row>
+    <row r="145" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C145" s="266"/>
+      <c r="D145" s="266"/>
+      <c r="E145" s="266"/>
+      <c r="F145" s="266"/>
+      <c r="G145" s="266"/>
+      <c r="H145" s="266"/>
+      <c r="I145" s="266"/>
+      <c r="J145" s="266"/>
+      <c r="K145" s="266"/>
+      <c r="L145" s="266"/>
+      <c r="M145" s="266"/>
+      <c r="N145" s="266"/>
+    </row>
+    <row r="146" spans="3:16" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="79"/>
       <c r="D146" s="79"/>
       <c r="E146" s="79"/>
@@ -12380,7 +12442,7 @@
       <c r="M146" s="79"/>
       <c r="N146" s="79"/>
     </row>
-    <row r="147" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:16" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="79"/>
       <c r="D147" s="79"/>
       <c r="E147" s="79"/>
@@ -12394,109 +12456,109 @@
       <c r="M147" s="79"/>
       <c r="N147" s="79"/>
     </row>
-    <row r="148" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C148" s="252" t="s">
+    <row r="148" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C148" s="265" t="s">
         <v>263</v>
       </c>
-      <c r="D148" s="252"/>
-      <c r="E148" s="252"/>
-      <c r="F148" s="252"/>
-      <c r="G148" s="252"/>
-      <c r="H148" s="252"/>
-      <c r="I148" s="252"/>
-      <c r="J148" s="252"/>
-      <c r="K148" s="252"/>
-      <c r="L148" s="252"/>
-      <c r="M148" s="252"/>
-      <c r="N148" s="252"/>
-    </row>
-    <row r="149" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C149" s="252"/>
-      <c r="D149" s="252"/>
-      <c r="E149" s="252"/>
-      <c r="F149" s="252"/>
-      <c r="G149" s="252"/>
-      <c r="H149" s="252"/>
-      <c r="I149" s="252"/>
-      <c r="J149" s="252"/>
-      <c r="K149" s="252"/>
-      <c r="L149" s="252"/>
-      <c r="M149" s="252"/>
-      <c r="N149" s="252"/>
-    </row>
-    <row r="150" spans="3:16" x14ac:dyDescent="0.25">
-      <c r="C150" s="252"/>
-      <c r="D150" s="252"/>
-      <c r="E150" s="252"/>
-      <c r="F150" s="252"/>
-      <c r="G150" s="252"/>
-      <c r="H150" s="252"/>
-      <c r="I150" s="252"/>
-      <c r="J150" s="252"/>
-      <c r="K150" s="252"/>
-      <c r="L150" s="252"/>
-      <c r="M150" s="252"/>
-      <c r="N150" s="252"/>
+      <c r="D148" s="265"/>
+      <c r="E148" s="265"/>
+      <c r="F148" s="265"/>
+      <c r="G148" s="265"/>
+      <c r="H148" s="265"/>
+      <c r="I148" s="265"/>
+      <c r="J148" s="265"/>
+      <c r="K148" s="265"/>
+      <c r="L148" s="265"/>
+      <c r="M148" s="265"/>
+      <c r="N148" s="265"/>
+    </row>
+    <row r="149" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C149" s="265"/>
+      <c r="D149" s="265"/>
+      <c r="E149" s="265"/>
+      <c r="F149" s="265"/>
+      <c r="G149" s="265"/>
+      <c r="H149" s="265"/>
+      <c r="I149" s="265"/>
+      <c r="J149" s="265"/>
+      <c r="K149" s="265"/>
+      <c r="L149" s="265"/>
+      <c r="M149" s="265"/>
+      <c r="N149" s="265"/>
+    </row>
+    <row r="150" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C150" s="265"/>
+      <c r="D150" s="265"/>
+      <c r="E150" s="265"/>
+      <c r="F150" s="265"/>
+      <c r="G150" s="265"/>
+      <c r="H150" s="265"/>
+      <c r="I150" s="265"/>
+      <c r="J150" s="265"/>
+      <c r="K150" s="265"/>
+      <c r="L150" s="265"/>
+      <c r="M150" s="265"/>
+      <c r="N150" s="265"/>
       <c r="P150" s="86">
         <f>L1-K133</f>
         <v>-3644929.4026400018</v>
       </c>
     </row>
-    <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="252"/>
-      <c r="D151" s="252"/>
-      <c r="E151" s="252"/>
-      <c r="F151" s="252"/>
-      <c r="G151" s="252"/>
-      <c r="H151" s="252"/>
-      <c r="I151" s="252"/>
-      <c r="J151" s="252"/>
-      <c r="K151" s="252"/>
-      <c r="L151" s="252"/>
-      <c r="M151" s="252"/>
-      <c r="N151" s="252"/>
-    </row>
-    <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="252"/>
-      <c r="D152" s="252"/>
-      <c r="E152" s="252"/>
-      <c r="F152" s="252"/>
-      <c r="G152" s="252"/>
-      <c r="H152" s="252"/>
-      <c r="I152" s="252"/>
-      <c r="J152" s="252"/>
-      <c r="K152" s="252"/>
-      <c r="L152" s="252"/>
-      <c r="M152" s="252"/>
-      <c r="N152" s="252"/>
-    </row>
-    <row r="153" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="252"/>
-      <c r="D153" s="252"/>
-      <c r="E153" s="252"/>
-      <c r="F153" s="252"/>
-      <c r="G153" s="252"/>
-      <c r="H153" s="252"/>
-      <c r="I153" s="252"/>
-      <c r="J153" s="252"/>
-      <c r="K153" s="252"/>
-      <c r="L153" s="252"/>
-      <c r="M153" s="252"/>
-      <c r="N153" s="252"/>
-    </row>
-    <row r="154" spans="3:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="252"/>
-      <c r="D154" s="252"/>
-      <c r="E154" s="252"/>
-      <c r="F154" s="252"/>
-      <c r="G154" s="252"/>
-      <c r="H154" s="252"/>
-      <c r="I154" s="252"/>
-      <c r="J154" s="252"/>
-      <c r="K154" s="252"/>
-      <c r="L154" s="252"/>
-      <c r="M154" s="252"/>
-      <c r="N154" s="252"/>
+    <row r="151" spans="3:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C151" s="265"/>
+      <c r="D151" s="265"/>
+      <c r="E151" s="265"/>
+      <c r="F151" s="265"/>
+      <c r="G151" s="265"/>
+      <c r="H151" s="265"/>
+      <c r="I151" s="265"/>
+      <c r="J151" s="265"/>
+      <c r="K151" s="265"/>
+      <c r="L151" s="265"/>
+      <c r="M151" s="265"/>
+      <c r="N151" s="265"/>
+    </row>
+    <row r="152" spans="3:16" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" s="265"/>
+      <c r="D152" s="265"/>
+      <c r="E152" s="265"/>
+      <c r="F152" s="265"/>
+      <c r="G152" s="265"/>
+      <c r="H152" s="265"/>
+      <c r="I152" s="265"/>
+      <c r="J152" s="265"/>
+      <c r="K152" s="265"/>
+      <c r="L152" s="265"/>
+      <c r="M152" s="265"/>
+      <c r="N152" s="265"/>
+    </row>
+    <row r="153" spans="3:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="265"/>
+      <c r="D153" s="265"/>
+      <c r="E153" s="265"/>
+      <c r="F153" s="265"/>
+      <c r="G153" s="265"/>
+      <c r="H153" s="265"/>
+      <c r="I153" s="265"/>
+      <c r="J153" s="265"/>
+      <c r="K153" s="265"/>
+      <c r="L153" s="265"/>
+      <c r="M153" s="265"/>
+      <c r="N153" s="265"/>
+    </row>
+    <row r="154" spans="3:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C154" s="265"/>
+      <c r="D154" s="265"/>
+      <c r="E154" s="265"/>
+      <c r="F154" s="265"/>
+      <c r="G154" s="265"/>
+      <c r="H154" s="265"/>
+      <c r="I154" s="265"/>
+      <c r="J154" s="265"/>
+      <c r="K154" s="265"/>
+      <c r="L154" s="265"/>
+      <c r="M154" s="265"/>
+      <c r="N154" s="265"/>
     </row>
   </sheetData>
   <mergeCells count="21">
@@ -12531,20 +12593,195 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
-  <dimension ref="B4:G4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B4:K19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="214" t="s">
-        <v>330</v>
-      </c>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="213"/>
-      <c r="F4" s="213"/>
-      <c r="G4" s="213"/>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="239" t="s">
+        <v>367</v>
+      </c>
+      <c r="C4" s="240"/>
+      <c r="D4" s="240"/>
+      <c r="E4" s="240"/>
+      <c r="F4" s="240"/>
+      <c r="G4" s="240"/>
+      <c r="H4" s="240"/>
+      <c r="I4" s="240"/>
+      <c r="J4" s="240"/>
+      <c r="K4" s="240"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="240"/>
+      <c r="C5" s="240"/>
+      <c r="D5" s="240"/>
+      <c r="E5" s="240"/>
+      <c r="F5" s="240"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="240"/>
+      <c r="I5" s="240"/>
+      <c r="J5" s="240"/>
+      <c r="K5" s="240"/>
+    </row>
+    <row r="6" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="241" t="s">
+        <v>362</v>
+      </c>
+      <c r="C6" s="240"/>
+      <c r="D6" s="240"/>
+      <c r="E6" s="240"/>
+      <c r="F6" s="240"/>
+      <c r="G6" s="240"/>
+      <c r="H6" s="240"/>
+      <c r="I6" s="240"/>
+      <c r="J6" s="240"/>
+      <c r="K6" s="240"/>
+    </row>
+    <row r="7" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B7" s="241" t="s">
+        <v>363</v>
+      </c>
+      <c r="C7" s="240"/>
+      <c r="D7" s="240"/>
+      <c r="E7" s="240"/>
+      <c r="F7" s="240"/>
+      <c r="G7" s="240"/>
+      <c r="H7" s="240"/>
+      <c r="I7" s="240"/>
+      <c r="J7" s="240"/>
+      <c r="K7" s="240"/>
+    </row>
+    <row r="8" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="241" t="s">
+        <v>364</v>
+      </c>
+      <c r="C8" s="240"/>
+      <c r="D8" s="240"/>
+      <c r="E8" s="240"/>
+      <c r="F8" s="240"/>
+      <c r="G8" s="240"/>
+      <c r="H8" s="240"/>
+      <c r="I8" s="240"/>
+      <c r="J8" s="240"/>
+      <c r="K8" s="240"/>
+    </row>
+    <row r="9" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="241" t="s">
+        <v>365</v>
+      </c>
+      <c r="C9" s="240"/>
+      <c r="D9" s="240"/>
+      <c r="E9" s="240"/>
+      <c r="F9" s="240"/>
+      <c r="G9" s="240"/>
+      <c r="H9" s="240"/>
+      <c r="I9" s="240"/>
+      <c r="J9" s="240"/>
+      <c r="K9" s="240"/>
+    </row>
+    <row r="10" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="241" t="s">
+        <v>366</v>
+      </c>
+      <c r="C10" s="240"/>
+      <c r="D10" s="240"/>
+      <c r="E10" s="240"/>
+      <c r="F10" s="240"/>
+      <c r="G10" s="240"/>
+      <c r="H10" s="240"/>
+      <c r="I10" s="240"/>
+      <c r="J10" s="240"/>
+      <c r="K10" s="240"/>
+    </row>
+    <row r="13" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="311" t="s">
+        <v>368</v>
+      </c>
+      <c r="C13" s="311"/>
+      <c r="D13" s="311"/>
+      <c r="E13" s="311"/>
+      <c r="F13" s="311"/>
+      <c r="G13" s="311"/>
+      <c r="H13" s="311"/>
+      <c r="I13" s="311"/>
+      <c r="J13" s="311"/>
+      <c r="K13" s="311"/>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="311"/>
+      <c r="C14" s="311"/>
+      <c r="D14" s="311"/>
+      <c r="E14" s="311"/>
+      <c r="F14" s="311"/>
+      <c r="G14" s="311"/>
+      <c r="H14" s="311"/>
+      <c r="I14" s="311"/>
+      <c r="J14" s="311"/>
+      <c r="K14" s="311"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="311"/>
+      <c r="C15" s="311"/>
+      <c r="D15" s="311"/>
+      <c r="E15" s="311"/>
+      <c r="F15" s="311"/>
+      <c r="G15" s="311"/>
+      <c r="H15" s="311"/>
+      <c r="I15" s="311"/>
+      <c r="J15" s="311"/>
+      <c r="K15" s="311"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="311"/>
+      <c r="C16" s="311"/>
+      <c r="D16" s="311"/>
+      <c r="E16" s="311"/>
+      <c r="F16" s="311"/>
+      <c r="G16" s="311"/>
+      <c r="H16" s="311"/>
+      <c r="I16" s="311"/>
+      <c r="J16" s="311"/>
+      <c r="K16" s="311"/>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17" s="311"/>
+      <c r="C17" s="311"/>
+      <c r="D17" s="311"/>
+      <c r="E17" s="311"/>
+      <c r="F17" s="311"/>
+      <c r="G17" s="311"/>
+      <c r="H17" s="311"/>
+      <c r="I17" s="311"/>
+      <c r="J17" s="311"/>
+      <c r="K17" s="311"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="311"/>
+      <c r="C18" s="311"/>
+      <c r="D18" s="311"/>
+      <c r="E18" s="311"/>
+      <c r="F18" s="311"/>
+      <c r="G18" s="311"/>
+      <c r="H18" s="311"/>
+      <c r="I18" s="311"/>
+      <c r="J18" s="311"/>
+      <c r="K18" s="311"/>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="311"/>
+      <c r="C19" s="311"/>
+      <c r="D19" s="311"/>
+      <c r="E19" s="311"/>
+      <c r="F19" s="311"/>
+      <c r="G19" s="311"/>
+      <c r="H19" s="311"/>
+      <c r="I19" s="311"/>
+      <c r="J19" s="311"/>
+      <c r="K19" s="311"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B13:K19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -12552,34 +12789,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0166F049-50A4-4ACA-9F6E-1C2F2AD24458}">
   <dimension ref="A2:J27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.5703125" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.5546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C3" s="284" t="str">
+    <row r="2" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C3" s="297" t="str">
         <f>RESUMEN!C5</f>
         <v>PERÍODO: NOVIEMBRE</v>
       </c>
-      <c r="D3" s="285"/>
-      <c r="E3" s="285"/>
-      <c r="F3" s="285" t="str">
+      <c r="D3" s="298"/>
+      <c r="E3" s="298"/>
+      <c r="F3" s="298" t="str">
         <f>[1]RESUMEN!A22</f>
         <v xml:space="preserve">Sueldo encargada Sonia Arzamendia Galeano </v>
       </c>
-      <c r="G3" s="285"/>
-      <c r="H3" s="285"/>
-      <c r="I3" s="285"/>
-      <c r="J3" s="286"/>
-    </row>
-    <row r="4" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="G3" s="298"/>
+      <c r="H3" s="298"/>
+      <c r="I3" s="298"/>
+      <c r="J3" s="299"/>
+    </row>
+    <row r="4" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
-      <c r="J4" s="215"/>
-    </row>
-    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="J4" s="209"/>
+    </row>
+    <row r="5" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="str">
         <f>RESUMEN!A26</f>
         <v xml:space="preserve">Haberes </v>
@@ -12588,13 +12825,13 @@
         <f>RESUMEN!D26</f>
         <v>1042462</v>
       </c>
-      <c r="H5" s="282" t="s">
-        <v>331</v>
-      </c>
-      <c r="I5" s="282"/>
-      <c r="J5" s="283"/>
-    </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H5" s="295" t="s">
+        <v>330</v>
+      </c>
+      <c r="I5" s="295"/>
+      <c r="J5" s="296"/>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="str">
         <f>RESUMEN!A27</f>
         <v>Plus pileta</v>
@@ -12603,13 +12840,13 @@
         <f>RESUMEN!D27</f>
         <v>36382.699999999997</v>
       </c>
-      <c r="H6" s="282" t="s">
-        <v>332</v>
-      </c>
-      <c r="I6" s="282"/>
-      <c r="J6" s="283"/>
-    </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H6" s="295" t="s">
+        <v>331</v>
+      </c>
+      <c r="I6" s="295"/>
+      <c r="J6" s="296"/>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="str">
         <f>RESUMEN!A28</f>
         <v>Plus retiro de basura</v>
@@ -12618,11 +12855,11 @@
         <f>RESUMEN!D28</f>
         <v>126784</v>
       </c>
-      <c r="H7" s="282"/>
-      <c r="I7" s="282"/>
-      <c r="J7" s="283"/>
-    </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H7" s="295"/>
+      <c r="I7" s="295"/>
+      <c r="J7" s="296"/>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C8" s="1" t="str">
         <f>RESUMEN!A29</f>
         <v>Plus cochera</v>
@@ -12631,9 +12868,9 @@
         <f>RESUMEN!D29</f>
         <v>21627.4</v>
       </c>
-      <c r="J8" s="215"/>
-    </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="J8" s="209"/>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C9" s="1" t="str">
         <f>RESUMEN!A30</f>
         <v>Adicional Viaticos</v>
@@ -12642,13 +12879,13 @@
         <f>RESUMEN!D30</f>
         <v>60810.3</v>
       </c>
-      <c r="H9" s="282" t="s">
-        <v>333</v>
-      </c>
-      <c r="I9" s="282"/>
-      <c r="J9" s="283"/>
-    </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H9" s="295" t="s">
+        <v>332</v>
+      </c>
+      <c r="I9" s="295"/>
+      <c r="J9" s="296"/>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C10" s="1" t="str">
         <f>RESUMEN!A31</f>
         <v>Adicional remuneracion</v>
@@ -12657,72 +12894,72 @@
         <f>RESUMEN!D31</f>
         <v>50000</v>
       </c>
-      <c r="H10" s="282" t="s">
-        <v>332</v>
-      </c>
-      <c r="I10" s="282"/>
-      <c r="J10" s="283"/>
-    </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H10" s="295" t="s">
+        <v>331</v>
+      </c>
+      <c r="I10" s="295"/>
+      <c r="J10" s="296"/>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
-      <c r="H11" s="282"/>
-      <c r="I11" s="282"/>
-      <c r="J11" s="283"/>
-    </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C12" s="218" t="s">
+      <c r="H11" s="295"/>
+      <c r="I11" s="295"/>
+      <c r="J11" s="296"/>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="212" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="219">
+      <c r="G12" s="213">
         <f>SUM(G5:G11)</f>
         <v>1338066.3999999999</v>
       </c>
-      <c r="J12" s="215"/>
-    </row>
-    <row r="13" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="220"/>
-      <c r="D13" s="221"/>
-      <c r="E13" s="221"/>
-      <c r="F13" s="221"/>
-      <c r="G13" s="221"/>
-      <c r="H13" s="221"/>
-      <c r="I13" s="221"/>
-      <c r="J13" s="222"/>
-    </row>
-    <row r="15" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C16" s="284" t="str">
+      <c r="J12" s="209"/>
+    </row>
+    <row r="13" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C13" s="214"/>
+      <c r="D13" s="215"/>
+      <c r="E13" s="215"/>
+      <c r="F13" s="215"/>
+      <c r="G13" s="215"/>
+      <c r="H13" s="215"/>
+      <c r="I13" s="215"/>
+      <c r="J13" s="216"/>
+    </row>
+    <row r="15" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="297" t="str">
         <f>C3</f>
         <v>PERÍODO: NOVIEMBRE</v>
       </c>
-      <c r="D16" s="285"/>
-      <c r="E16" s="285"/>
-      <c r="F16" s="285" t="str">
+      <c r="D16" s="298"/>
+      <c r="E16" s="298"/>
+      <c r="F16" s="298" t="str">
         <f>[1]RESUMEN!A30</f>
         <v>Sueldo encargada Miriam</v>
       </c>
-      <c r="G16" s="285"/>
-      <c r="H16" s="285"/>
-      <c r="I16" s="285"/>
-      <c r="J16" s="286"/>
-    </row>
-    <row r="17" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="G16" s="298"/>
+      <c r="H16" s="298"/>
+      <c r="I16" s="298"/>
+      <c r="J16" s="299"/>
+    </row>
+    <row r="17" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C17" s="1"/>
-      <c r="J17" s="215"/>
-    </row>
-    <row r="18" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="J17" s="209"/>
+    </row>
+    <row r="18" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C18" s="1"/>
       <c r="G18" s="43"/>
-      <c r="H18" s="282" t="s">
-        <v>331</v>
-      </c>
-      <c r="I18" s="282"/>
-      <c r="J18" s="283"/>
-    </row>
-    <row r="19" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H18" s="295" t="s">
+        <v>330</v>
+      </c>
+      <c r="I18" s="295"/>
+      <c r="J18" s="296"/>
+    </row>
+    <row r="19" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="str">
         <f>RESUMEN!A34</f>
         <v xml:space="preserve">Haberes </v>
@@ -12731,13 +12968,13 @@
         <f>RESUMEN!D34</f>
         <v>521231</v>
       </c>
-      <c r="H19" s="282" t="s">
-        <v>332</v>
-      </c>
-      <c r="I19" s="282"/>
-      <c r="J19" s="283"/>
-    </row>
-    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H19" s="295" t="s">
+        <v>331</v>
+      </c>
+      <c r="I19" s="295"/>
+      <c r="J19" s="296"/>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" s="1" t="str">
         <f>RESUMEN!A35</f>
         <v>Horas extras</v>
@@ -12746,11 +12983,11 @@
         <f>RESUMEN!D35</f>
         <v>100235</v>
       </c>
-      <c r="H20" s="282"/>
-      <c r="I20" s="282"/>
-      <c r="J20" s="283"/>
-    </row>
-    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H20" s="295"/>
+      <c r="I20" s="295"/>
+      <c r="J20" s="296"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C21" s="1" t="str">
         <f>RESUMEN!A36</f>
         <v>Plus pileta</v>
@@ -12759,9 +12996,9 @@
         <f>RESUMEN!D36</f>
         <v>36382.699999999997</v>
       </c>
-      <c r="J21" s="215"/>
-    </row>
-    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="J21" s="209"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C22" s="1" t="str">
         <f>RESUMEN!A37</f>
         <v>Plus retiro de basura</v>
@@ -12770,13 +13007,13 @@
         <f>RESUMEN!D37</f>
         <v>126784</v>
       </c>
-      <c r="H22" s="282" t="s">
-        <v>333</v>
-      </c>
-      <c r="I22" s="282"/>
-      <c r="J22" s="283"/>
-    </row>
-    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H22" s="295" t="s">
+        <v>332</v>
+      </c>
+      <c r="I22" s="295"/>
+      <c r="J22" s="296"/>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C23" s="1" t="str">
         <f>RESUMEN!A38</f>
         <v>Plus cochera</v>
@@ -12785,13 +13022,13 @@
         <f>RESUMEN!D38</f>
         <v>21627.4</v>
       </c>
-      <c r="H23" s="282" t="s">
-        <v>332</v>
-      </c>
-      <c r="I23" s="282"/>
-      <c r="J23" s="283"/>
-    </row>
-    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H23" s="295" t="s">
+        <v>331</v>
+      </c>
+      <c r="I23" s="295"/>
+      <c r="J23" s="296"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C24" s="1" t="str">
         <f>RESUMEN!A39</f>
         <v>Adicional Viaticos</v>
@@ -12800,11 +13037,11 @@
         <f>RESUMEN!D39</f>
         <v>60810.3</v>
       </c>
-      <c r="H24" s="282"/>
-      <c r="I24" s="282"/>
-      <c r="J24" s="283"/>
-    </row>
-    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
+      <c r="H24" s="295"/>
+      <c r="I24" s="295"/>
+      <c r="J24" s="296"/>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C25" s="1" t="str">
         <f>RESUMEN!A40</f>
         <v>Adicional remuneracion</v>
@@ -12813,32 +13050,32 @@
         <f>RESUMEN!D40</f>
         <v>50000</v>
       </c>
-      <c r="H25" s="216"/>
-      <c r="I25" s="216"/>
-      <c r="J25" s="217"/>
-    </row>
-    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C26" s="218" t="s">
+      <c r="H25" s="210"/>
+      <c r="I25" s="210"/>
+      <c r="J25" s="211"/>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C26" s="212" t="s">
         <v>17</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="219">
+      <c r="G26" s="213">
         <f>SUM(G18:G25)</f>
         <v>917070.4</v>
       </c>
-      <c r="J26" s="215"/>
-    </row>
-    <row r="27" spans="3:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="220"/>
-      <c r="D27" s="221"/>
-      <c r="E27" s="221"/>
-      <c r="F27" s="221"/>
-      <c r="G27" s="221"/>
-      <c r="H27" s="221"/>
-      <c r="I27" s="221"/>
-      <c r="J27" s="222"/>
+      <c r="J26" s="209"/>
+    </row>
+    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C27" s="214"/>
+      <c r="D27" s="215"/>
+      <c r="E27" s="215"/>
+      <c r="F27" s="215"/>
+      <c r="G27" s="215"/>
+      <c r="H27" s="215"/>
+      <c r="I27" s="215"/>
+      <c r="J27" s="216"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -12863,18 +13100,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A8B3D07-243A-48F3-942B-AB44D486DEC8}">
   <dimension ref="C4:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C4" s="287" t="s">
+    <row r="4" spans="3:4" x14ac:dyDescent="0.3">
+      <c r="C4" s="300" t="s">
         <v>286</v>
       </c>
-      <c r="D4" s="287"/>
-    </row>
-    <row r="5" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="D4" s="300"/>
+    </row>
+    <row r="5" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C5" s="145">
         <v>52141.08</v>
       </c>
@@ -12882,7 +13119,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="6" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C6" s="145">
         <v>67140.100000000006</v>
       </c>
@@ -12890,7 +13127,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="7" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C7" s="145">
         <v>52121.11</v>
       </c>
@@ -12898,7 +13135,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="8" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C8" s="145">
         <v>67885.119999999995</v>
       </c>
@@ -12906,7 +13143,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="9" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C9" s="145">
         <v>67140.160000000003</v>
       </c>
@@ -12914,7 +13151,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="10" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C10" s="145">
         <v>62141.17</v>
       </c>
@@ -12922,7 +13159,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="11" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C11" s="145">
         <v>67855.179999999993</v>
       </c>
@@ -12930,7 +13167,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="12" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C12" s="145">
         <v>62141.23</v>
       </c>
@@ -12938,7 +13175,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="13" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C13" s="145">
         <v>67855.240000000005</v>
       </c>
@@ -12946,7 +13183,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="14" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C14" s="145">
         <f>SUM(C5:C13)</f>
         <v>566420.39</v>
